--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1_제출서류 현황'!$A$3:$G$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_불일치·확인 필요'!$A$3:$F$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3_등급 조정 내역'!$A$3:$J$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_증빙자료 수집 목록'!$A$3:$I$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_증빙자료 수집 목록'!$A$3:$I$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5_확인 후 등급 변동'!$A$3:$D$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1575,6 +1575,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="24">
       <c r="B27" s="36" t="inlineStr">
         <is>
@@ -1679,6 +1680,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="24">
       <c r="A3" s="27" t="inlineStr">
         <is>
@@ -2285,6 +2287,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="24">
       <c r="A3" s="28" t="inlineStr">
         <is>
@@ -4281,7 +4284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="23" min="1" max="1"/>
@@ -4381,7 +4384,7 @@
       </c>
       <c r="F4" s="29" t="inlineStr">
         <is>
-          <t>Smartship 재고 입고신청 화면 캡처</t>
+          <t>Smartship(OMS) 재고 입고 신청 화면</t>
         </is>
       </c>
       <c r="G4" s="30" t="inlineStr">
@@ -4418,7 +4421,7 @@
       </c>
       <c r="F5" s="29" t="inlineStr">
         <is>
-          <t>SW 입고신청 화면(C1~CC 상태) 캡처</t>
+          <t>SW(WMS) 입고신청 화면 – 고객 신청 후 상태별 조회</t>
         </is>
       </c>
       <c r="G5" s="30" t="inlineStr">
@@ -4455,7 +4458,7 @@
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>SW 입고신청 화면 도착예정일 조회 캡처</t>
+          <t>SW(WMS) 입고신청 화면 – 도착예정일 기준 조회</t>
         </is>
       </c>
       <c r="G6" s="30" t="inlineStr">
@@ -4566,7 +4569,7 @@
       </c>
       <c r="F9" s="46" t="inlineStr">
         <is>
-          <t>도착 처리 화면(PDA·PC)</t>
+          <t>SW(WMS) 입고신청 화면 – 도착 처리 PC/PDA 화면</t>
         </is>
       </c>
       <c r="G9" s="30" t="inlineStr">
@@ -4603,7 +4606,7 @@
       </c>
       <c r="F10" s="46" t="inlineStr">
         <is>
-          <t>작업자 추적 화면(WMS-입고 공정) 현재·레포트 캡처</t>
+          <t>SW(WMS) 공정별 인원관리 – 현재 투입 인원(WMS-입고 공정)</t>
         </is>
       </c>
       <c r="G10" s="30" t="inlineStr">
@@ -4620,32 +4623,32 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>1.1.3</t>
+          <t>1.1.2</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>상품 검수/검품/분류</t>
+          <t>하역 작업</t>
         </is>
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>p.9</t>
+          <t>p.8</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F11" s="30" t="inlineStr">
-        <is>
-          <t>입고 검수대 PDA 스캔 작업 사진</t>
+          <t>[사진 5]</t>
+        </is>
+      </c>
+      <c r="F11" s="46" t="inlineStr">
+        <is>
+          <t>SW(WMS) 공정별 인원관리 – 기간별 작업 레포트</t>
         </is>
       </c>
       <c r="G11" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H11" s="29" t="n"/>
@@ -4672,17 +4675,17 @@
       </c>
       <c r="E12" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>입고 SKU 화면(도착·손상수량 입력) 캡처</t>
+          <t>입고 검수대 PDA 스캔 작업 사진</t>
         </is>
       </c>
       <c r="G12" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H12" s="29" t="n"/>
@@ -4709,17 +4712,17 @@
       </c>
       <c r="E13" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F13" s="30" t="inlineStr">
         <is>
-          <t>입고 검수 기록서 양식</t>
+          <t>SW 모바일(PDA) 입고 SKU 화면 – SKU 수량 검수(도착·손상수량 입력)</t>
         </is>
       </c>
       <c r="G13" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H13" s="29" t="n"/>
@@ -4731,32 +4734,32 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>1.1.4</t>
+          <t>1.1.3</t>
         </is>
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>제품정보의 인식 및 등록</t>
+          <t>상품 검수/검품/분류</t>
         </is>
       </c>
       <c r="D14" s="29" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>p.9</t>
         </is>
       </c>
       <c r="E14" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>입고 SKU 화면 "정의하기"(SKU 개별 정의) 캡처</t>
+          <t>SW(WMS) 입고신청 화면 – 입고 신청서 출력물(하차·검수 수량 기록)</t>
         </is>
       </c>
       <c r="G14" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H14" s="29" t="n"/>
@@ -4768,27 +4771,27 @@
       </c>
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>1.1.4</t>
+          <t>1.1.3</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>제품정보의 인식 및 등록</t>
+          <t>상품 검수/검품/분류</t>
         </is>
       </c>
       <c r="D15" s="29" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>p.9</t>
         </is>
       </c>
       <c r="E15" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F15" s="29" t="inlineStr">
-        <is>
-          <t>SKU 관리 화면 캡처</t>
+          <t>[사진 4]</t>
+        </is>
+      </c>
+      <c r="F15" s="30" t="inlineStr">
+        <is>
+          <t>SW 모바일(PDA) 화면 – 수량 불일치 경고</t>
         </is>
       </c>
       <c r="G15" s="30" t="inlineStr">
@@ -4820,12 +4823,12 @@
       </c>
       <c r="E16" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
-        </is>
-      </c>
-      <c r="F16" s="29" t="inlineStr">
-        <is>
-          <t>SKU 라벨 출력·부착 사진</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>SW 모바일(PDA) 화면 – SKU 개별 정의</t>
         </is>
       </c>
       <c r="G16" s="30" t="inlineStr">
@@ -4842,27 +4845,27 @@
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>1.1.5</t>
+          <t>1.1.4</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>입고 처리</t>
+          <t>제품정보의 인식 및 등록</t>
         </is>
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>p.11</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F17" s="30" t="inlineStr">
-        <is>
-          <t>입고 확정 화면 캡처</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F17" s="29" t="inlineStr">
+        <is>
+          <t>SW(WMS) SKU 관리 화면 – 정의·미정의 SKU 현황</t>
         </is>
       </c>
       <c r="G17" s="30" t="inlineStr">
@@ -4879,27 +4882,27 @@
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>1.1.5</t>
+          <t>1.1.4</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>입고 처리</t>
+          <t>제품정보의 인식 및 등록</t>
         </is>
       </c>
       <c r="D18" s="29" t="inlineStr">
         <is>
-          <t>p.11</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>Smartship 재고 반영 화면 캡처</t>
+          <t>SKU 라벨 출력·부착 사진</t>
         </is>
       </c>
       <c r="G18" s="30" t="inlineStr">
@@ -4931,12 +4934,12 @@
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
-        </is>
-      </c>
-      <c r="F19" s="29" t="inlineStr">
-        <is>
-          <t>입고 화물 수량 일괄 입력 화면 캡처</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F19" s="30" t="inlineStr">
+        <is>
+          <t>SW(WMS) 입고 확정 – 도착완료 → 입고완료 처리</t>
         </is>
       </c>
       <c r="G19" s="30" t="inlineStr">
@@ -4953,27 +4956,27 @@
       </c>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>1.1.5</t>
         </is>
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>작업정보의 정보제공</t>
+          <t>입고 처리</t>
         </is>
       </c>
       <c r="D20" s="29" t="inlineStr">
         <is>
-          <t>p.12</t>
+          <t>p.11</t>
         </is>
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>PDA 추천 로케이션 화면 캡처</t>
+          <t>Smartship(OMS) 입고신청 목록 – 입고완료·실제입고수량 반영</t>
         </is>
       </c>
       <c r="G20" s="30" t="inlineStr">
@@ -4990,32 +4993,32 @@
       </c>
       <c r="B21" s="29" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>1.1.5</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>작업정보의 정보제공</t>
+          <t>입고 처리</t>
         </is>
       </c>
       <c r="D21" s="29" t="inlineStr">
         <is>
-          <t>p.12</t>
+          <t>p.11</t>
         </is>
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F21" s="30" t="inlineStr">
-        <is>
-          <t>적치 작업 사진</t>
+          <t>[사진 3]</t>
+        </is>
+      </c>
+      <c r="F21" s="29" t="inlineStr">
+        <is>
+          <t>SW 모바일(PDA) 입고 SKU 화면 – SKU별 도착수량 입력·배치 선반 지정</t>
         </is>
       </c>
       <c r="G21" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H21" s="29" t="n"/>
@@ -5027,32 +5030,32 @@
       </c>
       <c r="B22" s="29" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.1.5</t>
         </is>
       </c>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>적치장소 이동</t>
+          <t>입고 처리</t>
         </is>
       </c>
       <c r="D22" s="29" t="inlineStr">
         <is>
-          <t>p.13</t>
+          <t>p.11</t>
         </is>
       </c>
       <c r="E22" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F22" s="30" t="inlineStr">
-        <is>
-          <t>지게차 적치 작업 사진</t>
+          <t>[사진 4]</t>
+        </is>
+      </c>
+      <c r="F22" s="29" t="inlineStr">
+        <is>
+          <t>SW(WMS) SKU 입출고 이력 – 입고 수량·로케이션·LOT 기록</t>
         </is>
       </c>
       <c r="G22" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H22" s="29" t="n"/>
@@ -5064,32 +5067,32 @@
       </c>
       <c r="B23" s="29" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>적치장소 이동</t>
+          <t>작업정보의 정보제공</t>
         </is>
       </c>
       <c r="D23" s="29" t="inlineStr">
         <is>
-          <t>p.13</t>
+          <t>p.12</t>
         </is>
       </c>
       <c r="E23" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F23" s="30" t="inlineStr">
-        <is>
-          <t>셀렉티브 랙 전경 사진</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F23" s="29" t="inlineStr">
+        <is>
+          <t>PDA 추천 로케이션 화면 캡처</t>
         </is>
       </c>
       <c r="G23" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H23" s="29" t="n"/>
@@ -5101,32 +5104,32 @@
       </c>
       <c r="B24" s="29" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>작업경로 관리</t>
+          <t>작업정보의 정보제공</t>
         </is>
       </c>
       <c r="D24" s="29" t="inlineStr">
         <is>
-          <t>p.14</t>
+          <t>p.12</t>
         </is>
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>레이아웃관리 화면 캡처</t>
+          <t>적치 작업 사진</t>
         </is>
       </c>
       <c r="G24" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H24" s="29" t="n"/>
@@ -5138,32 +5141,32 @@
       </c>
       <c r="B25" s="29" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>1.2.2</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>작업경로 관리</t>
+          <t>적치장소 이동</t>
         </is>
       </c>
       <c r="D25" s="29" t="inlineStr">
         <is>
-          <t>p.14</t>
+          <t>p.13</t>
         </is>
       </c>
       <c r="E25" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F25" s="30" t="inlineStr">
         <is>
-          <t>보관 영역 로케이션 배치도</t>
+          <t>지게차 적치 작업 사진</t>
         </is>
       </c>
       <c r="G25" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H25" s="29" t="n"/>
@@ -5175,27 +5178,27 @@
       </c>
       <c r="B26" s="29" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>1.2.2</t>
         </is>
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>적치장소 식별 및 작업</t>
+          <t>적치장소 이동</t>
         </is>
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
-          <t>p.15</t>
+          <t>p.13</t>
         </is>
       </c>
       <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>로케이션 라벨 부착 사진</t>
+          <t>셀렉티브 랙 전경 사진</t>
         </is>
       </c>
       <c r="G26" s="30" t="inlineStr">
@@ -5212,27 +5215,27 @@
       </c>
       <c r="B27" s="29" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>1.2.3</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>적치장소 식별 및 작업</t>
+          <t>작업경로 관리</t>
         </is>
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
-          <t>p.15</t>
+          <t>p.14</t>
         </is>
       </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F27" s="30" t="inlineStr">
         <is>
-          <t>셀 상세 화면 캡처</t>
+          <t>레이아웃관리 화면 캡처</t>
         </is>
       </c>
       <c r="G27" s="30" t="inlineStr">
@@ -5249,32 +5252,32 @@
       </c>
       <c r="B28" s="29" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>1.2.3</t>
         </is>
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>재고조사의 수행 및 방법</t>
+          <t>작업경로 관리</t>
         </is>
       </c>
       <c r="D28" s="29" t="inlineStr">
         <is>
-          <t>p.16</t>
+          <t>p.14</t>
         </is>
       </c>
       <c r="E28" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>재고실사 생성·수행 화면 캡처</t>
+          <t>보관 영역 로케이션 배치도</t>
         </is>
       </c>
       <c r="G28" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H28" s="29" t="n"/>
@@ -5286,32 +5289,32 @@
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>재고조사의 수행 및 방법</t>
+          <t>적치장소 식별 및 작업</t>
         </is>
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>p.16</t>
+          <t>p.15</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F29" s="30" t="inlineStr">
         <is>
-          <t>실사 결과 및 재고 조정 이력</t>
+          <t>로케이션 라벨 부착 사진</t>
         </is>
       </c>
       <c r="G29" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H29" s="29" t="n"/>
@@ -5323,27 +5326,27 @@
       </c>
       <c r="B30" s="29" t="inlineStr">
         <is>
-          <t>1.3.2</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>재고보충정보의 생성 및 지시</t>
+          <t>적치장소 식별 및 작업</t>
         </is>
       </c>
       <c r="D30" s="29" t="inlineStr">
         <is>
-          <t>p.17</t>
+          <t>p.15</t>
         </is>
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>재고 재배치(보충) 화면 캡처</t>
+          <t>셀 상세 화면 캡처</t>
         </is>
       </c>
       <c r="G30" s="30" t="inlineStr">
@@ -5360,17 +5363,17 @@
       </c>
       <c r="B31" s="29" t="inlineStr">
         <is>
-          <t>1.3.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>재고 보관위치의 조정</t>
+          <t>재고조사의 수행 및 방법</t>
         </is>
       </c>
       <c r="D31" s="29" t="inlineStr">
         <is>
-          <t>p.18</t>
+          <t>p.16</t>
         </is>
       </c>
       <c r="E31" s="29" t="inlineStr">
@@ -5380,7 +5383,7 @@
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>재배치 상세 화면 캡처</t>
+          <t>재고실사 생성·수행 화면 캡처</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -5397,32 +5400,32 @@
       </c>
       <c r="B32" s="29" t="inlineStr">
         <is>
-          <t>1.3.4</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>보관장소의 모니터링 및 관리</t>
+          <t>재고조사의 수행 및 방법</t>
         </is>
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
-          <t>p.19</t>
+          <t>p.16</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>전체 대시보드·대시보드 모니터 화면 캡처</t>
+          <t>실사 결과 및 재고 조정 이력</t>
         </is>
       </c>
       <c r="G32" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H32" s="29" t="n"/>
@@ -5434,32 +5437,32 @@
       </c>
       <c r="B33" s="29" t="inlineStr">
         <is>
-          <t>1.3.4</t>
+          <t>1.3.2</t>
         </is>
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>보관장소의 모니터링 및 관리</t>
+          <t>재고보충정보의 생성 및 지시</t>
         </is>
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
-          <t>p.19</t>
+          <t>p.17</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F33" s="30" t="inlineStr">
         <is>
-          <t>현장 상황판 사진</t>
+          <t>재고 재배치(보충) 화면 캡처</t>
         </is>
       </c>
       <c r="G33" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H33" s="29" t="n"/>
@@ -5471,27 +5474,27 @@
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>1.3.4</t>
+          <t>1.3.3</t>
         </is>
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>보관장소의 모니터링 및 관리</t>
+          <t>재고 보관위치의 조정</t>
         </is>
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>p.19</t>
+          <t>p.18</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>마감리포트 캡처</t>
+          <t>재배치 상세 화면 캡처</t>
         </is>
       </c>
       <c r="G34" s="30" t="inlineStr">
@@ -5508,17 +5511,17 @@
       </c>
       <c r="B35" s="29" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.4</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>재고 이력(선입선출 등) 및 품질관리</t>
+          <t>보관장소의 모니터링 및 관리</t>
         </is>
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>p.19</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
@@ -5528,7 +5531,7 @@
       </c>
       <c r="F35" s="30" t="inlineStr">
         <is>
-          <t>유통기한·로트 그룹핑 화면 및 자동 할당 결과 캡처</t>
+          <t>전체 대시보드·대시보드 모니터 화면 캡처</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
@@ -5545,32 +5548,32 @@
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>1.3.4</t>
         </is>
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>작업정보의 생성 및 지시</t>
+          <t>보관장소의 모니터링 및 관리</t>
         </is>
       </c>
       <c r="D36" s="29" t="inlineStr">
         <is>
-          <t>p.21</t>
+          <t>p.19</t>
         </is>
       </c>
       <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>픽킹 리스트 생성·관리 화면 캡처</t>
+          <t>현장 상황판 사진</t>
         </is>
       </c>
       <c r="G36" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H36" s="29" t="n"/>
@@ -5582,27 +5585,27 @@
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>1.3.4</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>작업정보의 생성 및 지시</t>
+          <t>보관장소의 모니터링 및 관리</t>
         </is>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>p.21</t>
+          <t>p.19</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F37" s="29" t="inlineStr">
-        <is>
-          <t>PDA 피킹 지시 화면</t>
+          <t>[사진 3]</t>
+        </is>
+      </c>
+      <c r="F37" s="30" t="inlineStr">
+        <is>
+          <t>마감리포트 캡처</t>
         </is>
       </c>
       <c r="G37" s="30" t="inlineStr">
@@ -5619,17 +5622,17 @@
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>1.3.5</t>
         </is>
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>작업정보의 확인 방법</t>
+          <t>재고 이력(선입선출 등) 및 품질관리</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>p.22</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
@@ -5637,9 +5640,9 @@
           <t>[사진 1]</t>
         </is>
       </c>
-      <c r="F38" s="29" t="inlineStr">
-        <is>
-          <t>PDA 피킹 화면</t>
+      <c r="F38" s="30" t="inlineStr">
+        <is>
+          <t>유통기한·로트 그룹핑 화면 및 자동 할당 결과 캡처</t>
         </is>
       </c>
       <c r="G38" s="30" t="inlineStr">
@@ -5656,32 +5659,32 @@
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>작업정보의 확인 방법</t>
+          <t>작업정보의 생성 및 지시</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>p.22</t>
+          <t>p.21</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F39" s="29" t="inlineStr">
-        <is>
-          <t>PTL 점등 사진</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F39" s="30" t="inlineStr">
+        <is>
+          <t>픽킹 리스트 생성·관리 화면 캡처</t>
         </is>
       </c>
       <c r="G39" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H39" s="29" t="n"/>
@@ -5693,27 +5696,27 @@
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>1.4.3</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>작업경로의 실시간 관리</t>
+          <t>작업정보의 생성 및 지시</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>p.23</t>
+          <t>p.21</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F40" s="30" t="inlineStr">
-        <is>
-          <t>픽킹 리스트 상세(로케이션 순) 캡처</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F40" s="29" t="inlineStr">
+        <is>
+          <t>PDA 피킹 지시 화면</t>
         </is>
       </c>
       <c r="G40" s="30" t="inlineStr">
@@ -5730,17 +5733,17 @@
       </c>
       <c r="B41" s="29" t="inlineStr">
         <is>
-          <t>1.4.4</t>
+          <t>1.4.2</t>
         </is>
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>피킹 장소의 확인 및 작업</t>
+          <t>작업정보의 확인 방법</t>
         </is>
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>p.24</t>
+          <t>p.22</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
@@ -5748,14 +5751,14 @@
           <t>[사진 1]</t>
         </is>
       </c>
-      <c r="F41" s="30" t="inlineStr">
-        <is>
-          <t>카트피킹 작업 사진</t>
+      <c r="F41" s="29" t="inlineStr">
+        <is>
+          <t>PDA 피킹 화면</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H41" s="29" t="n"/>
@@ -5767,17 +5770,17 @@
       </c>
       <c r="B42" s="29" t="inlineStr">
         <is>
-          <t>1.4.4</t>
+          <t>1.4.2</t>
         </is>
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>피킹 장소의 확인 및 작업</t>
+          <t>작업정보의 확인 방법</t>
         </is>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>p.24</t>
+          <t>p.22</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
@@ -5787,12 +5790,12 @@
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>PDA 스캔 검증 화면</t>
+          <t>PTL 점등 사진</t>
         </is>
       </c>
       <c r="G42" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H42" s="29" t="n"/>
@@ -5804,17 +5807,17 @@
       </c>
       <c r="B43" s="29" t="inlineStr">
         <is>
-          <t>1.4.5</t>
+          <t>1.4.3</t>
         </is>
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>분류정보의 생성 및 지시</t>
+          <t>작업경로의 실시간 관리</t>
         </is>
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>p.25</t>
+          <t>p.23</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
@@ -5824,7 +5827,7 @@
       </c>
       <c r="F43" s="30" t="inlineStr">
         <is>
-          <t>슈트 설정 화면 캡처</t>
+          <t>픽킹 리스트 상세(로케이션 순) 캡처</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
@@ -5841,27 +5844,27 @@
       </c>
       <c r="B44" s="29" t="inlineStr">
         <is>
-          <t>1.4.5</t>
+          <t>1.4.4</t>
         </is>
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>분류정보의 생성 및 지시</t>
+          <t>피킹 장소의 확인 및 작업</t>
         </is>
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>p.25</t>
+          <t>p.24</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>분류 영역 전경 사진</t>
+          <t>카트피킹 작업 사진</t>
         </is>
       </c>
       <c r="G44" s="30" t="inlineStr">
@@ -5878,32 +5881,32 @@
       </c>
       <c r="B45" s="29" t="inlineStr">
         <is>
-          <t>1.4.6</t>
+          <t>1.4.4</t>
         </is>
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>분류 작업</t>
+          <t>피킹 장소의 확인 및 작업</t>
         </is>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>p.26</t>
+          <t>p.24</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F45" s="30" t="inlineStr">
-        <is>
-          <t>휠소터·3D 소터·싱귤레이터 사진</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F45" s="29" t="inlineStr">
+        <is>
+          <t>PDA 스캔 검증 화면</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H45" s="29" t="n"/>
@@ -5915,27 +5918,27 @@
       </c>
       <c r="B46" s="29" t="inlineStr">
         <is>
-          <t>1.4.6</t>
+          <t>1.4.5</t>
         </is>
       </c>
       <c r="C46" s="30" t="inlineStr">
         <is>
-          <t>분류 작업</t>
+          <t>분류정보의 생성 및 지시</t>
         </is>
       </c>
       <c r="D46" s="29" t="inlineStr">
         <is>
-          <t>p.26</t>
+          <t>p.25</t>
         </is>
       </c>
       <c r="E46" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>소터 모니터링 화면 캡처</t>
+          <t>슈트 설정 화면 캡처</t>
         </is>
       </c>
       <c r="G46" s="30" t="inlineStr">
@@ -5952,32 +5955,32 @@
       </c>
       <c r="B47" s="29" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.4.5</t>
         </is>
       </c>
       <c r="C47" s="30" t="inlineStr">
         <is>
-          <t>포장장소로의 정보 제공 및 이동</t>
+          <t>분류정보의 생성 및 지시</t>
         </is>
       </c>
       <c r="D47" s="29" t="inlineStr">
         <is>
-          <t>p.27</t>
+          <t>p.25</t>
         </is>
       </c>
       <c r="E47" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F47" s="30" t="inlineStr">
         <is>
-          <t>패킹 리스트 화면 캡처</t>
+          <t>분류 영역 전경 사진</t>
         </is>
       </c>
       <c r="G47" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H47" s="29" t="n"/>
@@ -5989,27 +5992,27 @@
       </c>
       <c r="B48" s="29" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.4.6</t>
         </is>
       </c>
       <c r="C48" s="30" t="inlineStr">
         <is>
-          <t>포장장소로의 정보 제공 및 이동</t>
+          <t>분류 작업</t>
         </is>
       </c>
       <c r="D48" s="29" t="inlineStr">
         <is>
-          <t>p.27</t>
+          <t>p.26</t>
         </is>
       </c>
       <c r="E48" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>포장대 전경 사진</t>
+          <t>휠소터·3D 소터·싱귤레이터 사진</t>
         </is>
       </c>
       <c r="G48" s="30" t="inlineStr">
@@ -6026,32 +6029,32 @@
       </c>
       <c r="B49" s="29" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.4.6</t>
         </is>
       </c>
       <c r="C49" s="30" t="inlineStr">
         <is>
-          <t>포장재 및 포장물품 관리</t>
+          <t>분류 작업</t>
         </is>
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>p.28</t>
+          <t>p.26</t>
         </is>
       </c>
       <c r="E49" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F49" s="30" t="inlineStr">
         <is>
-          <t>포장재 보관 구역 사진</t>
+          <t>소터 모니터링 화면 캡처</t>
         </is>
       </c>
       <c r="G49" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H49" s="29" t="n"/>
@@ -6063,17 +6066,17 @@
       </c>
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="C50" s="30" t="inlineStr">
         <is>
-          <t>검품/검수 및 오류관리(인식 및 처리)</t>
+          <t>포장장소로의 정보 제공 및 이동</t>
         </is>
       </c>
       <c r="D50" s="29" t="inlineStr">
         <is>
-          <t>p.29</t>
+          <t>p.27</t>
         </is>
       </c>
       <c r="E50" s="29" t="inlineStr">
@@ -6083,7 +6086,7 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>검품 스캔 화면</t>
+          <t>패킹 리스트 화면 캡처</t>
         </is>
       </c>
       <c r="G50" s="30" t="inlineStr">
@@ -6100,17 +6103,17 @@
       </c>
       <c r="B51" s="29" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="C51" s="30" t="inlineStr">
         <is>
-          <t>검품/검수 및 오류관리(인식 및 처리)</t>
+          <t>포장장소로의 정보 제공 및 이동</t>
         </is>
       </c>
       <c r="D51" s="29" t="inlineStr">
         <is>
-          <t>p.29</t>
+          <t>p.27</t>
         </is>
       </c>
       <c r="E51" s="29" t="inlineStr">
@@ -6120,12 +6123,12 @@
       </c>
       <c r="F51" s="30" t="inlineStr">
         <is>
-          <t>녹화 영상 조회 화면 캡처</t>
+          <t>포장대 전경 사진</t>
         </is>
       </c>
       <c r="G51" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H51" s="29" t="n"/>
@@ -6137,27 +6140,27 @@
       </c>
       <c r="B52" s="29" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="C52" s="30" t="inlineStr">
         <is>
-          <t>검품/검수 및 오류관리(인식 및 처리)</t>
+          <t>포장재 및 포장물품 관리</t>
         </is>
       </c>
       <c r="D52" s="29" t="inlineStr">
         <is>
-          <t>p.29</t>
+          <t>p.28</t>
         </is>
       </c>
       <c r="E52" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
-        </is>
-      </c>
-      <c r="F52" s="29" t="inlineStr">
-        <is>
-          <t>DWS 계측 사진</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F52" s="30" t="inlineStr">
+        <is>
+          <t>포장재 보관 구역 사진</t>
         </is>
       </c>
       <c r="G52" s="30" t="inlineStr">
@@ -6189,17 +6192,17 @@
       </c>
       <c r="E53" s="29" t="inlineStr">
         <is>
-          <t>[사진 4]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F53" s="30" t="inlineStr">
         <is>
-          <t>이상/클레임 보고서 양식</t>
+          <t>검품 스캔 화면</t>
         </is>
       </c>
       <c r="G53" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H53" s="29" t="n"/>
@@ -6211,32 +6214,32 @@
       </c>
       <c r="B54" s="29" t="inlineStr">
         <is>
-          <t>1.5.4</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>포장 작업</t>
+          <t>검품/검수 및 오류관리(인식 및 처리)</t>
         </is>
       </c>
       <c r="D54" s="29" t="inlineStr">
         <is>
-          <t>p.30</t>
+          <t>p.29</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>포장대·봉함기 사진</t>
+          <t>녹화 영상 조회 화면 캡처</t>
         </is>
       </c>
       <c r="G54" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H54" s="29" t="n"/>
@@ -6248,27 +6251,27 @@
       </c>
       <c r="B55" s="29" t="inlineStr">
         <is>
-          <t>1.5.5</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>배송정보 표시(라벨) 및 부착</t>
+          <t>검품/검수 및 오류관리(인식 및 처리)</t>
         </is>
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
-          <t>p.31</t>
+          <t>p.29</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F55" s="30" t="inlineStr">
-        <is>
-          <t>오토라벨러 사진</t>
+          <t>[사진 3]</t>
+        </is>
+      </c>
+      <c r="F55" s="29" t="inlineStr">
+        <is>
+          <t>DWS 계측 사진</t>
         </is>
       </c>
       <c r="G55" s="30" t="inlineStr">
@@ -6285,32 +6288,32 @@
       </c>
       <c r="B56" s="29" t="inlineStr">
         <is>
-          <t>1.5.5</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="C56" s="30" t="inlineStr">
         <is>
-          <t>배송정보 표시(라벨) 및 부착</t>
+          <t>검품/검수 및 오류관리(인식 및 처리)</t>
         </is>
       </c>
       <c r="D56" s="29" t="inlineStr">
         <is>
-          <t>p.31</t>
+          <t>p.29</t>
         </is>
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 4]</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>송장 출력 화면</t>
+          <t>이상/클레임 보고서 양식</t>
         </is>
       </c>
       <c r="G56" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H56" s="29" t="n"/>
@@ -6322,17 +6325,17 @@
       </c>
       <c r="B57" s="29" t="inlineStr">
         <is>
-          <t>1.6.1</t>
+          <t>1.5.4</t>
         </is>
       </c>
       <c r="C57" s="30" t="inlineStr">
         <is>
-          <t>발주처별 분류</t>
+          <t>포장 작업</t>
         </is>
       </c>
       <c r="D57" s="29" t="inlineStr">
         <is>
-          <t>p.32</t>
+          <t>p.30</t>
         </is>
       </c>
       <c r="E57" s="29" t="inlineStr">
@@ -6342,7 +6345,7 @@
       </c>
       <c r="F57" s="30" t="inlineStr">
         <is>
-          <t>슈트별 분류 사진</t>
+          <t>포장대·봉함기 사진</t>
         </is>
       </c>
       <c r="G57" s="30" t="inlineStr">
@@ -6359,32 +6362,32 @@
       </c>
       <c r="B58" s="29" t="inlineStr">
         <is>
-          <t>1.6.1</t>
+          <t>1.5.5</t>
         </is>
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>발주처별 분류</t>
+          <t>배송정보 표시(라벨) 및 부착</t>
         </is>
       </c>
       <c r="D58" s="29" t="inlineStr">
         <is>
-          <t>p.32</t>
+          <t>p.31</t>
         </is>
       </c>
       <c r="E58" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>번들 검증 PDA 화면</t>
+          <t>오토라벨러 사진</t>
         </is>
       </c>
       <c r="G58" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H58" s="29" t="n"/>
@@ -6396,32 +6399,32 @@
       </c>
       <c r="B59" s="29" t="inlineStr">
         <is>
-          <t>1.6.2</t>
+          <t>1.5.5</t>
         </is>
       </c>
       <c r="C59" s="30" t="inlineStr">
         <is>
-          <t>차량입차정보의 인식</t>
+          <t>배송정보 표시(라벨) 및 부착</t>
         </is>
       </c>
       <c r="D59" s="29" t="inlineStr">
         <is>
-          <t>p.33</t>
+          <t>p.31</t>
         </is>
       </c>
       <c r="E59" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F59" s="30" t="inlineStr">
         <is>
-          <t>상차 도크 사진</t>
+          <t>송장 출력 화면</t>
         </is>
       </c>
       <c r="G59" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H59" s="29" t="n"/>
@@ -6433,32 +6436,32 @@
       </c>
       <c r="B60" s="29" t="inlineStr">
         <is>
-          <t>1.6.2</t>
+          <t>1.6.1</t>
         </is>
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>차량입차정보의 인식</t>
+          <t>발주처별 분류</t>
         </is>
       </c>
       <c r="D60" s="29" t="inlineStr">
         <is>
-          <t>p.33</t>
+          <t>p.32</t>
         </is>
       </c>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F60" s="29" t="inlineStr">
-        <is>
-          <t>TLPS 인계 일정 화면</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F60" s="30" t="inlineStr">
+        <is>
+          <t>슈트별 분류 사진</t>
         </is>
       </c>
       <c r="G60" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H60" s="29" t="n"/>
@@ -6470,32 +6473,32 @@
       </c>
       <c r="B61" s="29" t="inlineStr">
         <is>
-          <t>1.6.3</t>
+          <t>1.6.1</t>
         </is>
       </c>
       <c r="C61" s="30" t="inlineStr">
         <is>
-          <t>상차순서 관리 및 작업</t>
+          <t>발주처별 분류</t>
         </is>
       </c>
       <c r="D61" s="29" t="inlineStr">
         <is>
-          <t>p.34</t>
+          <t>p.32</t>
         </is>
       </c>
       <c r="E61" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F61" s="30" t="inlineStr">
         <is>
-          <t>상차 작업 사진</t>
+          <t>번들 검증 PDA 화면</t>
         </is>
       </c>
       <c r="G61" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H61" s="29" t="n"/>
@@ -6507,32 +6510,32 @@
       </c>
       <c r="B62" s="29" t="inlineStr">
         <is>
-          <t>1.6.3</t>
+          <t>1.6.2</t>
         </is>
       </c>
       <c r="C62" s="30" t="inlineStr">
         <is>
-          <t>상차순서 관리 및 작업</t>
+          <t>차량입차정보의 인식</t>
         </is>
       </c>
       <c r="D62" s="29" t="inlineStr">
         <is>
-          <t>p.34</t>
+          <t>p.33</t>
         </is>
       </c>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>인계 확인(스캔) 화면</t>
+          <t>상차 도크 사진</t>
         </is>
       </c>
       <c r="G62" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H62" s="29" t="n"/>
@@ -6544,27 +6547,27 @@
       </c>
       <c r="B63" s="29" t="inlineStr">
         <is>
-          <t>1.6.4</t>
+          <t>1.6.2</t>
         </is>
       </c>
       <c r="C63" s="30" t="inlineStr">
         <is>
-          <t>출고정보의 전달</t>
+          <t>차량입차정보의 인식</t>
         </is>
       </c>
       <c r="D63" s="29" t="inlineStr">
         <is>
-          <t>p.35</t>
+          <t>p.33</t>
         </is>
       </c>
       <c r="E63" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F63" s="30" t="inlineStr">
-        <is>
-          <t>출고 확정·송장 조회 화면</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F63" s="29" t="inlineStr">
+        <is>
+          <t>TLPS 인계 일정 화면</t>
         </is>
       </c>
       <c r="G63" s="30" t="inlineStr">
@@ -6581,32 +6584,32 @@
       </c>
       <c r="B64" s="29" t="inlineStr">
         <is>
-          <t>1.6.4</t>
+          <t>1.6.3</t>
         </is>
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>출고정보의 전달</t>
+          <t>상차순서 관리 및 작업</t>
         </is>
       </c>
       <c r="D64" s="29" t="inlineStr">
         <is>
-          <t>p.35</t>
+          <t>p.34</t>
         </is>
       </c>
       <c r="E64" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>출고 영상 매핑 화면</t>
+          <t>상차 작업 사진</t>
         </is>
       </c>
       <c r="G64" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H64" s="29" t="n"/>
@@ -6618,32 +6621,32 @@
       </c>
       <c r="B65" s="29" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>1.6.3</t>
         </is>
       </c>
       <c r="C65" s="30" t="inlineStr">
         <is>
-          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
+          <t>상차순서 관리 및 작업</t>
         </is>
       </c>
       <c r="D65" s="29" t="inlineStr">
         <is>
-          <t>p.36</t>
+          <t>p.34</t>
         </is>
       </c>
       <c r="E65" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F65" s="30" t="inlineStr">
         <is>
-          <t>도크·레벨러·차양 사진</t>
+          <t>인계 확인(스캔) 화면</t>
         </is>
       </c>
       <c r="G65" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H65" s="29" t="n"/>
@@ -6655,32 +6658,32 @@
       </c>
       <c r="B66" s="29" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>1.6.4</t>
         </is>
       </c>
       <c r="C66" s="30" t="inlineStr">
         <is>
-          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
+          <t>출고정보의 전달</t>
         </is>
       </c>
       <c r="D66" s="29" t="inlineStr">
         <is>
-          <t>p.36</t>
+          <t>p.35</t>
         </is>
       </c>
       <c r="E66" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>바닥 평탄도·하중 근거(건축 설계도서 또는 임대인 제원표)</t>
+          <t>출고 확정·송장 조회 화면</t>
         </is>
       </c>
       <c r="G66" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H66" s="29" t="n"/>
@@ -6692,32 +6695,32 @@
       </c>
       <c r="B67" s="29" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>1.6.4</t>
         </is>
       </c>
       <c r="C67" s="30" t="inlineStr">
         <is>
-          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
+          <t>출고정보의 전달</t>
         </is>
       </c>
       <c r="D67" s="29" t="inlineStr">
         <is>
-          <t>p.36</t>
+          <t>p.35</t>
         </is>
       </c>
       <c r="E67" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F67" s="30" t="inlineStr">
         <is>
-          <t>바닥 라인 표시 사진</t>
+          <t>출고 영상 매핑 화면</t>
         </is>
       </c>
       <c r="G67" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H67" s="29" t="n"/>
@@ -6729,17 +6732,17 @@
       </c>
       <c r="B68" s="29" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="C68" s="30" t="inlineStr">
         <is>
-          <t>내부구조(층고 및 기둥의 배치구조)</t>
+          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
         </is>
       </c>
       <c r="D68" s="29" t="inlineStr">
         <is>
-          <t>p.38</t>
+          <t>p.36</t>
         </is>
       </c>
       <c r="E68" s="29" t="inlineStr">
@@ -6749,7 +6752,7 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>평면도(기둥 격자 치수)</t>
+          <t>도크·레벨러·차양 사진</t>
         </is>
       </c>
       <c r="G68" s="30" t="inlineStr">
@@ -6766,17 +6769,17 @@
       </c>
       <c r="B69" s="29" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>내부구조(층고 및 기둥의 배치구조)</t>
+          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
         </is>
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>p.38</t>
+          <t>p.36</t>
         </is>
       </c>
       <c r="E69" s="29" t="inlineStr">
@@ -6786,12 +6789,12 @@
       </c>
       <c r="F69" s="30" t="inlineStr">
         <is>
-          <t>보관 영역 전경(층고) 사진</t>
+          <t>바닥 평탄도·하중 근거(건축 설계도서 또는 임대인 제원표)</t>
         </is>
       </c>
       <c r="G69" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H69" s="29" t="n"/>
@@ -6803,32 +6806,32 @@
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>2.1.3</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>배치 및 동선 관리</t>
+          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>p.39</t>
+          <t>p.36</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>운영 Lay-out 도면</t>
+          <t>바닥 라인 표시 사진</t>
         </is>
       </c>
       <c r="G70" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H70" s="29" t="n"/>
@@ -6840,27 +6843,27 @@
       </c>
       <c r="B71" s="29" t="inlineStr">
         <is>
-          <t>2.1.3</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="C71" s="30" t="inlineStr">
         <is>
-          <t>배치 및 동선 관리</t>
+          <t>내부구조(층고 및 기둥의 배치구조)</t>
         </is>
       </c>
       <c r="D71" s="29" t="inlineStr">
         <is>
-          <t>p.39</t>
+          <t>p.38</t>
         </is>
       </c>
       <c r="E71" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F71" s="30" t="inlineStr">
         <is>
-          <t>램프웨이·동선 표시 사진</t>
+          <t>평면도(기둥 격자 치수)</t>
         </is>
       </c>
       <c r="G71" s="30" t="inlineStr">
@@ -6877,32 +6880,32 @@
       </c>
       <c r="B72" s="29" t="inlineStr">
         <is>
-          <t>2.1.4</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>작업환경 관리(공조, 온도, 습도 등)</t>
+          <t>내부구조(층고 및 기둥의 배치구조)</t>
         </is>
       </c>
       <c r="D72" s="29" t="inlineStr">
         <is>
-          <t>p.40</t>
+          <t>p.38</t>
         </is>
       </c>
       <c r="E72" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>조도·온습도 측정 기록</t>
+          <t>보관 영역 전경(층고) 사진</t>
         </is>
       </c>
       <c r="G72" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H72" s="29" t="n"/>
@@ -6914,27 +6917,27 @@
       </c>
       <c r="B73" s="29" t="inlineStr">
         <is>
-          <t>2.1.4</t>
+          <t>2.1.3</t>
         </is>
       </c>
       <c r="C73" s="30" t="inlineStr">
         <is>
-          <t>작업환경 관리(공조, 온도, 습도 등)</t>
+          <t>배치 및 동선 관리</t>
         </is>
       </c>
       <c r="D73" s="29" t="inlineStr">
         <is>
-          <t>p.40</t>
+          <t>p.39</t>
         </is>
       </c>
       <c r="E73" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F73" s="30" t="inlineStr">
         <is>
-          <t>방충·방서 관리 기록</t>
+          <t>운영 Lay-out 도면</t>
         </is>
       </c>
       <c r="G73" s="30" t="inlineStr">
@@ -6951,27 +6954,27 @@
       </c>
       <c r="B74" s="29" t="inlineStr">
         <is>
-          <t>2.1.4</t>
+          <t>2.1.3</t>
         </is>
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>작업환경 관리(공조, 온도, 습도 등)</t>
+          <t>배치 및 동선 관리</t>
         </is>
       </c>
       <c r="D74" s="29" t="inlineStr">
         <is>
-          <t>p.40</t>
+          <t>p.39</t>
         </is>
       </c>
       <c r="E74" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>휴게실 사진</t>
+          <t>램프웨이·동선 표시 사진</t>
         </is>
       </c>
       <c r="G74" s="30" t="inlineStr">
@@ -6988,17 +6991,17 @@
       </c>
       <c r="B75" s="29" t="inlineStr">
         <is>
-          <t>2.1.5</t>
+          <t>2.1.4</t>
         </is>
       </c>
       <c r="C75" s="30" t="inlineStr">
         <is>
-          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
+          <t>작업환경 관리(공조, 온도, 습도 등)</t>
         </is>
       </c>
       <c r="D75" s="29" t="inlineStr">
         <is>
-          <t>p.41</t>
+          <t>p.40</t>
         </is>
       </c>
       <c r="E75" s="29" t="inlineStr">
@@ -7008,7 +7011,7 @@
       </c>
       <c r="F75" s="30" t="inlineStr">
         <is>
-          <t>소방시설 자체점검 결과보고서</t>
+          <t>조도·온습도 측정 기록</t>
         </is>
       </c>
       <c r="G75" s="30" t="inlineStr">
@@ -7025,17 +7028,17 @@
       </c>
       <c r="B76" s="29" t="inlineStr">
         <is>
-          <t>2.1.5</t>
+          <t>2.1.4</t>
         </is>
       </c>
       <c r="C76" s="30" t="inlineStr">
         <is>
-          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
+          <t>작업환경 관리(공조, 온도, 습도 등)</t>
         </is>
       </c>
       <c r="D76" s="29" t="inlineStr">
         <is>
-          <t>p.41</t>
+          <t>p.40</t>
         </is>
       </c>
       <c r="E76" s="29" t="inlineStr">
@@ -7045,12 +7048,12 @@
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>비상구·소화설비 사진</t>
+          <t>방충·방서 관리 기록</t>
         </is>
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H76" s="29" t="n"/>
@@ -7062,17 +7065,17 @@
       </c>
       <c r="B77" s="29" t="inlineStr">
         <is>
-          <t>2.1.5</t>
+          <t>2.1.4</t>
         </is>
       </c>
       <c r="C77" s="30" t="inlineStr">
         <is>
-          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
+          <t>작업환경 관리(공조, 온도, 습도 등)</t>
         </is>
       </c>
       <c r="D77" s="29" t="inlineStr">
         <is>
-          <t>p.41</t>
+          <t>p.40</t>
         </is>
       </c>
       <c r="E77" s="29" t="inlineStr">
@@ -7082,12 +7085,12 @@
       </c>
       <c r="F77" s="30" t="inlineStr">
         <is>
-          <t>안전교육 이수 기록</t>
+          <t>휴게실 사진</t>
         </is>
       </c>
       <c r="G77" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H77" s="29" t="n"/>
@@ -7114,17 +7117,17 @@
       </c>
       <c r="E78" s="29" t="inlineStr">
         <is>
-          <t>[사진 4]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>작업자 추적(QR) 화면</t>
+          <t>소방시설 자체점검 결과보고서</t>
         </is>
       </c>
       <c r="G78" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H78" s="29" t="n"/>
@@ -7136,32 +7139,32 @@
       </c>
       <c r="B79" s="29" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>2.1.5</t>
         </is>
       </c>
       <c r="C79" s="30" t="inlineStr">
         <is>
-          <t>비용 절감</t>
+          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
         </is>
       </c>
       <c r="D79" s="29" t="inlineStr">
         <is>
-          <t>p.42</t>
+          <t>p.41</t>
         </is>
       </c>
       <c r="E79" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F79" s="30" t="inlineStr">
         <is>
-          <t>최근 3년 물류비·절감률 실적표</t>
+          <t>비상구·소화설비 사진</t>
         </is>
       </c>
       <c r="G79" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H79" s="29" t="n"/>
@@ -7173,27 +7176,27 @@
       </c>
       <c r="B80" s="29" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>2.1.5</t>
         </is>
       </c>
       <c r="C80" s="30" t="inlineStr">
         <is>
-          <t>비용 절감</t>
+          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
         </is>
       </c>
       <c r="D80" s="29" t="inlineStr">
         <is>
-          <t>p.42</t>
+          <t>p.41</t>
         </is>
       </c>
       <c r="E80" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>월간 성과보고 자료</t>
+          <t>안전교육 이수 기록</t>
         </is>
       </c>
       <c r="G80" s="30" t="inlineStr">
@@ -7210,27 +7213,27 @@
       </c>
       <c r="B81" s="29" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.1.5</t>
         </is>
       </c>
       <c r="C81" s="30" t="inlineStr">
         <is>
-          <t>생산성 향상</t>
+          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
         </is>
       </c>
       <c r="D81" s="29" t="inlineStr">
         <is>
-          <t>p.43</t>
+          <t>p.41</t>
         </is>
       </c>
       <c r="E81" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 4]</t>
         </is>
       </c>
       <c r="F81" s="30" t="inlineStr">
         <is>
-          <t>작업자 추적 화면·리포트 캡처</t>
+          <t>작업자 추적(QR) 화면</t>
         </is>
       </c>
       <c r="G81" s="30" t="inlineStr">
@@ -7247,27 +7250,27 @@
       </c>
       <c r="B82" s="29" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>생산성 향상</t>
+          <t>비용 절감</t>
         </is>
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>p.43</t>
+          <t>p.42</t>
         </is>
       </c>
       <c r="E82" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>최근 3년 UPH 실적표</t>
+          <t>최근 3년 물류비·절감률 실적표</t>
         </is>
       </c>
       <c r="G82" s="30" t="inlineStr">
@@ -7284,27 +7287,27 @@
       </c>
       <c r="B83" s="29" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="C83" s="30" t="inlineStr">
         <is>
-          <t>품질 및 안전관리</t>
+          <t>비용 절감</t>
         </is>
       </c>
       <c r="D83" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.42</t>
         </is>
       </c>
       <c r="E83" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F83" s="30" t="inlineStr">
         <is>
-          <t>최근 3년 오출고율·정확도 실적</t>
+          <t>월간 성과보고 자료</t>
         </is>
       </c>
       <c r="G83" s="30" t="inlineStr">
@@ -7321,32 +7324,32 @@
       </c>
       <c r="B84" s="29" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>품질 및 안전관리</t>
+          <t>생산성 향상</t>
         </is>
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.43</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>클레임 처리 이력</t>
+          <t>작업자 추적 화면·리포트 캡처</t>
         </is>
       </c>
       <c r="G84" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H84" s="29" t="n"/>
@@ -7358,27 +7361,27 @@
       </c>
       <c r="B85" s="29" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="C85" s="30" t="inlineStr">
         <is>
-          <t>품질 및 안전관리</t>
+          <t>생산성 향상</t>
         </is>
       </c>
       <c r="D85" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.43</t>
         </is>
       </c>
       <c r="E85" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F85" s="30" t="inlineStr">
         <is>
-          <t>안전교육 기록</t>
+          <t>최근 3년 UPH 실적표</t>
         </is>
       </c>
       <c r="G85" s="30" t="inlineStr">
@@ -7395,17 +7398,17 @@
       </c>
       <c r="B86" s="29" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
+          <t>품질 및 안전관리</t>
         </is>
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>p.45</t>
+          <t>p.44</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
@@ -7415,7 +7418,7 @@
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>친환경 포장재 적용률 실적</t>
+          <t>최근 3년 오출고율·정확도 실적</t>
         </is>
       </c>
       <c r="G86" s="30" t="inlineStr">
@@ -7432,17 +7435,17 @@
       </c>
       <c r="B87" s="29" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
         <is>
-          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
+          <t>품질 및 안전관리</t>
         </is>
       </c>
       <c r="D87" s="29" t="inlineStr">
         <is>
-          <t>p.45</t>
+          <t>p.44</t>
         </is>
       </c>
       <c r="E87" s="29" t="inlineStr">
@@ -7452,7 +7455,7 @@
       </c>
       <c r="F87" s="30" t="inlineStr">
         <is>
-          <t>폐기물 재활용 실적</t>
+          <t>클레임 처리 이력</t>
         </is>
       </c>
       <c r="G87" s="30" t="inlineStr">
@@ -7469,17 +7472,17 @@
       </c>
       <c r="B88" s="29" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C88" s="30" t="inlineStr">
         <is>
-          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
+          <t>품질 및 안전관리</t>
         </is>
       </c>
       <c r="D88" s="29" t="inlineStr">
         <is>
-          <t>p.45</t>
+          <t>p.44</t>
         </is>
       </c>
       <c r="E88" s="29" t="inlineStr">
@@ -7487,14 +7490,14 @@
           <t>[사진 3]</t>
         </is>
       </c>
-      <c r="F88" s="29" t="inlineStr">
-        <is>
-          <t>LED 조명 등 설비 사진</t>
+      <c r="F88" s="30" t="inlineStr">
+        <is>
+          <t>안전교육 기록</t>
         </is>
       </c>
       <c r="G88" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H88" s="29" t="n"/>
@@ -7506,17 +7509,17 @@
       </c>
       <c r="B89" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>수발주시스템/상품분류시스템</t>
+          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
         </is>
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>p.46</t>
+          <t>p.45</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
@@ -7524,14 +7527,14 @@
           <t>[사진 1]</t>
         </is>
       </c>
-      <c r="F89" s="29" t="inlineStr">
-        <is>
-          <t>Smartship 주문 수집·검증 화면</t>
+      <c r="F89" s="30" t="inlineStr">
+        <is>
+          <t>친환경 포장재 적용률 실적</t>
         </is>
       </c>
       <c r="G89" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H89" s="29" t="n"/>
@@ -7543,17 +7546,17 @@
       </c>
       <c r="B90" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C90" s="30" t="inlineStr">
         <is>
-          <t>수발주시스템/상품분류시스템</t>
+          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
         </is>
       </c>
       <c r="D90" s="29" t="inlineStr">
         <is>
-          <t>p.46</t>
+          <t>p.45</t>
         </is>
       </c>
       <c r="E90" s="29" t="inlineStr">
@@ -7563,12 +7566,12 @@
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>채널 연동 현황 화면</t>
+          <t>폐기물 재활용 실적</t>
         </is>
       </c>
       <c r="G90" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H90" s="29" t="n"/>
@@ -7580,32 +7583,32 @@
       </c>
       <c r="B91" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-2</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C91" s="30" t="inlineStr">
         <is>
-          <t>입출고 및 배차배송시스템</t>
+          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
         </is>
       </c>
       <c r="D91" s="29" t="inlineStr">
         <is>
-          <t>p.47</t>
+          <t>p.45</t>
         </is>
       </c>
       <c r="E91" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F91" s="30" t="inlineStr">
-        <is>
-          <t>입고·출고 화면</t>
+          <t>[사진 3]</t>
+        </is>
+      </c>
+      <c r="F91" s="29" t="inlineStr">
+        <is>
+          <t>LED 조명 등 설비 사진</t>
         </is>
       </c>
       <c r="G91" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H91" s="29" t="n"/>
@@ -7617,27 +7620,27 @@
       </c>
       <c r="B92" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-2</t>
+          <t>2.3.1-1</t>
         </is>
       </c>
       <c r="C92" s="30" t="inlineStr">
         <is>
-          <t>입출고 및 배차배송시스템</t>
+          <t>수발주시스템/상품분류시스템</t>
         </is>
       </c>
       <c r="D92" s="29" t="inlineStr">
         <is>
-          <t>p.47</t>
+          <t>p.46</t>
         </is>
       </c>
       <c r="E92" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F92" s="29" t="inlineStr">
         <is>
-          <t>TLPS 운송·인계 화면</t>
+          <t>Smartship 주문 수집·검증 화면</t>
         </is>
       </c>
       <c r="G92" s="30" t="inlineStr">
@@ -7654,27 +7657,27 @@
       </c>
       <c r="B93" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-3</t>
+          <t>2.3.1-1</t>
         </is>
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>재고관리시스템</t>
+          <t>수발주시스템/상품분류시스템</t>
         </is>
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>p.48</t>
+          <t>p.46</t>
         </is>
       </c>
       <c r="E93" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F93" s="30" t="inlineStr">
         <is>
-          <t>대시보드·셀 상세·실사·마감리포트 화면</t>
+          <t>채널 연동 현황 화면</t>
         </is>
       </c>
       <c r="G93" s="30" t="inlineStr">
@@ -7691,17 +7694,17 @@
       </c>
       <c r="B94" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-4</t>
+          <t>2.3.1-2</t>
         </is>
       </c>
       <c r="C94" s="30" t="inlineStr">
         <is>
-          <t>자원관리시스템</t>
+          <t>입출고 및 배차배송시스템</t>
         </is>
       </c>
       <c r="D94" s="29" t="inlineStr">
         <is>
-          <t>p.49</t>
+          <t>p.47</t>
         </is>
       </c>
       <c r="E94" s="29" t="inlineStr">
@@ -7711,7 +7714,7 @@
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>레이아웃관리·디바이스·작업자 추적 화면</t>
+          <t>입고·출고 화면</t>
         </is>
       </c>
       <c r="G94" s="30" t="inlineStr">
@@ -7728,32 +7731,32 @@
       </c>
       <c r="B95" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-5</t>
+          <t>2.3.1-2</t>
         </is>
       </c>
       <c r="C95" s="30" t="inlineStr">
         <is>
-          <t>물류지원시스템</t>
+          <t>입출고 및 배차배송시스템</t>
         </is>
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>p.50</t>
+          <t>p.47</t>
         </is>
       </c>
       <c r="E95" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F95" s="30" t="inlineStr">
-        <is>
-          <t>풀필먼트 주문관리 대시보드</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F95" s="29" t="inlineStr">
+        <is>
+          <t>TLPS 운송·인계 화면</t>
         </is>
       </c>
       <c r="G95" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H95" s="29" t="n"/>
@@ -7765,27 +7768,27 @@
       </c>
       <c r="B96" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-5</t>
+          <t>2.3.1-3</t>
         </is>
       </c>
       <c r="C96" s="30" t="inlineStr">
         <is>
-          <t>물류지원시스템</t>
+          <t>재고관리시스템</t>
         </is>
       </c>
       <c r="D96" s="29" t="inlineStr">
         <is>
-          <t>p.50</t>
+          <t>p.48</t>
         </is>
       </c>
       <c r="E96" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>반품 출고 관리 화면</t>
+          <t>대시보드·셀 상세·실사·마감리포트 화면</t>
         </is>
       </c>
       <c r="G96" s="30" t="inlineStr">
@@ -7802,27 +7805,27 @@
       </c>
       <c r="B97" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-5</t>
+          <t>2.3.1-4</t>
         </is>
       </c>
       <c r="C97" s="30" t="inlineStr">
         <is>
-          <t>물류지원시스템</t>
+          <t>자원관리시스템</t>
         </is>
       </c>
       <c r="D97" s="29" t="inlineStr">
         <is>
-          <t>p.50</t>
+          <t>p.49</t>
         </is>
       </c>
       <c r="E97" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F97" s="30" t="inlineStr">
         <is>
-          <t>오류화물 관리 화면</t>
+          <t>레이아웃관리·디바이스·작업자 추적 화면</t>
         </is>
       </c>
       <c r="G97" s="30" t="inlineStr">
@@ -7839,17 +7842,17 @@
       </c>
       <c r="B98" s="29" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>2.3.1-5</t>
         </is>
       </c>
       <c r="C98" s="30" t="inlineStr">
         <is>
-          <t>창고제어시스템(WCS, MCS)</t>
+          <t>물류지원시스템</t>
         </is>
       </c>
       <c r="D98" s="29" t="inlineStr">
         <is>
-          <t>p.51</t>
+          <t>p.50</t>
         </is>
       </c>
       <c r="E98" s="29" t="inlineStr">
@@ -7859,12 +7862,12 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>소터 모니터링·슈트 설정 화면</t>
+          <t>풀필먼트 주문관리 대시보드</t>
         </is>
       </c>
       <c r="G98" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H98" s="29" t="n"/>
@@ -7876,17 +7879,17 @@
       </c>
       <c r="B99" s="29" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>2.3.1-5</t>
         </is>
       </c>
       <c r="C99" s="30" t="inlineStr">
         <is>
-          <t>창고제어시스템(WCS, MCS)</t>
+          <t>물류지원시스템</t>
         </is>
       </c>
       <c r="D99" s="29" t="inlineStr">
         <is>
-          <t>p.51</t>
+          <t>p.50</t>
         </is>
       </c>
       <c r="E99" s="29" t="inlineStr">
@@ -7896,19 +7899,130 @@
       </c>
       <c r="F99" s="30" t="inlineStr">
         <is>
-          <t>설비 구성도</t>
+          <t>반품 출고 관리 화면</t>
         </is>
       </c>
       <c r="G99" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H99" s="29" t="n"/>
       <c r="I99" s="29" t="n"/>
     </row>
+    <row r="100">
+      <c r="A100" s="29" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="29" t="inlineStr">
+        <is>
+          <t>2.3.1-5</t>
+        </is>
+      </c>
+      <c r="C100" s="30" t="inlineStr">
+        <is>
+          <t>물류지원시스템</t>
+        </is>
+      </c>
+      <c r="D100" s="29" t="inlineStr">
+        <is>
+          <t>p.50</t>
+        </is>
+      </c>
+      <c r="E100" s="29" t="inlineStr">
+        <is>
+          <t>[사진 3]</t>
+        </is>
+      </c>
+      <c r="F100" s="30" t="inlineStr">
+        <is>
+          <t>오류화물 관리 화면</t>
+        </is>
+      </c>
+      <c r="G100" s="30" t="inlineStr">
+        <is>
+          <t>캡처</t>
+        </is>
+      </c>
+      <c r="H100" s="29" t="n"/>
+      <c r="I100" s="29" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="29" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="29" t="inlineStr">
+        <is>
+          <t>2.3.2</t>
+        </is>
+      </c>
+      <c r="C101" s="30" t="inlineStr">
+        <is>
+          <t>창고제어시스템(WCS, MCS)</t>
+        </is>
+      </c>
+      <c r="D101" s="29" t="inlineStr">
+        <is>
+          <t>p.51</t>
+        </is>
+      </c>
+      <c r="E101" s="29" t="inlineStr">
+        <is>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F101" s="30" t="inlineStr">
+        <is>
+          <t>소터 모니터링·슈트 설정 화면</t>
+        </is>
+      </c>
+      <c r="G101" s="30" t="inlineStr">
+        <is>
+          <t>캡처</t>
+        </is>
+      </c>
+      <c r="H101" s="29" t="n"/>
+      <c r="I101" s="29" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="29" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="29" t="inlineStr">
+        <is>
+          <t>2.3.2</t>
+        </is>
+      </c>
+      <c r="C102" s="30" t="inlineStr">
+        <is>
+          <t>창고제어시스템(WCS, MCS)</t>
+        </is>
+      </c>
+      <c r="D102" s="29" t="inlineStr">
+        <is>
+          <t>p.51</t>
+        </is>
+      </c>
+      <c r="E102" s="29" t="inlineStr">
+        <is>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F102" s="30" t="inlineStr">
+        <is>
+          <t>설비 구성도</t>
+        </is>
+      </c>
+      <c r="G102" s="30" t="inlineStr">
+        <is>
+          <t>자료</t>
+        </is>
+      </c>
+      <c r="H102" s="29" t="n"/>
+      <c r="I102" s="29" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I99"/>
+  <autoFilter ref="A3:I102"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7937,6 +8051,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="29.25" customHeight="1" s="24">
       <c r="A3" s="28" t="inlineStr">
         <is>

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -1575,7 +1575,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="24">
       <c r="B27" s="36" t="inlineStr">
         <is>
@@ -1680,7 +1679,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="24">
       <c r="A3" s="27" t="inlineStr">
         <is>
@@ -2287,7 +2285,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="24">
       <c r="A3" s="28" t="inlineStr">
         <is>
@@ -4393,7 +4390,11 @@
         </is>
       </c>
       <c r="H4" s="29" t="n"/>
-      <c r="I4" s="29" t="n"/>
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="24">
       <c r="A5" s="29" t="n">
@@ -4430,7 +4431,11 @@
         </is>
       </c>
       <c r="H5" s="29" t="n"/>
-      <c r="I5" s="29" t="n"/>
+      <c r="I5" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="24">
       <c r="A6" s="29" t="n">
@@ -4467,7 +4472,11 @@
         </is>
       </c>
       <c r="H6" s="29" t="n"/>
-      <c r="I6" s="29" t="n"/>
+      <c r="I6" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="24">
       <c r="A7" s="29" t="n">
@@ -4578,7 +4587,11 @@
         </is>
       </c>
       <c r="H9" s="29" t="n"/>
-      <c r="I9" s="29" t="n"/>
+      <c r="I9" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="24">
       <c r="A10" s="29" t="n">
@@ -4615,7 +4628,11 @@
         </is>
       </c>
       <c r="H10" s="29" t="n"/>
-      <c r="I10" s="29" t="n"/>
+      <c r="I10" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="24">
       <c r="A11" s="29" t="n">
@@ -4652,7 +4669,11 @@
         </is>
       </c>
       <c r="H11" s="29" t="n"/>
-      <c r="I11" s="29" t="n"/>
+      <c r="I11" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="24">
       <c r="A12" s="29" t="n">
@@ -4726,7 +4747,11 @@
         </is>
       </c>
       <c r="H13" s="29" t="n"/>
-      <c r="I13" s="29" t="n"/>
+      <c r="I13" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="24">
       <c r="A14" s="29" t="n">
@@ -4763,7 +4788,11 @@
         </is>
       </c>
       <c r="H14" s="29" t="n"/>
-      <c r="I14" s="29" t="n"/>
+      <c r="I14" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="24">
       <c r="A15" s="29" t="n">
@@ -4800,7 +4829,11 @@
         </is>
       </c>
       <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
+      <c r="I15" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="24">
       <c r="A16" s="29" t="n">
@@ -4837,7 +4870,11 @@
         </is>
       </c>
       <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="n"/>
+      <c r="I16" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="24">
       <c r="A17" s="29" t="n">
@@ -4865,7 +4902,7 @@
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>SW(WMS) SKU 관리 화면 – 정의·미정의 SKU 현황</t>
+          <t>SW(WMS) SKU 관리 화면 – 정의·미정의 SKU 현황 및 EXCEL 일괄 정의</t>
         </is>
       </c>
       <c r="G17" s="30" t="inlineStr">
@@ -4874,7 +4911,11 @@
         </is>
       </c>
       <c r="H17" s="29" t="n"/>
-      <c r="I17" s="29" t="n"/>
+      <c r="I17" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="24">
       <c r="A18" s="29" t="n">
@@ -4948,7 +4989,11 @@
         </is>
       </c>
       <c r="H19" s="29" t="n"/>
-      <c r="I19" s="29" t="n"/>
+      <c r="I19" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="24">
       <c r="A20" s="29" t="n">
@@ -4985,7 +5030,11 @@
         </is>
       </c>
       <c r="H20" s="29" t="n"/>
-      <c r="I20" s="29" t="n"/>
+      <c r="I20" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="24">
       <c r="A21" s="29" t="n">
@@ -5022,7 +5071,11 @@
         </is>
       </c>
       <c r="H21" s="29" t="n"/>
-      <c r="I21" s="29" t="n"/>
+      <c r="I21" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="24">
       <c r="A22" s="29" t="n">
@@ -5059,7 +5112,11 @@
         </is>
       </c>
       <c r="H22" s="29" t="n"/>
-      <c r="I22" s="29" t="n"/>
+      <c r="I22" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="24">
       <c r="A23" s="29" t="n">
@@ -8051,7 +8108,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="29.25" customHeight="1" s="24">
       <c r="A3" s="28" t="inlineStr">
         <is>

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1_제출서류 현황'!$A$3:$G$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_불일치·확인 필요'!$A$3:$F$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3_등급 조정 내역'!$A$3:$J$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_증빙자료 수집 목록'!$A$3:$I$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_증빙자료 수집 목록'!$A$3:$I$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5_확인 후 등급 변동'!$A$3:$D$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -4281,7 +4281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="23" min="1" max="1"/>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>SW(WMS) SKU 관리 화면 – 정의·미정의 SKU 현황 및 EXCEL 일괄 정의</t>
+          <t>SW(WMS) SKU 관리 화면 – 정의·미정의 SKU 현황, EXCEL 일괄 정의</t>
         </is>
       </c>
       <c r="G17" s="30" t="inlineStr">
@@ -5272,36 +5272,40 @@
       </c>
       <c r="B27" s="29" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>1.2.2</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>작업경로 관리</t>
+          <t>적치장소 이동</t>
         </is>
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
-          <t>p.14</t>
+          <t>p.13</t>
         </is>
       </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F27" s="30" t="inlineStr">
         <is>
-          <t>레이아웃관리 화면 캡처</t>
+          <t>지게차 안전작업 실천 서약서(2026.06.23, 영종센터 운전자 8명)</t>
         </is>
       </c>
       <c r="G27" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H27" s="29" t="n"/>
-      <c r="I27" s="29" t="n"/>
+      <c r="I27" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="24">
       <c r="A28" s="29" t="n">
@@ -5324,17 +5328,17 @@
       </c>
       <c r="E28" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>보관 영역 로케이션 배치도</t>
+          <t>레이아웃관리 화면 캡처</t>
         </is>
       </c>
       <c r="G28" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H28" s="29" t="n"/>
@@ -5346,32 +5350,32 @@
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>1.2.3</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>적치장소 식별 및 작업</t>
+          <t>작업경로 관리</t>
         </is>
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>p.15</t>
+          <t>p.14</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F29" s="30" t="inlineStr">
         <is>
-          <t>로케이션 라벨 부착 사진</t>
+          <t>보관 영역 로케이션 배치도</t>
         </is>
       </c>
       <c r="G29" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H29" s="29" t="n"/>
@@ -5398,17 +5402,17 @@
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>셀 상세 화면 캡처</t>
+          <t>로케이션 라벨 부착 사진</t>
         </is>
       </c>
       <c r="G30" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H30" s="29" t="n"/>
@@ -5420,27 +5424,27 @@
       </c>
       <c r="B31" s="29" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>재고조사의 수행 및 방법</t>
+          <t>적치장소 식별 및 작업</t>
         </is>
       </c>
       <c r="D31" s="29" t="inlineStr">
         <is>
-          <t>p.16</t>
+          <t>p.15</t>
         </is>
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>재고실사 생성·수행 화면 캡처</t>
+          <t>셀 상세 화면 캡처</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -5472,17 +5476,17 @@
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>실사 결과 및 재고 조정 이력</t>
+          <t>재고실사 생성·수행 화면 캡처</t>
         </is>
       </c>
       <c r="G32" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H32" s="29" t="n"/>
@@ -5494,32 +5498,32 @@
       </c>
       <c r="B33" s="29" t="inlineStr">
         <is>
-          <t>1.3.2</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>재고보충정보의 생성 및 지시</t>
+          <t>재고조사의 수행 및 방법</t>
         </is>
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
-          <t>p.17</t>
+          <t>p.16</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F33" s="30" t="inlineStr">
         <is>
-          <t>재고 재배치(보충) 화면 캡처</t>
+          <t>실사 결과 및 재고 조정 이력</t>
         </is>
       </c>
       <c r="G33" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H33" s="29" t="n"/>
@@ -5531,17 +5535,17 @@
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>1.3.3</t>
+          <t>1.3.2</t>
         </is>
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>재고 보관위치의 조정</t>
+          <t>재고보충정보의 생성 및 지시</t>
         </is>
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>p.18</t>
+          <t>p.17</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
@@ -5551,7 +5555,7 @@
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>재배치 상세 화면 캡처</t>
+          <t>재고 재배치(보충) 화면 캡처</t>
         </is>
       </c>
       <c r="G34" s="30" t="inlineStr">
@@ -5568,17 +5572,17 @@
       </c>
       <c r="B35" s="29" t="inlineStr">
         <is>
-          <t>1.3.4</t>
+          <t>1.3.3</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>보관장소의 모니터링 및 관리</t>
+          <t>재고 보관위치의 조정</t>
         </is>
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
-          <t>p.19</t>
+          <t>p.18</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
@@ -5588,7 +5592,7 @@
       </c>
       <c r="F35" s="30" t="inlineStr">
         <is>
-          <t>전체 대시보드·대시보드 모니터 화면 캡처</t>
+          <t>재배치 상세 화면 캡처</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
@@ -5620,17 +5624,17 @@
       </c>
       <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>현장 상황판 사진</t>
+          <t>전체 대시보드·대시보드 모니터 화면 캡처</t>
         </is>
       </c>
       <c r="G36" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H36" s="29" t="n"/>
@@ -5657,17 +5661,17 @@
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F37" s="30" t="inlineStr">
         <is>
-          <t>마감리포트 캡처</t>
+          <t>현장 상황판 사진</t>
         </is>
       </c>
       <c r="G37" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H37" s="29" t="n"/>
@@ -5679,27 +5683,27 @@
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.4</t>
         </is>
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>재고 이력(선입선출 등) 및 품질관리</t>
+          <t>보관장소의 모니터링 및 관리</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>p.19</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>유통기한·로트 그룹핑 화면 및 자동 할당 결과 캡처</t>
+          <t>마감리포트 캡처</t>
         </is>
       </c>
       <c r="G38" s="30" t="inlineStr">
@@ -5716,17 +5720,17 @@
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>1.3.5</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>작업정보의 생성 및 지시</t>
+          <t>재고 이력(선입선출 등) 및 품질관리</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>p.21</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
@@ -5736,7 +5740,7 @@
       </c>
       <c r="F39" s="30" t="inlineStr">
         <is>
-          <t>픽킹 리스트 생성·관리 화면 캡처</t>
+          <t>유통기한·로트 그룹핑 화면 및 자동 할당 결과 캡처</t>
         </is>
       </c>
       <c r="G39" s="30" t="inlineStr">
@@ -5768,12 +5772,12 @@
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F40" s="29" t="inlineStr">
-        <is>
-          <t>PDA 피킹 지시 화면</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F40" s="30" t="inlineStr">
+        <is>
+          <t>픽킹 리스트 생성·관리 화면 캡처</t>
         </is>
       </c>
       <c r="G40" s="30" t="inlineStr">
@@ -5790,27 +5794,27 @@
       </c>
       <c r="B41" s="29" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>작업정보의 확인 방법</t>
+          <t>작업정보의 생성 및 지시</t>
         </is>
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>p.22</t>
+          <t>p.21</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>PDA 피킹 화면</t>
+          <t>PDA 피킹 지시 화면</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
@@ -5842,17 +5846,17 @@
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>PTL 점등 사진</t>
+          <t>PDA 피킹 화면</t>
         </is>
       </c>
       <c r="G42" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H42" s="29" t="n"/>
@@ -5864,32 +5868,32 @@
       </c>
       <c r="B43" s="29" t="inlineStr">
         <is>
-          <t>1.4.3</t>
+          <t>1.4.2</t>
         </is>
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>작업경로의 실시간 관리</t>
+          <t>작업정보의 확인 방법</t>
         </is>
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>p.23</t>
+          <t>p.22</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F43" s="30" t="inlineStr">
-        <is>
-          <t>픽킹 리스트 상세(로케이션 순) 캡처</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F43" s="29" t="inlineStr">
+        <is>
+          <t>PTL 점등 사진</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H43" s="29" t="n"/>
@@ -5901,17 +5905,17 @@
       </c>
       <c r="B44" s="29" t="inlineStr">
         <is>
-          <t>1.4.4</t>
+          <t>1.4.3</t>
         </is>
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>피킹 장소의 확인 및 작업</t>
+          <t>작업경로의 실시간 관리</t>
         </is>
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>p.24</t>
+          <t>p.23</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
@@ -5921,12 +5925,12 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>카트피킹 작업 사진</t>
+          <t>픽킹 리스트 상세(로케이션 순) 캡처</t>
         </is>
       </c>
       <c r="G44" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H44" s="29" t="n"/>
@@ -5953,17 +5957,17 @@
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F45" s="29" t="inlineStr">
-        <is>
-          <t>PDA 스캔 검증 화면</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F45" s="30" t="inlineStr">
+        <is>
+          <t>카트피킹 작업 사진</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H45" s="29" t="n"/>
@@ -5975,27 +5979,27 @@
       </c>
       <c r="B46" s="29" t="inlineStr">
         <is>
-          <t>1.4.5</t>
+          <t>1.4.4</t>
         </is>
       </c>
       <c r="C46" s="30" t="inlineStr">
         <is>
-          <t>분류정보의 생성 및 지시</t>
+          <t>피킹 장소의 확인 및 작업</t>
         </is>
       </c>
       <c r="D46" s="29" t="inlineStr">
         <is>
-          <t>p.25</t>
+          <t>p.24</t>
         </is>
       </c>
       <c r="E46" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F46" s="30" t="inlineStr">
-        <is>
-          <t>슈트 설정 화면 캡처</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F46" s="29" t="inlineStr">
+        <is>
+          <t>PDA 스캔 검증 화면</t>
         </is>
       </c>
       <c r="G46" s="30" t="inlineStr">
@@ -6027,17 +6031,17 @@
       </c>
       <c r="E47" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F47" s="30" t="inlineStr">
         <is>
-          <t>분류 영역 전경 사진</t>
+          <t>슈트 설정 화면 캡처</t>
         </is>
       </c>
       <c r="G47" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H47" s="29" t="n"/>
@@ -6049,27 +6053,27 @@
       </c>
       <c r="B48" s="29" t="inlineStr">
         <is>
-          <t>1.4.6</t>
+          <t>1.4.5</t>
         </is>
       </c>
       <c r="C48" s="30" t="inlineStr">
         <is>
-          <t>분류 작업</t>
+          <t>분류정보의 생성 및 지시</t>
         </is>
       </c>
       <c r="D48" s="29" t="inlineStr">
         <is>
-          <t>p.26</t>
+          <t>p.25</t>
         </is>
       </c>
       <c r="E48" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>휠소터·3D 소터·싱귤레이터 사진</t>
+          <t>분류 영역 전경 사진</t>
         </is>
       </c>
       <c r="G48" s="30" t="inlineStr">
@@ -6101,17 +6105,17 @@
       </c>
       <c r="E49" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F49" s="30" t="inlineStr">
         <is>
-          <t>소터 모니터링 화면 캡처</t>
+          <t>휠소터·3D 소터·싱귤레이터 사진</t>
         </is>
       </c>
       <c r="G49" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H49" s="29" t="n"/>
@@ -6123,27 +6127,27 @@
       </c>
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.4.6</t>
         </is>
       </c>
       <c r="C50" s="30" t="inlineStr">
         <is>
-          <t>포장장소로의 정보 제공 및 이동</t>
+          <t>분류 작업</t>
         </is>
       </c>
       <c r="D50" s="29" t="inlineStr">
         <is>
-          <t>p.27</t>
+          <t>p.26</t>
         </is>
       </c>
       <c r="E50" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>패킹 리스트 화면 캡처</t>
+          <t>소터 모니터링 화면 캡처</t>
         </is>
       </c>
       <c r="G50" s="30" t="inlineStr">
@@ -6175,17 +6179,17 @@
       </c>
       <c r="E51" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F51" s="30" t="inlineStr">
         <is>
-          <t>포장대 전경 사진</t>
+          <t>패킹 리스트 화면 캡처</t>
         </is>
       </c>
       <c r="G51" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H51" s="29" t="n"/>
@@ -6197,27 +6201,27 @@
       </c>
       <c r="B52" s="29" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="C52" s="30" t="inlineStr">
         <is>
-          <t>포장재 및 포장물품 관리</t>
+          <t>포장장소로의 정보 제공 및 이동</t>
         </is>
       </c>
       <c r="D52" s="29" t="inlineStr">
         <is>
-          <t>p.28</t>
+          <t>p.27</t>
         </is>
       </c>
       <c r="E52" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>포장재 보관 구역 사진</t>
+          <t>포장대 전경 사진</t>
         </is>
       </c>
       <c r="G52" s="30" t="inlineStr">
@@ -6234,17 +6238,17 @@
       </c>
       <c r="B53" s="29" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="C53" s="30" t="inlineStr">
         <is>
-          <t>검품/검수 및 오류관리(인식 및 처리)</t>
+          <t>포장재 및 포장물품 관리</t>
         </is>
       </c>
       <c r="D53" s="29" t="inlineStr">
         <is>
-          <t>p.29</t>
+          <t>p.28</t>
         </is>
       </c>
       <c r="E53" s="29" t="inlineStr">
@@ -6254,12 +6258,12 @@
       </c>
       <c r="F53" s="30" t="inlineStr">
         <is>
-          <t>검품 스캔 화면</t>
+          <t>포장재 보관 구역 사진</t>
         </is>
       </c>
       <c r="G53" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H53" s="29" t="n"/>
@@ -6286,12 +6290,12 @@
       </c>
       <c r="E54" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>녹화 영상 조회 화면 캡처</t>
+          <t>검품 스캔 화면</t>
         </is>
       </c>
       <c r="G54" s="30" t="inlineStr">
@@ -6323,17 +6327,17 @@
       </c>
       <c r="E55" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
-        </is>
-      </c>
-      <c r="F55" s="29" t="inlineStr">
-        <is>
-          <t>DWS 계측 사진</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F55" s="30" t="inlineStr">
+        <is>
+          <t>녹화 영상 조회 화면 캡처</t>
         </is>
       </c>
       <c r="G55" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H55" s="29" t="n"/>
@@ -6360,17 +6364,17 @@
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>[사진 4]</t>
-        </is>
-      </c>
-      <c r="F56" s="30" t="inlineStr">
-        <is>
-          <t>이상/클레임 보고서 양식</t>
+          <t>[사진 3]</t>
+        </is>
+      </c>
+      <c r="F56" s="29" t="inlineStr">
+        <is>
+          <t>DWS 계측 사진</t>
         </is>
       </c>
       <c r="G56" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H56" s="29" t="n"/>
@@ -6382,32 +6386,32 @@
       </c>
       <c r="B57" s="29" t="inlineStr">
         <is>
-          <t>1.5.4</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="C57" s="30" t="inlineStr">
         <is>
-          <t>포장 작업</t>
+          <t>검품/검수 및 오류관리(인식 및 처리)</t>
         </is>
       </c>
       <c r="D57" s="29" t="inlineStr">
         <is>
-          <t>p.30</t>
+          <t>p.29</t>
         </is>
       </c>
       <c r="E57" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 4]</t>
         </is>
       </c>
       <c r="F57" s="30" t="inlineStr">
         <is>
-          <t>포장대·봉함기 사진</t>
+          <t>이상/클레임 보고서 양식</t>
         </is>
       </c>
       <c r="G57" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H57" s="29" t="n"/>
@@ -6419,17 +6423,17 @@
       </c>
       <c r="B58" s="29" t="inlineStr">
         <is>
-          <t>1.5.5</t>
+          <t>1.5.4</t>
         </is>
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>배송정보 표시(라벨) 및 부착</t>
+          <t>포장 작업</t>
         </is>
       </c>
       <c r="D58" s="29" t="inlineStr">
         <is>
-          <t>p.31</t>
+          <t>p.30</t>
         </is>
       </c>
       <c r="E58" s="29" t="inlineStr">
@@ -6439,7 +6443,7 @@
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>오토라벨러 사진</t>
+          <t>포장대·봉함기 사진</t>
         </is>
       </c>
       <c r="G58" s="30" t="inlineStr">
@@ -6471,17 +6475,17 @@
       </c>
       <c r="E59" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F59" s="30" t="inlineStr">
         <is>
-          <t>송장 출력 화면</t>
+          <t>오토라벨러 사진</t>
         </is>
       </c>
       <c r="G59" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H59" s="29" t="n"/>
@@ -6493,32 +6497,32 @@
       </c>
       <c r="B60" s="29" t="inlineStr">
         <is>
-          <t>1.6.1</t>
+          <t>1.5.5</t>
         </is>
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>발주처별 분류</t>
+          <t>배송정보 표시(라벨) 및 부착</t>
         </is>
       </c>
       <c r="D60" s="29" t="inlineStr">
         <is>
-          <t>p.32</t>
+          <t>p.31</t>
         </is>
       </c>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>슈트별 분류 사진</t>
+          <t>송장 출력 화면</t>
         </is>
       </c>
       <c r="G60" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H60" s="29" t="n"/>
@@ -6545,17 +6549,17 @@
       </c>
       <c r="E61" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F61" s="30" t="inlineStr">
         <is>
-          <t>번들 검증 PDA 화면</t>
+          <t>슈트별 분류 사진</t>
         </is>
       </c>
       <c r="G61" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H61" s="29" t="n"/>
@@ -6567,32 +6571,32 @@
       </c>
       <c r="B62" s="29" t="inlineStr">
         <is>
-          <t>1.6.2</t>
+          <t>1.6.1</t>
         </is>
       </c>
       <c r="C62" s="30" t="inlineStr">
         <is>
-          <t>차량입차정보의 인식</t>
+          <t>발주처별 분류</t>
         </is>
       </c>
       <c r="D62" s="29" t="inlineStr">
         <is>
-          <t>p.33</t>
+          <t>p.32</t>
         </is>
       </c>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>상차 도크 사진</t>
+          <t>번들 검증 PDA 화면</t>
         </is>
       </c>
       <c r="G62" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H62" s="29" t="n"/>
@@ -6619,17 +6623,17 @@
       </c>
       <c r="E63" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F63" s="29" t="inlineStr">
-        <is>
-          <t>TLPS 인계 일정 화면</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F63" s="30" t="inlineStr">
+        <is>
+          <t>상차 도크 사진</t>
         </is>
       </c>
       <c r="G63" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H63" s="29" t="n"/>
@@ -6641,32 +6645,32 @@
       </c>
       <c r="B64" s="29" t="inlineStr">
         <is>
-          <t>1.6.3</t>
+          <t>1.6.2</t>
         </is>
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>상차순서 관리 및 작업</t>
+          <t>차량입차정보의 인식</t>
         </is>
       </c>
       <c r="D64" s="29" t="inlineStr">
         <is>
-          <t>p.34</t>
+          <t>p.33</t>
         </is>
       </c>
       <c r="E64" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F64" s="30" t="inlineStr">
-        <is>
-          <t>상차 작업 사진</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F64" s="29" t="inlineStr">
+        <is>
+          <t>TLPS 인계 일정 화면</t>
         </is>
       </c>
       <c r="G64" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H64" s="29" t="n"/>
@@ -6693,17 +6697,17 @@
       </c>
       <c r="E65" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F65" s="30" t="inlineStr">
         <is>
-          <t>인계 확인(스캔) 화면</t>
+          <t>상차 작업 사진</t>
         </is>
       </c>
       <c r="G65" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H65" s="29" t="n"/>
@@ -6715,27 +6719,27 @@
       </c>
       <c r="B66" s="29" t="inlineStr">
         <is>
-          <t>1.6.4</t>
+          <t>1.6.3</t>
         </is>
       </c>
       <c r="C66" s="30" t="inlineStr">
         <is>
-          <t>출고정보의 전달</t>
+          <t>상차순서 관리 및 작업</t>
         </is>
       </c>
       <c r="D66" s="29" t="inlineStr">
         <is>
-          <t>p.35</t>
+          <t>p.34</t>
         </is>
       </c>
       <c r="E66" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>출고 확정·송장 조회 화면</t>
+          <t>인계 확인(스캔) 화면</t>
         </is>
       </c>
       <c r="G66" s="30" t="inlineStr">
@@ -6767,12 +6771,12 @@
       </c>
       <c r="E67" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F67" s="30" t="inlineStr">
         <is>
-          <t>출고 영상 매핑 화면</t>
+          <t>출고 확정·송장 조회 화면</t>
         </is>
       </c>
       <c r="G67" s="30" t="inlineStr">
@@ -6789,32 +6793,32 @@
       </c>
       <c r="B68" s="29" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>1.6.4</t>
         </is>
       </c>
       <c r="C68" s="30" t="inlineStr">
         <is>
-          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
+          <t>출고정보의 전달</t>
         </is>
       </c>
       <c r="D68" s="29" t="inlineStr">
         <is>
-          <t>p.36</t>
+          <t>p.35</t>
         </is>
       </c>
       <c r="E68" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>도크·레벨러·차양 사진</t>
+          <t>출고 영상 매핑 화면</t>
         </is>
       </c>
       <c r="G68" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H68" s="29" t="n"/>
@@ -6841,17 +6845,17 @@
       </c>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F69" s="30" t="inlineStr">
         <is>
-          <t>바닥 평탄도·하중 근거(건축 설계도서 또는 임대인 제원표)</t>
+          <t>도크·레벨러·차양 사진</t>
         </is>
       </c>
       <c r="G69" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H69" s="29" t="n"/>
@@ -6878,17 +6882,17 @@
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>바닥 라인 표시 사진</t>
+          <t>바닥 평탄도·하중 근거(건축 설계도서 또는 임대인 제원표)</t>
         </is>
       </c>
       <c r="G70" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H70" s="29" t="n"/>
@@ -6900,27 +6904,27 @@
       </c>
       <c r="B71" s="29" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="C71" s="30" t="inlineStr">
         <is>
-          <t>내부구조(층고 및 기둥의 배치구조)</t>
+          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
         </is>
       </c>
       <c r="D71" s="29" t="inlineStr">
         <is>
-          <t>p.38</t>
+          <t>p.36</t>
         </is>
       </c>
       <c r="E71" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F71" s="30" t="inlineStr">
         <is>
-          <t>평면도(기둥 격자 치수)</t>
+          <t>바닥 라인 표시 사진</t>
         </is>
       </c>
       <c r="G71" s="30" t="inlineStr">
@@ -6952,12 +6956,12 @@
       </c>
       <c r="E72" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>보관 영역 전경(층고) 사진</t>
+          <t>평면도(기둥 격자 치수)</t>
         </is>
       </c>
       <c r="G72" s="30" t="inlineStr">
@@ -6974,32 +6978,32 @@
       </c>
       <c r="B73" s="29" t="inlineStr">
         <is>
-          <t>2.1.3</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="C73" s="30" t="inlineStr">
         <is>
-          <t>배치 및 동선 관리</t>
+          <t>내부구조(층고 및 기둥의 배치구조)</t>
         </is>
       </c>
       <c r="D73" s="29" t="inlineStr">
         <is>
-          <t>p.39</t>
+          <t>p.38</t>
         </is>
       </c>
       <c r="E73" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F73" s="30" t="inlineStr">
         <is>
-          <t>운영 Lay-out 도면</t>
+          <t>보관 영역 전경(층고) 사진</t>
         </is>
       </c>
       <c r="G73" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H73" s="29" t="n"/>
@@ -7026,17 +7030,17 @@
       </c>
       <c r="E74" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>램프웨이·동선 표시 사진</t>
+          <t>운영 Lay-out 도면</t>
         </is>
       </c>
       <c r="G74" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H74" s="29" t="n"/>
@@ -7048,32 +7052,32 @@
       </c>
       <c r="B75" s="29" t="inlineStr">
         <is>
-          <t>2.1.4</t>
+          <t>2.1.3</t>
         </is>
       </c>
       <c r="C75" s="30" t="inlineStr">
         <is>
-          <t>작업환경 관리(공조, 온도, 습도 등)</t>
+          <t>배치 및 동선 관리</t>
         </is>
       </c>
       <c r="D75" s="29" t="inlineStr">
         <is>
-          <t>p.40</t>
+          <t>p.39</t>
         </is>
       </c>
       <c r="E75" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F75" s="30" t="inlineStr">
         <is>
-          <t>조도·온습도 측정 기록</t>
+          <t>램프웨이·동선 표시 사진</t>
         </is>
       </c>
       <c r="G75" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H75" s="29" t="n"/>
@@ -7100,12 +7104,12 @@
       </c>
       <c r="E76" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>방충·방서 관리 기록</t>
+          <t>조도·온습도 측정 기록</t>
         </is>
       </c>
       <c r="G76" s="30" t="inlineStr">
@@ -7137,17 +7141,17 @@
       </c>
       <c r="E77" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F77" s="30" t="inlineStr">
         <is>
-          <t>휴게실 사진</t>
+          <t>방충·방서 관리 기록</t>
         </is>
       </c>
       <c r="G77" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H77" s="29" t="n"/>
@@ -7159,32 +7163,32 @@
       </c>
       <c r="B78" s="29" t="inlineStr">
         <is>
-          <t>2.1.5</t>
+          <t>2.1.4</t>
         </is>
       </c>
       <c r="C78" s="30" t="inlineStr">
         <is>
-          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
+          <t>작업환경 관리(공조, 온도, 습도 등)</t>
         </is>
       </c>
       <c r="D78" s="29" t="inlineStr">
         <is>
-          <t>p.41</t>
+          <t>p.40</t>
         </is>
       </c>
       <c r="E78" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>소방시설 자체점검 결과보고서</t>
+          <t>휴게실 사진</t>
         </is>
       </c>
       <c r="G78" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H78" s="29" t="n"/>
@@ -7211,17 +7215,17 @@
       </c>
       <c r="E79" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F79" s="30" t="inlineStr">
         <is>
-          <t>비상구·소화설비 사진</t>
+          <t>소방시설 자체점검 결과보고서</t>
         </is>
       </c>
       <c r="G79" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H79" s="29" t="n"/>
@@ -7248,17 +7252,17 @@
       </c>
       <c r="E80" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>안전교육 이수 기록</t>
+          <t>비상구·소화설비 사진</t>
         </is>
       </c>
       <c r="G80" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H80" s="29" t="n"/>
@@ -7285,21 +7289,25 @@
       </c>
       <c r="E81" s="29" t="inlineStr">
         <is>
-          <t>[사진 4]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F81" s="30" t="inlineStr">
         <is>
-          <t>작업자 추적(QR) 화면</t>
+          <t>2025 근로자 안전보건교육 수료증(분기별 정기교육 1~4차, 올윈에듀)</t>
         </is>
       </c>
       <c r="G81" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H81" s="29" t="n"/>
-      <c r="I81" s="29" t="n"/>
+      <c r="I81" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="24">
       <c r="A82" s="29" t="n">
@@ -7307,32 +7315,32 @@
       </c>
       <c r="B82" s="29" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>2.1.5</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>비용 절감</t>
+          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
         </is>
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>p.42</t>
+          <t>p.41</t>
         </is>
       </c>
       <c r="E82" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 4]</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>최근 3년 물류비·절감률 실적표</t>
+          <t>작업자 추적(QR) 화면</t>
         </is>
       </c>
       <c r="G82" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H82" s="29" t="n"/>
@@ -7344,27 +7352,27 @@
       </c>
       <c r="B83" s="29" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>2.1.5</t>
         </is>
       </c>
       <c r="C83" s="30" t="inlineStr">
         <is>
-          <t>비용 절감</t>
+          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
         </is>
       </c>
       <c r="D83" s="29" t="inlineStr">
         <is>
-          <t>p.42</t>
+          <t>p.41</t>
         </is>
       </c>
       <c r="E83" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 5]</t>
         </is>
       </c>
       <c r="F83" s="30" t="inlineStr">
         <is>
-          <t>월간 성과보고 자료</t>
+          <t>지게차 안전작업 실천 서약서(2026.06.23, 영종센터 운전자 8명)</t>
         </is>
       </c>
       <c r="G83" s="30" t="inlineStr">
@@ -7373,7 +7381,11 @@
         </is>
       </c>
       <c r="H83" s="29" t="n"/>
-      <c r="I83" s="29" t="n"/>
+      <c r="I83" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="29.25" customHeight="1" s="24">
       <c r="A84" s="29" t="n">
@@ -7381,17 +7393,17 @@
       </c>
       <c r="B84" s="29" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>생산성 향상</t>
+          <t>비용 절감</t>
         </is>
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>p.43</t>
+          <t>p.42</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
@@ -7401,12 +7413,12 @@
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>작업자 추적 화면·리포트 캡처</t>
+          <t>최근 3년 물류비·절감률 실적표</t>
         </is>
       </c>
       <c r="G84" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H84" s="29" t="n"/>
@@ -7418,17 +7430,17 @@
       </c>
       <c r="B85" s="29" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="C85" s="30" t="inlineStr">
         <is>
-          <t>생산성 향상</t>
+          <t>비용 절감</t>
         </is>
       </c>
       <c r="D85" s="29" t="inlineStr">
         <is>
-          <t>p.43</t>
+          <t>p.42</t>
         </is>
       </c>
       <c r="E85" s="29" t="inlineStr">
@@ -7438,7 +7450,7 @@
       </c>
       <c r="F85" s="30" t="inlineStr">
         <is>
-          <t>최근 3년 UPH 실적표</t>
+          <t>월간 성과보고 자료</t>
         </is>
       </c>
       <c r="G85" s="30" t="inlineStr">
@@ -7455,17 +7467,17 @@
       </c>
       <c r="B86" s="29" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>품질 및 안전관리</t>
+          <t>생산성 향상</t>
         </is>
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.43</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
@@ -7475,12 +7487,12 @@
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>최근 3년 오출고율·정확도 실적</t>
+          <t>작업자 추적 화면·리포트 캡처</t>
         </is>
       </c>
       <c r="G86" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H86" s="29" t="n"/>
@@ -7492,17 +7504,17 @@
       </c>
       <c r="B87" s="29" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
         <is>
-          <t>품질 및 안전관리</t>
+          <t>생산성 향상</t>
         </is>
       </c>
       <c r="D87" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.43</t>
         </is>
       </c>
       <c r="E87" s="29" t="inlineStr">
@@ -7512,7 +7524,7 @@
       </c>
       <c r="F87" s="30" t="inlineStr">
         <is>
-          <t>클레임 처리 이력</t>
+          <t>최근 3년 UPH 실적표</t>
         </is>
       </c>
       <c r="G87" s="30" t="inlineStr">
@@ -7544,12 +7556,12 @@
       </c>
       <c r="E88" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>안전교육 기록</t>
+          <t>최근 3년 오출고율·정확도 실적</t>
         </is>
       </c>
       <c r="G88" s="30" t="inlineStr">
@@ -7566,27 +7578,27 @@
       </c>
       <c r="B89" s="29" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
+          <t>품질 및 안전관리</t>
         </is>
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>p.45</t>
+          <t>p.44</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F89" s="30" t="inlineStr">
         <is>
-          <t>친환경 포장재 적용률 실적</t>
+          <t>클레임 처리 이력</t>
         </is>
       </c>
       <c r="G89" s="30" t="inlineStr">
@@ -7603,27 +7615,27 @@
       </c>
       <c r="B90" s="29" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C90" s="30" t="inlineStr">
         <is>
-          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
+          <t>품질 및 안전관리</t>
         </is>
       </c>
       <c r="D90" s="29" t="inlineStr">
         <is>
-          <t>p.45</t>
+          <t>p.44</t>
         </is>
       </c>
       <c r="E90" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>폐기물 재활용 실적</t>
+          <t>2025 근로자 안전보건교육 수료증(분기별 정기교육 1~4차)</t>
         </is>
       </c>
       <c r="G90" s="30" t="inlineStr">
@@ -7632,7 +7644,11 @@
         </is>
       </c>
       <c r="H90" s="29" t="n"/>
-      <c r="I90" s="29" t="n"/>
+      <c r="I90" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="24">
       <c r="A91" s="29" t="n">
@@ -7655,17 +7671,17 @@
       </c>
       <c r="E91" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
-        </is>
-      </c>
-      <c r="F91" s="29" t="inlineStr">
-        <is>
-          <t>LED 조명 등 설비 사진</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F91" s="30" t="inlineStr">
+        <is>
+          <t>친환경 포장재 적용률 실적</t>
         </is>
       </c>
       <c r="G91" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H91" s="29" t="n"/>
@@ -7677,32 +7693,32 @@
       </c>
       <c r="B92" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C92" s="30" t="inlineStr">
         <is>
-          <t>수발주시스템/상품분류시스템</t>
+          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
         </is>
       </c>
       <c r="D92" s="29" t="inlineStr">
         <is>
-          <t>p.46</t>
+          <t>p.45</t>
         </is>
       </c>
       <c r="E92" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F92" s="29" t="inlineStr">
-        <is>
-          <t>Smartship 주문 수집·검증 화면</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F92" s="30" t="inlineStr">
+        <is>
+          <t>폐기물 재활용 실적</t>
         </is>
       </c>
       <c r="G92" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H92" s="29" t="n"/>
@@ -7714,32 +7730,32 @@
       </c>
       <c r="B93" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>수발주시스템/상품분류시스템</t>
+          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
         </is>
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>p.46</t>
+          <t>p.45</t>
         </is>
       </c>
       <c r="E93" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F93" s="30" t="inlineStr">
-        <is>
-          <t>채널 연동 현황 화면</t>
+          <t>[사진 3]</t>
+        </is>
+      </c>
+      <c r="F93" s="29" t="inlineStr">
+        <is>
+          <t>LED 조명 등 설비 사진</t>
         </is>
       </c>
       <c r="G93" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H93" s="29" t="n"/>
@@ -7751,17 +7767,17 @@
       </c>
       <c r="B94" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-2</t>
+          <t>2.3.1-1</t>
         </is>
       </c>
       <c r="C94" s="30" t="inlineStr">
         <is>
-          <t>입출고 및 배차배송시스템</t>
+          <t>수발주시스템/상품분류시스템</t>
         </is>
       </c>
       <c r="D94" s="29" t="inlineStr">
         <is>
-          <t>p.47</t>
+          <t>p.46</t>
         </is>
       </c>
       <c r="E94" s="29" t="inlineStr">
@@ -7769,9 +7785,9 @@
           <t>[사진 1]</t>
         </is>
       </c>
-      <c r="F94" s="30" t="inlineStr">
-        <is>
-          <t>입고·출고 화면</t>
+      <c r="F94" s="29" t="inlineStr">
+        <is>
+          <t>Smartship 주문 수집·검증 화면</t>
         </is>
       </c>
       <c r="G94" s="30" t="inlineStr">
@@ -7788,17 +7804,17 @@
       </c>
       <c r="B95" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-2</t>
+          <t>2.3.1-1</t>
         </is>
       </c>
       <c r="C95" s="30" t="inlineStr">
         <is>
-          <t>입출고 및 배차배송시스템</t>
+          <t>수발주시스템/상품분류시스템</t>
         </is>
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>p.47</t>
+          <t>p.46</t>
         </is>
       </c>
       <c r="E95" s="29" t="inlineStr">
@@ -7806,9 +7822,9 @@
           <t>[사진 2]</t>
         </is>
       </c>
-      <c r="F95" s="29" t="inlineStr">
-        <is>
-          <t>TLPS 운송·인계 화면</t>
+      <c r="F95" s="30" t="inlineStr">
+        <is>
+          <t>채널 연동 현황 화면</t>
         </is>
       </c>
       <c r="G95" s="30" t="inlineStr">
@@ -7825,17 +7841,17 @@
       </c>
       <c r="B96" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-3</t>
+          <t>2.3.1-2</t>
         </is>
       </c>
       <c r="C96" s="30" t="inlineStr">
         <is>
-          <t>재고관리시스템</t>
+          <t>입출고 및 배차배송시스템</t>
         </is>
       </c>
       <c r="D96" s="29" t="inlineStr">
         <is>
-          <t>p.48</t>
+          <t>p.47</t>
         </is>
       </c>
       <c r="E96" s="29" t="inlineStr">
@@ -7845,7 +7861,7 @@
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>대시보드·셀 상세·실사·마감리포트 화면</t>
+          <t>입고·출고 화면</t>
         </is>
       </c>
       <c r="G96" s="30" t="inlineStr">
@@ -7862,27 +7878,27 @@
       </c>
       <c r="B97" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-4</t>
+          <t>2.3.1-2</t>
         </is>
       </c>
       <c r="C97" s="30" t="inlineStr">
         <is>
-          <t>자원관리시스템</t>
+          <t>입출고 및 배차배송시스템</t>
         </is>
       </c>
       <c r="D97" s="29" t="inlineStr">
         <is>
-          <t>p.49</t>
+          <t>p.47</t>
         </is>
       </c>
       <c r="E97" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F97" s="30" t="inlineStr">
-        <is>
-          <t>레이아웃관리·디바이스·작업자 추적 화면</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F97" s="29" t="inlineStr">
+        <is>
+          <t>TLPS 운송·인계 화면</t>
         </is>
       </c>
       <c r="G97" s="30" t="inlineStr">
@@ -7899,17 +7915,17 @@
       </c>
       <c r="B98" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-5</t>
+          <t>2.3.1-3</t>
         </is>
       </c>
       <c r="C98" s="30" t="inlineStr">
         <is>
-          <t>물류지원시스템</t>
+          <t>재고관리시스템</t>
         </is>
       </c>
       <c r="D98" s="29" t="inlineStr">
         <is>
-          <t>p.50</t>
+          <t>p.48</t>
         </is>
       </c>
       <c r="E98" s="29" t="inlineStr">
@@ -7919,12 +7935,12 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>풀필먼트 주문관리 대시보드</t>
+          <t>대시보드·셀 상세·실사·마감리포트 화면</t>
         </is>
       </c>
       <c r="G98" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H98" s="29" t="n"/>
@@ -7936,27 +7952,27 @@
       </c>
       <c r="B99" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-5</t>
+          <t>2.3.1-4</t>
         </is>
       </c>
       <c r="C99" s="30" t="inlineStr">
         <is>
-          <t>물류지원시스템</t>
+          <t>자원관리시스템</t>
         </is>
       </c>
       <c r="D99" s="29" t="inlineStr">
         <is>
-          <t>p.50</t>
+          <t>p.49</t>
         </is>
       </c>
       <c r="E99" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F99" s="30" t="inlineStr">
         <is>
-          <t>반품 출고 관리 화면</t>
+          <t>레이아웃관리·디바이스·작업자 추적 화면</t>
         </is>
       </c>
       <c r="G99" s="30" t="inlineStr">
@@ -7988,17 +8004,17 @@
       </c>
       <c r="E100" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>오류화물 관리 화면</t>
+          <t>풀필먼트 주문관리 대시보드</t>
         </is>
       </c>
       <c r="G100" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H100" s="29" t="n"/>
@@ -8010,27 +8026,27 @@
       </c>
       <c r="B101" s="29" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>2.3.1-5</t>
         </is>
       </c>
       <c r="C101" s="30" t="inlineStr">
         <is>
-          <t>창고제어시스템(WCS, MCS)</t>
+          <t>물류지원시스템</t>
         </is>
       </c>
       <c r="D101" s="29" t="inlineStr">
         <is>
-          <t>p.51</t>
+          <t>p.50</t>
         </is>
       </c>
       <c r="E101" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F101" s="30" t="inlineStr">
         <is>
-          <t>소터 모니터링·슈트 설정 화면</t>
+          <t>반품 출고 관리 화면</t>
         </is>
       </c>
       <c r="G101" s="30" t="inlineStr">
@@ -8047,39 +8063,113 @@
       </c>
       <c r="B102" s="29" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>2.3.1-5</t>
         </is>
       </c>
       <c r="C102" s="30" t="inlineStr">
         <is>
-          <t>창고제어시스템(WCS, MCS)</t>
+          <t>물류지원시스템</t>
         </is>
       </c>
       <c r="D102" s="29" t="inlineStr">
         <is>
-          <t>p.51</t>
+          <t>p.50</t>
         </is>
       </c>
       <c r="E102" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>설비 구성도</t>
+          <t>오류화물 관리 화면</t>
         </is>
       </c>
       <c r="G102" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H102" s="29" t="n"/>
       <c r="I102" s="29" t="n"/>
     </row>
+    <row r="103">
+      <c r="A103" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="29" t="inlineStr">
+        <is>
+          <t>2.3.2</t>
+        </is>
+      </c>
+      <c r="C103" s="30" t="inlineStr">
+        <is>
+          <t>창고제어시스템(WCS, MCS)</t>
+        </is>
+      </c>
+      <c r="D103" s="29" t="inlineStr">
+        <is>
+          <t>p.51</t>
+        </is>
+      </c>
+      <c r="E103" s="29" t="inlineStr">
+        <is>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F103" s="30" t="inlineStr">
+        <is>
+          <t>소터 모니터링·슈트 설정 화면</t>
+        </is>
+      </c>
+      <c r="G103" s="30" t="inlineStr">
+        <is>
+          <t>캡처</t>
+        </is>
+      </c>
+      <c r="H103" s="29" t="n"/>
+      <c r="I103" s="29" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="29" t="n">
+        <v>101</v>
+      </c>
+      <c r="B104" s="29" t="inlineStr">
+        <is>
+          <t>2.3.2</t>
+        </is>
+      </c>
+      <c r="C104" s="30" t="inlineStr">
+        <is>
+          <t>창고제어시스템(WCS, MCS)</t>
+        </is>
+      </c>
+      <c r="D104" s="29" t="inlineStr">
+        <is>
+          <t>p.51</t>
+        </is>
+      </c>
+      <c r="E104" s="29" t="inlineStr">
+        <is>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F104" s="30" t="inlineStr">
+        <is>
+          <t>설비 구성도</t>
+        </is>
+      </c>
+      <c r="G104" s="30" t="inlineStr">
+        <is>
+          <t>자료</t>
+        </is>
+      </c>
+      <c r="H104" s="29" t="n"/>
+      <c r="I104" s="29" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I102"/>
+  <autoFilter ref="A3:I104"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -5144,7 +5144,7 @@
       </c>
       <c r="F23" s="29" t="inlineStr">
         <is>
-          <t>PDA 추천 로케이션 화면 캡처</t>
+          <t>SW 모바일(PDA) 적치 로케이션 지정 – 동일 SKU 기존 보관 위치 확인 → 배치 선반 할당</t>
         </is>
       </c>
       <c r="G23" s="30" t="inlineStr">
@@ -5153,7 +5153,11 @@
         </is>
       </c>
       <c r="H23" s="29" t="n"/>
-      <c r="I23" s="29" t="n"/>
+      <c r="I23" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="24">
       <c r="A24" s="29" t="n">
@@ -5333,7 +5337,7 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>레이아웃관리 화면 캡처</t>
+          <t>SW(WMS) 3D 뷰어 – 보관 구역·랙·셀 배치 및 셀별 재고 상태</t>
         </is>
       </c>
       <c r="G28" s="30" t="inlineStr">
@@ -5342,7 +5346,11 @@
         </is>
       </c>
       <c r="H28" s="29" t="n"/>
-      <c r="I28" s="29" t="n"/>
+      <c r="I28" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="24">
       <c r="A29" s="29" t="n">
@@ -5444,7 +5452,7 @@
       </c>
       <c r="F31" s="30" t="inlineStr">
         <is>
-          <t>셀 상세 화면 캡처</t>
+          <t>SW 모바일(PDA) 셀·SKU 스캔 – 로케이션별 SKU·수량 양방향 조회</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr">
@@ -5453,7 +5461,11 @@
         </is>
       </c>
       <c r="H31" s="29" t="n"/>
-      <c r="I31" s="29" t="n"/>
+      <c r="I31" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="24">
       <c r="A32" s="29" t="n">

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1_제출서류 현황'!$A$3:$G$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_불일치·확인 필요'!$A$3:$F$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3_등급 조정 내역'!$A$3:$J$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_증빙자료 수집 목록'!$A$3:$I$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_증빙자료 수집 목록'!$A$3:$I$106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5_확인 후 등급 변동'!$A$3:$D$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1575,6 +1575,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="24">
       <c r="B27" s="36" t="inlineStr">
         <is>
@@ -1679,6 +1680,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="24">
       <c r="A3" s="27" t="inlineStr">
         <is>
@@ -2285,6 +2287,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="24">
       <c r="A3" s="28" t="inlineStr">
         <is>
@@ -4281,7 +4284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="23" min="1" max="1"/>
@@ -5715,7 +5718,7 @@
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>마감리포트 캡처</t>
+          <t>SW(WMS) 마감리포트 – 일·주·월 단위 재고·입출고 집계(2026년 9월)</t>
         </is>
       </c>
       <c r="G38" s="30" t="inlineStr">
@@ -5724,7 +5727,11 @@
         </is>
       </c>
       <c r="H38" s="29" t="n"/>
-      <c r="I38" s="29" t="n"/>
+      <c r="I38" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="24">
       <c r="A39" s="29" t="n">
@@ -5843,27 +5850,27 @@
       </c>
       <c r="B42" s="29" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>작업정보의 확인 방법</t>
+          <t>작업정보의 생성 및 지시</t>
         </is>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>p.22</t>
+          <t>p.21</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>PDA 피킹 화면</t>
+          <t>SW(WMS) 픽킹 리스트 관리 – 주문 구성별 피킹 방식 구분</t>
         </is>
       </c>
       <c r="G42" s="30" t="inlineStr">
@@ -5872,7 +5879,11 @@
         </is>
       </c>
       <c r="H42" s="29" t="n"/>
-      <c r="I42" s="29" t="n"/>
+      <c r="I42" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="24">
       <c r="A43" s="29" t="n">
@@ -5895,17 +5906,17 @@
       </c>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F43" s="29" t="inlineStr">
         <is>
-          <t>PTL 점등 사진</t>
+          <t>PDA 피킹 화면</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H43" s="29" t="n"/>
@@ -5917,32 +5928,32 @@
       </c>
       <c r="B44" s="29" t="inlineStr">
         <is>
-          <t>1.4.3</t>
+          <t>1.4.2</t>
         </is>
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>작업경로의 실시간 관리</t>
+          <t>작업정보의 확인 방법</t>
         </is>
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>p.23</t>
+          <t>p.22</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F44" s="30" t="inlineStr">
-        <is>
-          <t>픽킹 리스트 상세(로케이션 순) 캡처</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F44" s="29" t="inlineStr">
+        <is>
+          <t>PTL 점등 사진</t>
         </is>
       </c>
       <c r="G44" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H44" s="29" t="n"/>
@@ -5954,17 +5965,17 @@
       </c>
       <c r="B45" s="29" t="inlineStr">
         <is>
-          <t>1.4.4</t>
+          <t>1.4.3</t>
         </is>
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>피킹 장소의 확인 및 작업</t>
+          <t>작업경로의 실시간 관리</t>
         </is>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>p.24</t>
+          <t>p.23</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
@@ -5974,16 +5985,20 @@
       </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>카트피킹 작업 사진</t>
+          <t>SW(WMS) 픽킹 리스트 출력 – 로케이션 순 피킹 순서 자동 정렬</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H45" s="29" t="n"/>
-      <c r="I45" s="29" t="n"/>
+      <c r="I45" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="24">
       <c r="A46" s="29" t="n">
@@ -6006,17 +6021,17 @@
       </c>
       <c r="E46" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F46" s="29" t="inlineStr">
-        <is>
-          <t>PDA 스캔 검증 화면</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F46" s="30" t="inlineStr">
+        <is>
+          <t>카트피킹 작업 사진</t>
         </is>
       </c>
       <c r="G46" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H46" s="29" t="n"/>
@@ -6028,27 +6043,27 @@
       </c>
       <c r="B47" s="29" t="inlineStr">
         <is>
-          <t>1.4.5</t>
+          <t>1.4.4</t>
         </is>
       </c>
       <c r="C47" s="30" t="inlineStr">
         <is>
-          <t>분류정보의 생성 및 지시</t>
+          <t>피킹 장소의 확인 및 작업</t>
         </is>
       </c>
       <c r="D47" s="29" t="inlineStr">
         <is>
-          <t>p.25</t>
+          <t>p.24</t>
         </is>
       </c>
       <c r="E47" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F47" s="30" t="inlineStr">
-        <is>
-          <t>슈트 설정 화면 캡처</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F47" s="29" t="inlineStr">
+        <is>
+          <t>PDA 스캔 검증 화면</t>
         </is>
       </c>
       <c r="G47" s="30" t="inlineStr">
@@ -6080,17 +6095,17 @@
       </c>
       <c r="E48" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>분류 영역 전경 사진</t>
+          <t>슈트 설정 화면 캡처</t>
         </is>
       </c>
       <c r="G48" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H48" s="29" t="n"/>
@@ -6102,27 +6117,27 @@
       </c>
       <c r="B49" s="29" t="inlineStr">
         <is>
-          <t>1.4.6</t>
+          <t>1.4.5</t>
         </is>
       </c>
       <c r="C49" s="30" t="inlineStr">
         <is>
-          <t>분류 작업</t>
+          <t>분류정보의 생성 및 지시</t>
         </is>
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>p.26</t>
+          <t>p.25</t>
         </is>
       </c>
       <c r="E49" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F49" s="30" t="inlineStr">
         <is>
-          <t>휠소터·3D 소터·싱귤레이터 사진</t>
+          <t>분류 영역 전경 사진</t>
         </is>
       </c>
       <c r="G49" s="30" t="inlineStr">
@@ -6154,17 +6169,17 @@
       </c>
       <c r="E50" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>소터 모니터링 화면 캡처</t>
+          <t>휠소터·3D 소터·싱귤레이터 사진</t>
         </is>
       </c>
       <c r="G50" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H50" s="29" t="n"/>
@@ -6176,27 +6191,27 @@
       </c>
       <c r="B51" s="29" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.4.6</t>
         </is>
       </c>
       <c r="C51" s="30" t="inlineStr">
         <is>
-          <t>포장장소로의 정보 제공 및 이동</t>
+          <t>분류 작업</t>
         </is>
       </c>
       <c r="D51" s="29" t="inlineStr">
         <is>
-          <t>p.27</t>
+          <t>p.26</t>
         </is>
       </c>
       <c r="E51" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F51" s="30" t="inlineStr">
         <is>
-          <t>패킹 리스트 화면 캡처</t>
+          <t>소터 모니터링 화면 캡처</t>
         </is>
       </c>
       <c r="G51" s="30" t="inlineStr">
@@ -6228,17 +6243,17 @@
       </c>
       <c r="E52" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>포장대 전경 사진</t>
+          <t>패킹 리스트 화면 캡처</t>
         </is>
       </c>
       <c r="G52" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H52" s="29" t="n"/>
@@ -6250,27 +6265,27 @@
       </c>
       <c r="B53" s="29" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="C53" s="30" t="inlineStr">
         <is>
-          <t>포장재 및 포장물품 관리</t>
+          <t>포장장소로의 정보 제공 및 이동</t>
         </is>
       </c>
       <c r="D53" s="29" t="inlineStr">
         <is>
-          <t>p.28</t>
+          <t>p.27</t>
         </is>
       </c>
       <c r="E53" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F53" s="30" t="inlineStr">
         <is>
-          <t>포장재 보관 구역 사진</t>
+          <t>포장대 전경 사진</t>
         </is>
       </c>
       <c r="G53" s="30" t="inlineStr">
@@ -6287,17 +6302,17 @@
       </c>
       <c r="B54" s="29" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>검품/검수 및 오류관리(인식 및 처리)</t>
+          <t>포장재 및 포장물품 관리</t>
         </is>
       </c>
       <c r="D54" s="29" t="inlineStr">
         <is>
-          <t>p.29</t>
+          <t>p.28</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
@@ -6307,12 +6322,12 @@
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>검품 스캔 화면</t>
+          <t>포장재 보관 구역 사진</t>
         </is>
       </c>
       <c r="G54" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H54" s="29" t="n"/>
@@ -6324,17 +6339,17 @@
       </c>
       <c r="B55" s="29" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>검품/검수 및 오류관리(인식 및 처리)</t>
+          <t>포장재 및 포장물품 관리</t>
         </is>
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
-          <t>p.29</t>
+          <t>p.28</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
@@ -6344,7 +6359,7 @@
       </c>
       <c r="F55" s="30" t="inlineStr">
         <is>
-          <t>녹화 영상 조회 화면 캡처</t>
+          <t>SW(WMS) SKU 관리 – 부자재(포장재) 품목별 재고 관리</t>
         </is>
       </c>
       <c r="G55" s="30" t="inlineStr">
@@ -6353,7 +6368,11 @@
         </is>
       </c>
       <c r="H55" s="29" t="n"/>
-      <c r="I55" s="29" t="n"/>
+      <c r="I55" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="24">
       <c r="A56" s="29" t="n">
@@ -6376,17 +6395,17 @@
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
-        </is>
-      </c>
-      <c r="F56" s="29" t="inlineStr">
-        <is>
-          <t>DWS 계측 사진</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F56" s="30" t="inlineStr">
+        <is>
+          <t>검품 스캔 화면</t>
         </is>
       </c>
       <c r="G56" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H56" s="29" t="n"/>
@@ -6413,17 +6432,17 @@
       </c>
       <c r="E57" s="29" t="inlineStr">
         <is>
-          <t>[사진 4]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F57" s="30" t="inlineStr">
         <is>
-          <t>이상/클레임 보고서 양식</t>
+          <t>녹화 영상 조회 화면 캡처</t>
         </is>
       </c>
       <c r="G57" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H57" s="29" t="n"/>
@@ -6435,27 +6454,27 @@
       </c>
       <c r="B58" s="29" t="inlineStr">
         <is>
-          <t>1.5.4</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>포장 작업</t>
+          <t>검품/검수 및 오류관리(인식 및 처리)</t>
         </is>
       </c>
       <c r="D58" s="29" t="inlineStr">
         <is>
-          <t>p.30</t>
+          <t>p.29</t>
         </is>
       </c>
       <c r="E58" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F58" s="30" t="inlineStr">
-        <is>
-          <t>포장대·봉함기 사진</t>
+          <t>[사진 3]</t>
+        </is>
+      </c>
+      <c r="F58" s="29" t="inlineStr">
+        <is>
+          <t>DWS 계측 사진</t>
         </is>
       </c>
       <c r="G58" s="30" t="inlineStr">
@@ -6472,32 +6491,32 @@
       </c>
       <c r="B59" s="29" t="inlineStr">
         <is>
-          <t>1.5.5</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="C59" s="30" t="inlineStr">
         <is>
-          <t>배송정보 표시(라벨) 및 부착</t>
+          <t>검품/검수 및 오류관리(인식 및 처리)</t>
         </is>
       </c>
       <c r="D59" s="29" t="inlineStr">
         <is>
-          <t>p.31</t>
+          <t>p.29</t>
         </is>
       </c>
       <c r="E59" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 4]</t>
         </is>
       </c>
       <c r="F59" s="30" t="inlineStr">
         <is>
-          <t>오토라벨러 사진</t>
+          <t>이상/클레임 보고서 양식</t>
         </is>
       </c>
       <c r="G59" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H59" s="29" t="n"/>
@@ -6509,32 +6528,32 @@
       </c>
       <c r="B60" s="29" t="inlineStr">
         <is>
-          <t>1.5.5</t>
+          <t>1.5.4</t>
         </is>
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>배송정보 표시(라벨) 및 부착</t>
+          <t>포장 작업</t>
         </is>
       </c>
       <c r="D60" s="29" t="inlineStr">
         <is>
-          <t>p.31</t>
+          <t>p.30</t>
         </is>
       </c>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>송장 출력 화면</t>
+          <t>포장대·봉함기 사진</t>
         </is>
       </c>
       <c r="G60" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H60" s="29" t="n"/>
@@ -6546,17 +6565,17 @@
       </c>
       <c r="B61" s="29" t="inlineStr">
         <is>
-          <t>1.6.1</t>
+          <t>1.5.5</t>
         </is>
       </c>
       <c r="C61" s="30" t="inlineStr">
         <is>
-          <t>발주처별 분류</t>
+          <t>배송정보 표시(라벨) 및 부착</t>
         </is>
       </c>
       <c r="D61" s="29" t="inlineStr">
         <is>
-          <t>p.32</t>
+          <t>p.31</t>
         </is>
       </c>
       <c r="E61" s="29" t="inlineStr">
@@ -6566,7 +6585,7 @@
       </c>
       <c r="F61" s="30" t="inlineStr">
         <is>
-          <t>슈트별 분류 사진</t>
+          <t>오토라벨러 사진</t>
         </is>
       </c>
       <c r="G61" s="30" t="inlineStr">
@@ -6583,17 +6602,17 @@
       </c>
       <c r="B62" s="29" t="inlineStr">
         <is>
-          <t>1.6.1</t>
+          <t>1.5.5</t>
         </is>
       </c>
       <c r="C62" s="30" t="inlineStr">
         <is>
-          <t>발주처별 분류</t>
+          <t>배송정보 표시(라벨) 및 부착</t>
         </is>
       </c>
       <c r="D62" s="29" t="inlineStr">
         <is>
-          <t>p.32</t>
+          <t>p.31</t>
         </is>
       </c>
       <c r="E62" s="29" t="inlineStr">
@@ -6603,7 +6622,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>번들 검증 PDA 화면</t>
+          <t>송장 출력 화면</t>
         </is>
       </c>
       <c r="G62" s="30" t="inlineStr">
@@ -6620,17 +6639,17 @@
       </c>
       <c r="B63" s="29" t="inlineStr">
         <is>
-          <t>1.6.2</t>
+          <t>1.6.1</t>
         </is>
       </c>
       <c r="C63" s="30" t="inlineStr">
         <is>
-          <t>차량입차정보의 인식</t>
+          <t>발주처별 분류</t>
         </is>
       </c>
       <c r="D63" s="29" t="inlineStr">
         <is>
-          <t>p.33</t>
+          <t>p.32</t>
         </is>
       </c>
       <c r="E63" s="29" t="inlineStr">
@@ -6640,7 +6659,7 @@
       </c>
       <c r="F63" s="30" t="inlineStr">
         <is>
-          <t>상차 도크 사진</t>
+          <t>슈트별 분류 사진</t>
         </is>
       </c>
       <c r="G63" s="30" t="inlineStr">
@@ -6657,17 +6676,17 @@
       </c>
       <c r="B64" s="29" t="inlineStr">
         <is>
-          <t>1.6.2</t>
+          <t>1.6.1</t>
         </is>
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>차량입차정보의 인식</t>
+          <t>발주처별 분류</t>
         </is>
       </c>
       <c r="D64" s="29" t="inlineStr">
         <is>
-          <t>p.33</t>
+          <t>p.32</t>
         </is>
       </c>
       <c r="E64" s="29" t="inlineStr">
@@ -6675,9 +6694,9 @@
           <t>[사진 2]</t>
         </is>
       </c>
-      <c r="F64" s="29" t="inlineStr">
-        <is>
-          <t>TLPS 인계 일정 화면</t>
+      <c r="F64" s="30" t="inlineStr">
+        <is>
+          <t>번들 검증 PDA 화면</t>
         </is>
       </c>
       <c r="G64" s="30" t="inlineStr">
@@ -6694,17 +6713,17 @@
       </c>
       <c r="B65" s="29" t="inlineStr">
         <is>
-          <t>1.6.3</t>
+          <t>1.6.2</t>
         </is>
       </c>
       <c r="C65" s="30" t="inlineStr">
         <is>
-          <t>상차순서 관리 및 작업</t>
+          <t>차량입차정보의 인식</t>
         </is>
       </c>
       <c r="D65" s="29" t="inlineStr">
         <is>
-          <t>p.34</t>
+          <t>p.33</t>
         </is>
       </c>
       <c r="E65" s="29" t="inlineStr">
@@ -6714,7 +6733,7 @@
       </c>
       <c r="F65" s="30" t="inlineStr">
         <is>
-          <t>상차 작업 사진</t>
+          <t>상차 도크 사진</t>
         </is>
       </c>
       <c r="G65" s="30" t="inlineStr">
@@ -6731,17 +6750,17 @@
       </c>
       <c r="B66" s="29" t="inlineStr">
         <is>
-          <t>1.6.3</t>
+          <t>1.6.2</t>
         </is>
       </c>
       <c r="C66" s="30" t="inlineStr">
         <is>
-          <t>상차순서 관리 및 작업</t>
+          <t>차량입차정보의 인식</t>
         </is>
       </c>
       <c r="D66" s="29" t="inlineStr">
         <is>
-          <t>p.34</t>
+          <t>p.33</t>
         </is>
       </c>
       <c r="E66" s="29" t="inlineStr">
@@ -6749,9 +6768,9 @@
           <t>[사진 2]</t>
         </is>
       </c>
-      <c r="F66" s="30" t="inlineStr">
-        <is>
-          <t>인계 확인(스캔) 화면</t>
+      <c r="F66" s="29" t="inlineStr">
+        <is>
+          <t>TLPS 인계 일정 화면</t>
         </is>
       </c>
       <c r="G66" s="30" t="inlineStr">
@@ -6768,17 +6787,17 @@
       </c>
       <c r="B67" s="29" t="inlineStr">
         <is>
-          <t>1.6.4</t>
+          <t>1.6.3</t>
         </is>
       </c>
       <c r="C67" s="30" t="inlineStr">
         <is>
-          <t>출고정보의 전달</t>
+          <t>상차순서 관리 및 작업</t>
         </is>
       </c>
       <c r="D67" s="29" t="inlineStr">
         <is>
-          <t>p.35</t>
+          <t>p.34</t>
         </is>
       </c>
       <c r="E67" s="29" t="inlineStr">
@@ -6788,12 +6807,12 @@
       </c>
       <c r="F67" s="30" t="inlineStr">
         <is>
-          <t>출고 확정·송장 조회 화면</t>
+          <t>상차 작업 사진</t>
         </is>
       </c>
       <c r="G67" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H67" s="29" t="n"/>
@@ -6805,17 +6824,17 @@
       </c>
       <c r="B68" s="29" t="inlineStr">
         <is>
-          <t>1.6.4</t>
+          <t>1.6.3</t>
         </is>
       </c>
       <c r="C68" s="30" t="inlineStr">
         <is>
-          <t>출고정보의 전달</t>
+          <t>상차순서 관리 및 작업</t>
         </is>
       </c>
       <c r="D68" s="29" t="inlineStr">
         <is>
-          <t>p.35</t>
+          <t>p.34</t>
         </is>
       </c>
       <c r="E68" s="29" t="inlineStr">
@@ -6825,7 +6844,7 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>출고 영상 매핑 화면</t>
+          <t>인계 확인(스캔) 화면</t>
         </is>
       </c>
       <c r="G68" s="30" t="inlineStr">
@@ -6842,17 +6861,17 @@
       </c>
       <c r="B69" s="29" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>1.6.4</t>
         </is>
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
+          <t>출고정보의 전달</t>
         </is>
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>p.36</t>
+          <t>p.35</t>
         </is>
       </c>
       <c r="E69" s="29" t="inlineStr">
@@ -6862,12 +6881,12 @@
       </c>
       <c r="F69" s="30" t="inlineStr">
         <is>
-          <t>도크·레벨러·차양 사진</t>
+          <t>출고 확정·송장 조회 화면</t>
         </is>
       </c>
       <c r="G69" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H69" s="29" t="n"/>
@@ -6879,17 +6898,17 @@
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>2.1.1</t>
+          <t>1.6.4</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
+          <t>출고정보의 전달</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>p.36</t>
+          <t>p.35</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
@@ -6899,12 +6918,12 @@
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>바닥 평탄도·하중 근거(건축 설계도서 또는 임대인 제원표)</t>
+          <t>출고 영상 매핑 화면</t>
         </is>
       </c>
       <c r="G70" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H70" s="29" t="n"/>
@@ -6931,12 +6950,12 @@
       </c>
       <c r="E71" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F71" s="30" t="inlineStr">
         <is>
-          <t>바닥 라인 표시 사진</t>
+          <t>도크·레벨러·차양 사진</t>
         </is>
       </c>
       <c r="G71" s="30" t="inlineStr">
@@ -6953,32 +6972,32 @@
       </c>
       <c r="B72" s="29" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>내부구조(층고 및 기둥의 배치구조)</t>
+          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
         </is>
       </c>
       <c r="D72" s="29" t="inlineStr">
         <is>
-          <t>p.38</t>
+          <t>p.36</t>
         </is>
       </c>
       <c r="E72" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>평면도(기둥 격자 치수)</t>
+          <t>바닥 평탄도·하중 근거(건축 설계도서 또는 임대인 제원표)</t>
         </is>
       </c>
       <c r="G72" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H72" s="29" t="n"/>
@@ -6990,27 +7009,27 @@
       </c>
       <c r="B73" s="29" t="inlineStr">
         <is>
-          <t>2.1.2</t>
+          <t>2.1.1</t>
         </is>
       </c>
       <c r="C73" s="30" t="inlineStr">
         <is>
-          <t>내부구조(층고 및 기둥의 배치구조)</t>
+          <t>도크 및 바닥성능(재질, 평탄도 및 하중)</t>
         </is>
       </c>
       <c r="D73" s="29" t="inlineStr">
         <is>
-          <t>p.38</t>
+          <t>p.36</t>
         </is>
       </c>
       <c r="E73" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F73" s="30" t="inlineStr">
         <is>
-          <t>보관 영역 전경(층고) 사진</t>
+          <t>바닥 라인 표시 사진</t>
         </is>
       </c>
       <c r="G73" s="30" t="inlineStr">
@@ -7027,17 +7046,17 @@
       </c>
       <c r="B74" s="29" t="inlineStr">
         <is>
-          <t>2.1.3</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>배치 및 동선 관리</t>
+          <t>내부구조(층고 및 기둥의 배치구조)</t>
         </is>
       </c>
       <c r="D74" s="29" t="inlineStr">
         <is>
-          <t>p.39</t>
+          <t>p.38</t>
         </is>
       </c>
       <c r="E74" s="29" t="inlineStr">
@@ -7047,12 +7066,12 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>운영 Lay-out 도면</t>
+          <t>평면도(기둥 격자 치수)</t>
         </is>
       </c>
       <c r="G74" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H74" s="29" t="n"/>
@@ -7064,17 +7083,17 @@
       </c>
       <c r="B75" s="29" t="inlineStr">
         <is>
-          <t>2.1.3</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="C75" s="30" t="inlineStr">
         <is>
-          <t>배치 및 동선 관리</t>
+          <t>내부구조(층고 및 기둥의 배치구조)</t>
         </is>
       </c>
       <c r="D75" s="29" t="inlineStr">
         <is>
-          <t>p.39</t>
+          <t>p.38</t>
         </is>
       </c>
       <c r="E75" s="29" t="inlineStr">
@@ -7084,7 +7103,7 @@
       </c>
       <c r="F75" s="30" t="inlineStr">
         <is>
-          <t>램프웨이·동선 표시 사진</t>
+          <t>보관 영역 전경(층고) 사진</t>
         </is>
       </c>
       <c r="G75" s="30" t="inlineStr">
@@ -7101,17 +7120,17 @@
       </c>
       <c r="B76" s="29" t="inlineStr">
         <is>
-          <t>2.1.4</t>
+          <t>2.1.3</t>
         </is>
       </c>
       <c r="C76" s="30" t="inlineStr">
         <is>
-          <t>작업환경 관리(공조, 온도, 습도 등)</t>
+          <t>배치 및 동선 관리</t>
         </is>
       </c>
       <c r="D76" s="29" t="inlineStr">
         <is>
-          <t>p.40</t>
+          <t>p.39</t>
         </is>
       </c>
       <c r="E76" s="29" t="inlineStr">
@@ -7121,7 +7140,7 @@
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>조도·온습도 측정 기록</t>
+          <t>운영 Lay-out 도면</t>
         </is>
       </c>
       <c r="G76" s="30" t="inlineStr">
@@ -7138,17 +7157,17 @@
       </c>
       <c r="B77" s="29" t="inlineStr">
         <is>
-          <t>2.1.4</t>
+          <t>2.1.3</t>
         </is>
       </c>
       <c r="C77" s="30" t="inlineStr">
         <is>
-          <t>작업환경 관리(공조, 온도, 습도 등)</t>
+          <t>배치 및 동선 관리</t>
         </is>
       </c>
       <c r="D77" s="29" t="inlineStr">
         <is>
-          <t>p.40</t>
+          <t>p.39</t>
         </is>
       </c>
       <c r="E77" s="29" t="inlineStr">
@@ -7158,12 +7177,12 @@
       </c>
       <c r="F77" s="30" t="inlineStr">
         <is>
-          <t>방충·방서 관리 기록</t>
+          <t>램프웨이·동선 표시 사진</t>
         </is>
       </c>
       <c r="G77" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H77" s="29" t="n"/>
@@ -7190,17 +7209,17 @@
       </c>
       <c r="E78" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>휴게실 사진</t>
+          <t>조도·온습도 측정 기록</t>
         </is>
       </c>
       <c r="G78" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H78" s="29" t="n"/>
@@ -7212,27 +7231,27 @@
       </c>
       <c r="B79" s="29" t="inlineStr">
         <is>
-          <t>2.1.5</t>
+          <t>2.1.4</t>
         </is>
       </c>
       <c r="C79" s="30" t="inlineStr">
         <is>
-          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
+          <t>작업환경 관리(공조, 온도, 습도 등)</t>
         </is>
       </c>
       <c r="D79" s="29" t="inlineStr">
         <is>
-          <t>p.41</t>
+          <t>p.40</t>
         </is>
       </c>
       <c r="E79" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F79" s="30" t="inlineStr">
         <is>
-          <t>소방시설 자체점검 결과보고서</t>
+          <t>방충·방서 관리 기록</t>
         </is>
       </c>
       <c r="G79" s="30" t="inlineStr">
@@ -7249,27 +7268,27 @@
       </c>
       <c r="B80" s="29" t="inlineStr">
         <is>
-          <t>2.1.5</t>
+          <t>2.1.4</t>
         </is>
       </c>
       <c r="C80" s="30" t="inlineStr">
         <is>
-          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
+          <t>작업환경 관리(공조, 온도, 습도 등)</t>
         </is>
       </c>
       <c r="D80" s="29" t="inlineStr">
         <is>
-          <t>p.41</t>
+          <t>p.40</t>
         </is>
       </c>
       <c r="E80" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>비상구·소화설비 사진</t>
+          <t>휴게실 사진</t>
         </is>
       </c>
       <c r="G80" s="30" t="inlineStr">
@@ -7301,12 +7320,12 @@
       </c>
       <c r="E81" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F81" s="30" t="inlineStr">
         <is>
-          <t>2025 근로자 안전보건교육 수료증(분기별 정기교육 1~4차, 올윈에듀)</t>
+          <t>소방시설 자체점검 결과보고서</t>
         </is>
       </c>
       <c r="G81" s="30" t="inlineStr">
@@ -7315,11 +7334,7 @@
         </is>
       </c>
       <c r="H81" s="29" t="n"/>
-      <c r="I81" s="29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="I81" s="29" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1" s="24">
       <c r="A82" s="29" t="n">
@@ -7342,17 +7357,17 @@
       </c>
       <c r="E82" s="29" t="inlineStr">
         <is>
-          <t>[사진 4]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>작업자 추적(QR) 화면</t>
+          <t>비상구·소화설비 사진</t>
         </is>
       </c>
       <c r="G82" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H82" s="29" t="n"/>
@@ -7379,12 +7394,12 @@
       </c>
       <c r="E83" s="29" t="inlineStr">
         <is>
-          <t>[사진 5]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F83" s="30" t="inlineStr">
         <is>
-          <t>지게차 안전작업 실천 서약서(2026.06.23, 영종센터 운전자 8명)</t>
+          <t>2025 근로자 안전보건교육 수료증(분기별 정기교육 1~4차, 올윈에듀)</t>
         </is>
       </c>
       <c r="G83" s="30" t="inlineStr">
@@ -7405,32 +7420,32 @@
       </c>
       <c r="B84" s="29" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>2.1.5</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>비용 절감</t>
+          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
         </is>
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>p.42</t>
+          <t>p.41</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 4]</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>최근 3년 물류비·절감률 실적표</t>
+          <t>작업자 추적(QR) 화면</t>
         </is>
       </c>
       <c r="G84" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H84" s="29" t="n"/>
@@ -7442,27 +7457,27 @@
       </c>
       <c r="B85" s="29" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>2.1.5</t>
         </is>
       </c>
       <c r="C85" s="30" t="inlineStr">
         <is>
-          <t>비용 절감</t>
+          <t>재해 및 안전관리(방화, 내진, 소방·대피시설, 안전사고관리 등)</t>
         </is>
       </c>
       <c r="D85" s="29" t="inlineStr">
         <is>
-          <t>p.42</t>
+          <t>p.41</t>
         </is>
       </c>
       <c r="E85" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 5]</t>
         </is>
       </c>
       <c r="F85" s="30" t="inlineStr">
         <is>
-          <t>월간 성과보고 자료</t>
+          <t>지게차 안전작업 실천 서약서(2026.06.23, 영종센터 운전자 8명)</t>
         </is>
       </c>
       <c r="G85" s="30" t="inlineStr">
@@ -7471,7 +7486,11 @@
         </is>
       </c>
       <c r="H85" s="29" t="n"/>
-      <c r="I85" s="29" t="n"/>
+      <c r="I85" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="29.25" customHeight="1" s="24">
       <c r="A86" s="29" t="n">
@@ -7479,17 +7498,17 @@
       </c>
       <c r="B86" s="29" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>생산성 향상</t>
+          <t>비용 절감</t>
         </is>
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>p.43</t>
+          <t>p.42</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
@@ -7499,12 +7518,12 @@
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>작업자 추적 화면·리포트 캡처</t>
+          <t>최근 3년 물류비·절감률 실적표</t>
         </is>
       </c>
       <c r="G86" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H86" s="29" t="n"/>
@@ -7516,17 +7535,17 @@
       </c>
       <c r="B87" s="29" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
         <is>
-          <t>생산성 향상</t>
+          <t>비용 절감</t>
         </is>
       </c>
       <c r="D87" s="29" t="inlineStr">
         <is>
-          <t>p.43</t>
+          <t>p.42</t>
         </is>
       </c>
       <c r="E87" s="29" t="inlineStr">
@@ -7536,7 +7555,7 @@
       </c>
       <c r="F87" s="30" t="inlineStr">
         <is>
-          <t>최근 3년 UPH 실적표</t>
+          <t>월간 성과보고 자료</t>
         </is>
       </c>
       <c r="G87" s="30" t="inlineStr">
@@ -7553,17 +7572,17 @@
       </c>
       <c r="B88" s="29" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="C88" s="30" t="inlineStr">
         <is>
-          <t>품질 및 안전관리</t>
+          <t>생산성 향상</t>
         </is>
       </c>
       <c r="D88" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.43</t>
         </is>
       </c>
       <c r="E88" s="29" t="inlineStr">
@@ -7573,12 +7592,12 @@
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>최근 3년 오출고율·정확도 실적</t>
+          <t>작업자 추적 화면·리포트 캡처</t>
         </is>
       </c>
       <c r="G88" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H88" s="29" t="n"/>
@@ -7590,17 +7609,17 @@
       </c>
       <c r="B89" s="29" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>품질 및 안전관리</t>
+          <t>생산성 향상</t>
         </is>
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.43</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
@@ -7610,7 +7629,7 @@
       </c>
       <c r="F89" s="30" t="inlineStr">
         <is>
-          <t>클레임 처리 이력</t>
+          <t>최근 3년 UPH 실적표</t>
         </is>
       </c>
       <c r="G89" s="30" t="inlineStr">
@@ -7642,12 +7661,12 @@
       </c>
       <c r="E90" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>2025 근로자 안전보건교육 수료증(분기별 정기교육 1~4차)</t>
+          <t>최근 3년 오출고율·정확도 실적</t>
         </is>
       </c>
       <c r="G90" s="30" t="inlineStr">
@@ -7656,11 +7675,7 @@
         </is>
       </c>
       <c r="H90" s="29" t="n"/>
-      <c r="I90" s="29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="I90" s="29" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1" s="24">
       <c r="A91" s="29" t="n">
@@ -7668,27 +7683,27 @@
       </c>
       <c r="B91" s="29" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C91" s="30" t="inlineStr">
         <is>
-          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
+          <t>품질 및 안전관리</t>
         </is>
       </c>
       <c r="D91" s="29" t="inlineStr">
         <is>
-          <t>p.45</t>
+          <t>p.44</t>
         </is>
       </c>
       <c r="E91" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F91" s="30" t="inlineStr">
         <is>
-          <t>친환경 포장재 적용률 실적</t>
+          <t>클레임 처리 이력</t>
         </is>
       </c>
       <c r="G91" s="30" t="inlineStr">
@@ -7705,27 +7720,27 @@
       </c>
       <c r="B92" s="29" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C92" s="30" t="inlineStr">
         <is>
-          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
+          <t>품질 및 안전관리</t>
         </is>
       </c>
       <c r="D92" s="29" t="inlineStr">
         <is>
-          <t>p.45</t>
+          <t>p.44</t>
         </is>
       </c>
       <c r="E92" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>폐기물 재활용 실적</t>
+          <t>2025 근로자 안전보건교육 수료증(분기별 정기교육 1~4차)</t>
         </is>
       </c>
       <c r="G92" s="30" t="inlineStr">
@@ -7734,7 +7749,11 @@
         </is>
       </c>
       <c r="H92" s="29" t="n"/>
-      <c r="I92" s="29" t="n"/>
+      <c r="I92" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="24">
       <c r="A93" s="29" t="n">
@@ -7757,17 +7776,17 @@
       </c>
       <c r="E93" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
-        </is>
-      </c>
-      <c r="F93" s="29" t="inlineStr">
-        <is>
-          <t>LED 조명 등 설비 사진</t>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F93" s="30" t="inlineStr">
+        <is>
+          <t>친환경 포장재 적용률 실적</t>
         </is>
       </c>
       <c r="G93" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H93" s="29" t="n"/>
@@ -7779,32 +7798,32 @@
       </c>
       <c r="B94" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C94" s="30" t="inlineStr">
         <is>
-          <t>수발주시스템/상품분류시스템</t>
+          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
         </is>
       </c>
       <c r="D94" s="29" t="inlineStr">
         <is>
-          <t>p.46</t>
+          <t>p.45</t>
         </is>
       </c>
       <c r="E94" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F94" s="29" t="inlineStr">
-        <is>
-          <t>Smartship 주문 수집·검증 화면</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F94" s="30" t="inlineStr">
+        <is>
+          <t>폐기물 재활용 실적</t>
         </is>
       </c>
       <c r="G94" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H94" s="29" t="n"/>
@@ -7816,32 +7835,32 @@
       </c>
       <c r="B95" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C95" s="30" t="inlineStr">
         <is>
-          <t>수발주시스템/상품분류시스템</t>
+          <t>친환경관리(절수, 절전, 폐기물, 재활용, 조명 등)</t>
         </is>
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>p.46</t>
+          <t>p.45</t>
         </is>
       </c>
       <c r="E95" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
-        </is>
-      </c>
-      <c r="F95" s="30" t="inlineStr">
-        <is>
-          <t>채널 연동 현황 화면</t>
+          <t>[사진 3]</t>
+        </is>
+      </c>
+      <c r="F95" s="29" t="inlineStr">
+        <is>
+          <t>LED 조명 등 설비 사진</t>
         </is>
       </c>
       <c r="G95" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H95" s="29" t="n"/>
@@ -7853,17 +7872,17 @@
       </c>
       <c r="B96" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-2</t>
+          <t>2.3.1-1</t>
         </is>
       </c>
       <c r="C96" s="30" t="inlineStr">
         <is>
-          <t>입출고 및 배차배송시스템</t>
+          <t>수발주시스템/상품분류시스템</t>
         </is>
       </c>
       <c r="D96" s="29" t="inlineStr">
         <is>
-          <t>p.47</t>
+          <t>p.46</t>
         </is>
       </c>
       <c r="E96" s="29" t="inlineStr">
@@ -7871,9 +7890,9 @@
           <t>[사진 1]</t>
         </is>
       </c>
-      <c r="F96" s="30" t="inlineStr">
-        <is>
-          <t>입고·출고 화면</t>
+      <c r="F96" s="29" t="inlineStr">
+        <is>
+          <t>Smartship 주문 수집·검증 화면</t>
         </is>
       </c>
       <c r="G96" s="30" t="inlineStr">
@@ -7890,17 +7909,17 @@
       </c>
       <c r="B97" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-2</t>
+          <t>2.3.1-1</t>
         </is>
       </c>
       <c r="C97" s="30" t="inlineStr">
         <is>
-          <t>입출고 및 배차배송시스템</t>
+          <t>수발주시스템/상품분류시스템</t>
         </is>
       </c>
       <c r="D97" s="29" t="inlineStr">
         <is>
-          <t>p.47</t>
+          <t>p.46</t>
         </is>
       </c>
       <c r="E97" s="29" t="inlineStr">
@@ -7908,9 +7927,9 @@
           <t>[사진 2]</t>
         </is>
       </c>
-      <c r="F97" s="29" t="inlineStr">
-        <is>
-          <t>TLPS 운송·인계 화면</t>
+      <c r="F97" s="30" t="inlineStr">
+        <is>
+          <t>채널 연동 현황 화면</t>
         </is>
       </c>
       <c r="G97" s="30" t="inlineStr">
@@ -7927,17 +7946,17 @@
       </c>
       <c r="B98" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-3</t>
+          <t>2.3.1-2</t>
         </is>
       </c>
       <c r="C98" s="30" t="inlineStr">
         <is>
-          <t>재고관리시스템</t>
+          <t>입출고 및 배차배송시스템</t>
         </is>
       </c>
       <c r="D98" s="29" t="inlineStr">
         <is>
-          <t>p.48</t>
+          <t>p.47</t>
         </is>
       </c>
       <c r="E98" s="29" t="inlineStr">
@@ -7947,7 +7966,7 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>대시보드·셀 상세·실사·마감리포트 화면</t>
+          <t>입고·출고 화면</t>
         </is>
       </c>
       <c r="G98" s="30" t="inlineStr">
@@ -7964,27 +7983,27 @@
       </c>
       <c r="B99" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-4</t>
+          <t>2.3.1-2</t>
         </is>
       </c>
       <c r="C99" s="30" t="inlineStr">
         <is>
-          <t>자원관리시스템</t>
+          <t>입출고 및 배차배송시스템</t>
         </is>
       </c>
       <c r="D99" s="29" t="inlineStr">
         <is>
-          <t>p.49</t>
+          <t>p.47</t>
         </is>
       </c>
       <c r="E99" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
-        </is>
-      </c>
-      <c r="F99" s="30" t="inlineStr">
-        <is>
-          <t>레이아웃관리·디바이스·작업자 추적 화면</t>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F99" s="29" t="inlineStr">
+        <is>
+          <t>TLPS 운송·인계 화면</t>
         </is>
       </c>
       <c r="G99" s="30" t="inlineStr">
@@ -8001,17 +8020,17 @@
       </c>
       <c r="B100" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-5</t>
+          <t>2.3.1-3</t>
         </is>
       </c>
       <c r="C100" s="30" t="inlineStr">
         <is>
-          <t>물류지원시스템</t>
+          <t>재고관리시스템</t>
         </is>
       </c>
       <c r="D100" s="29" t="inlineStr">
         <is>
-          <t>p.50</t>
+          <t>p.48</t>
         </is>
       </c>
       <c r="E100" s="29" t="inlineStr">
@@ -8021,12 +8040,12 @@
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>풀필먼트 주문관리 대시보드</t>
+          <t>대시보드·셀 상세·실사·마감리포트 화면</t>
         </is>
       </c>
       <c r="G100" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H100" s="29" t="n"/>
@@ -8038,27 +8057,27 @@
       </c>
       <c r="B101" s="29" t="inlineStr">
         <is>
-          <t>2.3.1-5</t>
+          <t>2.3.1-4</t>
         </is>
       </c>
       <c r="C101" s="30" t="inlineStr">
         <is>
-          <t>물류지원시스템</t>
+          <t>자원관리시스템</t>
         </is>
       </c>
       <c r="D101" s="29" t="inlineStr">
         <is>
-          <t>p.50</t>
+          <t>p.49</t>
         </is>
       </c>
       <c r="E101" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F101" s="30" t="inlineStr">
         <is>
-          <t>반품 출고 관리 화면</t>
+          <t>레이아웃관리·디바이스·작업자 추적 화면</t>
         </is>
       </c>
       <c r="G101" s="30" t="inlineStr">
@@ -8090,17 +8109,17 @@
       </c>
       <c r="E102" s="29" t="inlineStr">
         <is>
-          <t>[사진 3]</t>
+          <t>[사진 1]</t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>오류화물 관리 화면</t>
+          <t>풀필먼트 주문관리 대시보드</t>
         </is>
       </c>
       <c r="G102" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H102" s="29" t="n"/>
@@ -8112,27 +8131,27 @@
       </c>
       <c r="B103" s="29" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>2.3.1-5</t>
         </is>
       </c>
       <c r="C103" s="30" t="inlineStr">
         <is>
-          <t>창고제어시스템(WCS, MCS)</t>
+          <t>물류지원시스템</t>
         </is>
       </c>
       <c r="D103" s="29" t="inlineStr">
         <is>
-          <t>p.51</t>
+          <t>p.50</t>
         </is>
       </c>
       <c r="E103" s="29" t="inlineStr">
         <is>
-          <t>[사진 1]</t>
+          <t>[사진 2]</t>
         </is>
       </c>
       <c r="F103" s="30" t="inlineStr">
         <is>
-          <t>소터 모니터링·슈트 설정 화면</t>
+          <t>반품 출고 관리 화면</t>
         </is>
       </c>
       <c r="G103" s="30" t="inlineStr">
@@ -8149,39 +8168,113 @@
       </c>
       <c r="B104" s="29" t="inlineStr">
         <is>
-          <t>2.3.2</t>
+          <t>2.3.1-5</t>
         </is>
       </c>
       <c r="C104" s="30" t="inlineStr">
         <is>
-          <t>창고제어시스템(WCS, MCS)</t>
+          <t>물류지원시스템</t>
         </is>
       </c>
       <c r="D104" s="29" t="inlineStr">
         <is>
-          <t>p.51</t>
+          <t>p.50</t>
         </is>
       </c>
       <c r="E104" s="29" t="inlineStr">
         <is>
-          <t>[사진 2]</t>
+          <t>[사진 3]</t>
         </is>
       </c>
       <c r="F104" s="30" t="inlineStr">
         <is>
-          <t>설비 구성도</t>
+          <t>오류화물 관리 화면</t>
         </is>
       </c>
       <c r="G104" s="30" t="inlineStr">
         <is>
-          <t>자료</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H104" s="29" t="n"/>
       <c r="I104" s="29" t="n"/>
     </row>
+    <row r="105">
+      <c r="A105" s="29" t="n">
+        <v>102</v>
+      </c>
+      <c r="B105" s="29" t="inlineStr">
+        <is>
+          <t>2.3.2</t>
+        </is>
+      </c>
+      <c r="C105" s="30" t="inlineStr">
+        <is>
+          <t>창고제어시스템(WCS, MCS)</t>
+        </is>
+      </c>
+      <c r="D105" s="29" t="inlineStr">
+        <is>
+          <t>p.51</t>
+        </is>
+      </c>
+      <c r="E105" s="29" t="inlineStr">
+        <is>
+          <t>[사진 1]</t>
+        </is>
+      </c>
+      <c r="F105" s="30" t="inlineStr">
+        <is>
+          <t>소터 모니터링·슈트 설정 화면</t>
+        </is>
+      </c>
+      <c r="G105" s="30" t="inlineStr">
+        <is>
+          <t>캡처</t>
+        </is>
+      </c>
+      <c r="H105" s="29" t="n"/>
+      <c r="I105" s="29" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="29" t="n">
+        <v>103</v>
+      </c>
+      <c r="B106" s="29" t="inlineStr">
+        <is>
+          <t>2.3.2</t>
+        </is>
+      </c>
+      <c r="C106" s="30" t="inlineStr">
+        <is>
+          <t>창고제어시스템(WCS, MCS)</t>
+        </is>
+      </c>
+      <c r="D106" s="29" t="inlineStr">
+        <is>
+          <t>p.51</t>
+        </is>
+      </c>
+      <c r="E106" s="29" t="inlineStr">
+        <is>
+          <t>[사진 2]</t>
+        </is>
+      </c>
+      <c r="F106" s="30" t="inlineStr">
+        <is>
+          <t>설비 구성도</t>
+        </is>
+      </c>
+      <c r="G106" s="30" t="inlineStr">
+        <is>
+          <t>자료</t>
+        </is>
+      </c>
+      <c r="H106" s="29" t="n"/>
+      <c r="I106" s="29" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I104"/>
+  <autoFilter ref="A3:I106"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8210,6 +8303,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="29.25" customHeight="1" s="24">
       <c r="A3" s="28" t="inlineStr">
         <is>

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -1575,7 +1575,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="24">
       <c r="B27" s="36" t="inlineStr">
         <is>
@@ -1680,7 +1679,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="24">
       <c r="A3" s="27" t="inlineStr">
         <is>
@@ -2287,7 +2285,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="24">
       <c r="A3" s="28" t="inlineStr">
         <is>
@@ -2793,7 +2790,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="43">
         <f>0.5*D14+0.5*D14*(1-(E14-1)/5)</f>
@@ -2809,7 +2806,7 @@
       </c>
       <c r="J14" s="30" t="inlineStr">
         <is>
-          <t>보충정보가 정보시스템에서 생성·전달되고 실시간 관리되므로 3등급으로 평가함.</t>
+          <t>보관·피킹 겸용 셀 운영으로 보충 수요가 적고(최근 1년 보충 이동 2건), 필요 시 정보시스템에 수동 등록·추적하므로 4등급으로 평가함.</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5567,7 @@
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>재고 재배치(보충) 화면 캡처</t>
+          <t>SW(WMS) SKU 이동 처리 – 보충·이동 요청 등록 및 출발·도착 셀 지정</t>
         </is>
       </c>
       <c r="G34" s="30" t="inlineStr">
@@ -5607,7 +5604,7 @@
       </c>
       <c r="F35" s="30" t="inlineStr">
         <is>
-          <t>재배치 상세 화면 캡처</t>
+          <t>SW(WMS) SKU 이동 관리 – 유형별 이동 요청·처리 실적(입고·회수·SKU 이동·보충 등)</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
@@ -8303,7 +8300,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="29.25" customHeight="1" s="24">
       <c r="A3" s="28" t="inlineStr">
         <is>

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_확인 후 등급 변동" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1_제출서류 현황'!$A$3:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_불일치·확인 필요'!$A$3:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1_제출서류 현황'!$A$3:$H$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_불일치·확인 필요'!$A$3:$F$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3_등급 조정 내역'!$A$3:$J$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_증빙자료 수집 목록'!$A$3:$I$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_증빙자료 수집 목록'!$A$3:$K$106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5_확인 후 등급 변동'!$A$3:$D$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -120,8 +120,11 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -181,6 +184,16 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -216,7 +229,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -355,6 +368,13 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -698,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="23" min="1" max="1"/>
@@ -708,12 +728,13 @@
     <col width="13" customWidth="1" style="23" min="5" max="5"/>
     <col width="58" customWidth="1" style="23" min="6" max="6"/>
     <col width="34" customWidth="1" style="23" min="7" max="7"/>
+    <col width="62" customWidth="1" style="24" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="24">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>스마트물류센터 인증 제출서류 진행현황 (영종센터, 기준 2026.09.30)</t>
+          <t>스마트물류센터 인증 제출서류 진행현황 (영종센터, 기준 2026.10.14 · 「작성 서류 - yun」 폴더 기준)</t>
         </is>
       </c>
     </row>
@@ -760,6 +781,11 @@
           <t>이번 작성본</t>
         </is>
       </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>10.14 점검 결과 (작성 서류 - yun)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="29.25" customHeight="1" s="24">
       <c r="A4" s="29" t="inlineStr">
@@ -797,6 +823,11 @@
           <t>신청서_기재안.docx</t>
         </is>
       </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>건축물대장으로 기재값 확정 가능: 착공 2019.07.08, 사용승인 2021.01.22, 연면적 186,095.3㎡, 주용도 창고시설(지상 6층). 단, 본점이 2026.06.01 「서울 강서구 마곡중앙8로7길 57, 비동 905~907호」로 이전(등기 2026.06.08) → 기재안 주소(강서로 463 새싹타워) 수정 필요. 실무담당자 칸 공란</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="29.25" customHeight="1" s="24">
       <c r="A5" s="29" t="inlineStr">
@@ -826,12 +857,17 @@
       </c>
       <c r="F5" s="29" t="inlineStr">
         <is>
-          <t>44개 세부항목 서술 완료(787.5점). 항목별 사진·캡처 삽입, 작성 메모 확인 후 삭제</t>
+          <t>44개 세부항목 서술 완료(789.0점·3등급). 남은 사진·증빙 48칸 + Ⅳ장 2칸(현장사진 29·자료 21) 촬영·확보 후 삽입. Ⅲ장 종업원 수·최근 3년 매출액·2023~2025 물동량·인증업무 담당자 입력, 작성 메모 14곳 확인 후 삭제</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
         <is>
           <t>01_자체평가서 및 증명자료(완성본).docx</t>
+        </is>
+      </c>
+      <c r="H5" s="29" t="inlineStr">
+        <is>
+          <t>10.14 수정본 확인: 총점 789.0점(3등급, ⑤와 일치). 사진·캡처 105칸 중 55칸 삽입. 이미지 속 캡션과 어긋난 Word 캡션 4곳 수정(2.3.1-2 사진1·2, 2.3.1-3, 2.3.2 사진1). 1.1.5 [사진 2]는 [사진 1]과 같은 이미지가 들어가 있어 교체 필요. 서약서·교육 수료증 PDF가 yun 폴더에 있어 바로 삽입 가능. 작성 메모 14곳·Ⅲ장 공란 남음</t>
         </is>
       </c>
     </row>
@@ -871,6 +907,11 @@
           <t>02_설계도면 및 분야별 설계설명서(완성본).docx</t>
         </is>
       </c>
+      <c r="H6" s="29" t="inlineStr">
+        <is>
+          <t>변동 없음. 작성 메모 2곳(검수+맵핑 877.5㎡ 분야 배정, 출고 처리능력 30,000 vs 35,000), 단면도 "확보 필요", 상호 일부 "트랙스로지스" 표기</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="24">
       <c r="A7" s="29" t="inlineStr">
@@ -908,6 +949,11 @@
           <t>03_설계변경 확인서(완성본).docx</t>
         </is>
       </c>
+      <c r="H7" s="29" t="inlineStr">
+        <is>
+          <t>건축물대장 확보: 사용승인일 2021.01.22 기재 가능. 변동사항에 2022.08.18 3층 방화구획 관련 대수선, 2024.03.12 증축(1층 전기실 57.48㎡) 이력 있음 → "해당 없음" 판단 재검토 필요</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="29.25" customHeight="1" s="24">
       <c r="A8" s="29" t="inlineStr">
@@ -945,6 +991,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="H8" s="29" t="inlineStr">
+        <is>
+          <t>yun 폴더에 해당 파일 없음(변동 확인 불가)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="29.25" customHeight="1" s="24">
       <c r="A9" s="29" t="inlineStr">
@@ -982,6 +1033,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="H9" s="29" t="inlineStr">
+        <is>
+          <t>yun 폴더 「3_운영매뉴얼_영종센터」(v2.0, 10.02 저장)도 작성일 2026-07-13, 상호 "Tracx Logis", KPI 목표 "예시" 표기 남음</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="29.25" customHeight="1" s="24">
       <c r="A10" s="29" t="inlineStr">
@@ -1011,12 +1067,17 @@
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>본문 작성 완료. [ ] 항목(소방설비·교육 이력·친환경 실적) 입력 후 사내 제정·승인</t>
+          <t>본문 작성 완료. [ ] 항목 입력: 소방설비 수량·비상구, 신규채용·지게차 운전·소방훈련 실시일, KPI 목표(오출고율·클레임율), 2023~2025 친환경 실적, LED·ISO 보유 여부, 제정일 → 사내 제정·승인</t>
         </is>
       </c>
       <c r="G10" s="29" t="inlineStr">
         <is>
           <t>06_품질안전환경관리 매뉴얼(완성본).docx</t>
+        </is>
+      </c>
+      <c r="H10" s="29" t="inlineStr">
+        <is>
+          <t>교육 이력 반영 확인(2025 정기 안전교육 1~4차, 지게차 서약 2026.06.23). 근거 파일 「교육 결과 보고서_2025.xls」 폴더에 확보. [ ] 19곳 남음 / 교육 결과 보고서_2025.pdf·지게차 서약서 PDF도 확보</t>
         </is>
       </c>
     </row>
@@ -1056,6 +1117,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="H11" s="29" t="inlineStr">
+        <is>
+          <t>yun 폴더 「1_물류정보시스템_기술서_영종센터」(v2.0): 작성일 2026-07-13, 상호 "Tracx Logis", "예시" 9곳, 1.3에 "한국통합물류협회" 표기 남음</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="24">
       <c r="A12" s="29" t="inlineStr">
@@ -1093,6 +1159,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="H12" s="29" t="inlineStr">
+        <is>
+          <t>yun 폴더 「2_업무-시스템_연계기술서_영종센터」(v2.0): 작성일 2026-07-13, 상호 "Tracx Logis", 코드·SLA "예시" 6곳 남음</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="24">
       <c r="A13" s="29" t="inlineStr">
@@ -1130,6 +1201,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="H13" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="29.25" customHeight="1" s="24">
       <c r="A14" s="29" t="inlineStr">
@@ -1149,7 +1225,7 @@
       </c>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>공유 받은 서류/4 법인등기사항증명서.pdf</t>
+          <t>작성 서류 - yun/4 법인등기사항증명서.pdf (말소사항 포함, 발행 2026.06.10, 28쪽)</t>
         </is>
       </c>
       <c r="E14" s="33" t="inlineStr">
@@ -1165,6 +1241,11 @@
       <c r="G14" s="29" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="29" t="inlineStr">
+        <is>
+          <t>yun 폴더에 확보(발행 2026.06.10, 말소사항 포함). 상호 트랙스로지스코리아 주식회사(TracX Logis Korea Co., Ltd.), 대표이사 김양훈·노현석. 본점 2026.06.01 마곡 이전 반영본. 신청일 기준 재발급 여부 확인, 36MB → 압축본 필요</t>
         </is>
       </c>
     </row>
@@ -1204,6 +1285,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="H15" s="29" t="inlineStr">
+        <is>
+          <t>yun 폴더에 해당 파일 없음</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="29.25" customHeight="1" s="24">
       <c r="A16" s="29" t="inlineStr">
@@ -1223,7 +1309,7 @@
       </c>
       <c r="D16" s="29" t="inlineStr">
         <is>
-          <t>5-1~5-4 (창고업·국제물류주선·화물운송주선·상업서류송달)</t>
+          <t>작성 서류 - yun/5-1~5-4 (창고업·국제물류주선·화물운송주선·상업서류송달)</t>
         </is>
       </c>
       <c r="E16" s="35" t="inlineStr">
@@ -1239,6 +1325,11 @@
       <c r="G16" s="29" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="29" t="inlineStr">
+        <is>
+          <t>yun 폴더에 사본 확보. 창고업 등록 보관면적 19,412.63㎡는 2026.07.15 일부 해지 전 면적 → 변경등록 필요 여부 확인</t>
         </is>
       </c>
     </row>
@@ -1278,6 +1369,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="H17" s="29" t="inlineStr">
+        <is>
+          <t>yun 폴더에 해당 파일 없음</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="24">
       <c r="A18" s="29" t="inlineStr">
@@ -1307,12 +1403,17 @@
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>근거 기준 조정본(787.5점) 작성. ②-1과 동일 등급으로 제출</t>
+          <t>근거 기준 조정본 789.0점(3등급). ②-1과 동일 등급으로 제출</t>
         </is>
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
           <t>자체평가점수표(일반)_근거기준.xlsx</t>
+        </is>
+      </c>
+      <c r="H18" s="30" t="inlineStr">
+        <is>
+          <t>근거기준 점수표 789.0점(3등급) — 01·⑥·3번 시트와 44개 항목 등급 일치 확인</t>
         </is>
       </c>
     </row>
@@ -1337,19 +1438,24 @@
           <t>없음</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" s="49" t="inlineStr">
         <is>
           <t>초안 완료</t>
         </is>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>44개 항목 × 수록 쪽·증명자료 매핑 완료. 사진 삽입 후 쪽번호 재확인</t>
+          <t>44개 항목 × 수록 쪽·증명자료 매핑 완료. 사진 삽입 완료 후 쪽번호 재확인, 작성 메모 삭제</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
           <t>⑥_조견표.docx</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="inlineStr">
+        <is>
+          <t>10.14: 증명자료 칸 캡션 30곳을 01 최신 캡션으로 맞춤(103칸 모두 일치). 등급 44개 일치. 남은 것: 쪽번호 재확인(01 사진 추가로 쪽 밀림 예상), 작성 메모 삭제</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1477,7 @@
       </c>
       <c r="D20" s="29" t="inlineStr">
         <is>
-          <t>⑦_신청기업 소개자료.docx</t>
+          <t>⑦_신청기업 소개자료.docx / 참고: yun/KOR 2026 TracX Logis Korea 회사소개서 v2.pdf</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
@@ -1387,6 +1493,11 @@
       <c r="G20" s="29" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="29" t="inlineStr">
+        <is>
+          <t>회사소개서 v2(2026.07.23, 20쪽) 확보. 오출고율 "0.0001%" 그대로 표기 → 05·01 기준과 통일 필요. 설립 2009(등기 회사성립 2009.09.04와 일치)</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1519,7 @@
       </c>
       <c r="D21" s="29" t="inlineStr">
         <is>
-          <t>⑧_신청대상 물류센터 소개자료.docx</t>
+          <t>⑧_신청대상 물류센터 소개자료.docx / 참고: yun/글로벌 물류센터 네트워크 소개서 v2·compressed.pdf</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
@@ -1424,6 +1535,11 @@
       <c r="G21" s="29" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="inlineStr">
+        <is>
+          <t>네트워크 소개서 v2 확보(참고자료). 사용승인일은 건축물대장 2021.01.22로 확정 → ⑧ "2021년 1월 준공(확인 필요)" 수정 가능</t>
         </is>
       </c>
     </row>
@@ -1445,22 +1561,27 @@
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="E22" s="33" t="inlineStr">
-        <is>
-          <t>발급·수집 필요</t>
+          <t>작성 서류 - yun/16-1 건축물대장, 16-2 임대차 승계동의서, 16-3 일부 해지 통지</t>
+        </is>
+      </c>
+      <c r="E22" s="47" t="inlineStr">
+        <is>
+          <t>보완 필요</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>건축물대장(총괄·일반) 발급, 임대차계약서 사본 확보 — 사용승인일·연면적·용도 확인의 근거</t>
+          <t>임대차계약서 본문(최초 2021.06.04 계약 및 변경계약) 사본 확보, 승계동의서 날짜 "2026.01.[*]" 공란본 → 서명 완료본 확보. 건축물대장은 신청일 기준 재발급 검토</t>
         </is>
       </c>
       <c r="G22" s="29" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="29" t="inlineStr">
+        <is>
+          <t>건축물대장(2026.05.21 발급): 영종도 항공물류센터 창고동 제1동, 사용승인 2021.01.22, 연면적 186,095.3㎡, 3층 41,966.33㎡(창고·하역장·램프), 내진설계 적용(VII-0.170g), 소유자 하나은행(2026.01.29 이전). 임대차: 기간 2021.09.01~2028.08.31, 3층 북측 19,412.63㎡(5,872.32평) → 2026.07.15부 2,398.07평 해지, 잔여 3,474.25평(약 11,485㎡)</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1603,7 @@
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
-          <t>공유 받은 서류/17 중소기업 확인서.pdf</t>
+          <t>작성 서류 - yun/17 중소기업 확인서.pdf</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
@@ -1498,6 +1619,11 @@
       <c r="G23" s="29" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="29" t="inlineStr">
+        <is>
+          <t>yun 폴더에 사본 확보</t>
         </is>
       </c>
     </row>
@@ -1537,6 +1663,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="H24" s="29" t="inlineStr">
+        <is>
+          <t>변동 없음</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="24">
       <c r="A25" s="30" t="inlineStr">
@@ -1574,6 +1705,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="H25" s="29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="24">
       <c r="B27" s="36" t="inlineStr">
@@ -1649,7 +1785,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G25"/>
+  <autoFilter ref="A3:H25"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1662,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="23" min="1" max="1"/>
@@ -1722,7 +1858,7 @@
       </c>
       <c r="C4" s="30" t="inlineStr">
         <is>
-          <t>기존 초안 전체: (주)트랙스로지스</t>
+          <t>기존 초안 전체: (주)트랙스로지스 / yun 폴더 1~4 영종센터 문서(v2.0): "Tracx Logis"</t>
         </is>
       </c>
       <c r="D4" s="30" t="inlineStr">
@@ -1757,7 +1893,7 @@
       </c>
       <c r="D5" s="30" t="inlineStr">
         <is>
-          <t>창고업 등록증: 김양훈 외 1명 / 확인서: 김양훈</t>
+          <t>창고업 등록증: 김양훈 외 1명 / 법인등기: 대표이사 김양훈·노현석(2024.10.31 취임) 각각 등기 / 승계동의서: 대표자 2인 날인</t>
         </is>
       </c>
       <c r="E5" s="30" t="inlineStr">
@@ -1787,12 +1923,12 @@
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>Lay-out: 운영면적 2,845평(≈9,405㎡), 구역 합계 8,214㎡ / 창고업 등록증 보관시설 19,412.63㎡</t>
+          <t>Lay-out: 운영면적 2,845평(≈9,405㎡) / 임대차: 2026.07.15부 잔여 3,474.25평(≈11,485㎡) / 창고업 등록증 19,412.63㎡(해지 전) / 건축물대장 3층 41,966.33㎡(건물 전체 층)</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>임대차계약서 면적 기준으로 확정, 용어(임차면적·운영면적·기능구역 합계) 구분 표기</t>
+          <t>임차면적 3,474.25평(≈11,485㎡)과 운영면적 2,845평을 구분 표기해 전 문서 통일</t>
         </is>
       </c>
       <c r="F6" s="38" t="inlineStr">
@@ -1882,7 +2018,7 @@
       </c>
       <c r="E9" s="30" t="inlineStr">
         <is>
-          <t>설비 대장 기준 종류별(휴대용·컨베이어·수동) 수량 확정</t>
+          <t>설비 대장 기준 종류별(휴대용·컨베이어·수동) 수량 확정 (10.07 확인: 재고 입고 시 휴대용 DWS 미사용 → 01 1.1.3 반영. 공정별 수량 통일은 미완)</t>
         </is>
       </c>
       <c r="F9" s="38" t="inlineStr">
@@ -2142,12 +2278,12 @@
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
-          <t>01·03·06·07·08·⑦·⑧·④: 공란</t>
+          <t>03·⑦·⑧·④: 공란 / 06 제정일: "2026. . ." / yun 1~3 기술서·매뉴얼: 2026-07-13</t>
         </is>
       </c>
       <c r="D18" s="29" t="inlineStr">
         <is>
-          <t>04·05: 2026년 8월 10일</t>
+          <t>01·02·06 기준일자: 2026.09.30 / 04·05: 2026년 8월 10일</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
@@ -2172,7 +2308,7 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>작성 서류(yjw91)/1_물류정보시스템 기술서 1.3: "한국통합물류협회 인증 공고"</t>
+          <t>작성 서류(yjw91)/1_물류정보시스템 기술서 1.3: "한국통합물류협회 인증 공고" — 「작성 서류 - yun/1_물류정보시스템_기술서_영종센터」 1.3에도 동일 문구</t>
         </is>
       </c>
       <c r="D19" s="30" t="inlineStr">
@@ -2182,7 +2318,7 @@
       </c>
       <c r="E19" s="30" t="inlineStr">
         <is>
-          <t>해당 원고를 재사용할 경우 수정</t>
+          <t>제출본에 사용하는 원고 모두 "한국교통연구원 스마트물류시설인증센터"로 수정</t>
         </is>
       </c>
       <c r="F19" s="40" t="inlineStr">
@@ -2207,17 +2343,17 @@
       </c>
       <c r="D20" s="30" t="inlineStr">
         <is>
-          <t>건축물대장 미확보</t>
+          <t>건축물대장(16-1): 사용승인 2021.01.22, 착공 2019.07.08</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>건축물대장 발급 후 신청서·⑧·03에 반영</t>
+          <t>① 신청서·⑧·03에 2021.01.22 반영(자료 확보 완료)</t>
         </is>
       </c>
       <c r="F20" s="38" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
     </row>
@@ -2251,8 +2387,188 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>조견표 캡션</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>⑥ 조견표: 기존 캡션(예: "PDA 피킹 화면", "송장 출력 화면")</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>01 자체평가서(10.14 수정본): 실제 화면명 캡션 — ⑥과 30곳 불일치</t>
+        </is>
+      </c>
+      <c r="E22" s="30" t="inlineStr">
+        <is>
+          <t>2026.10.14 처리 완료 — ⑥ 캡션 30곳 수정, 01과 103칸 모두 일치</t>
+        </is>
+      </c>
+      <c r="F22" s="39" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>필수 기재 공란</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>01 Ⅲ장: 종업원 수·최근 3년 매출액·2023~2025 물동량·인증업무 담당자 [ ]</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="inlineStr">
+        <is>
+          <t>① 신청서 기재안: 실무담당자·전화·팩스·E-mail [ ]</t>
+        </is>
+      </c>
+      <c r="E23" s="30" t="inlineStr">
+        <is>
+          <t>인사·재무팀 확정값 입력, 담당자는 01·① 동일하게</t>
+        </is>
+      </c>
+      <c r="F23" s="39" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>본점 주소</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>① 신청서 기재안·승계동의서: 서울 강서구 강서로 463, 7층(새싹타워)</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="inlineStr">
+        <is>
+          <t>법인등기: 2026.06.01 「서울 강서구 마곡중앙8로7길 57, 비동 905~907호」로 이전(06.08 등기)</t>
+        </is>
+      </c>
+      <c r="E24" s="30" t="inlineStr">
+        <is>
+          <t>신청서·소개자료 주소를 등기 기준으로 수정</t>
+        </is>
+      </c>
+      <c r="F24" s="39" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>창고업 등록 면적</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>5-1 창고업 등록증: 보관시설 19,412.63㎡</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="inlineStr">
+        <is>
+          <t>16-3 해지 통지: 2026.07.15부 2,398.07평 해지 → 잔여 3,474.25평</t>
+        </is>
+      </c>
+      <c r="E25" s="30" t="inlineStr">
+        <is>
+          <t>물류창고업 변경등록 필요 여부 확인(관할 중구청)</t>
+        </is>
+      </c>
+      <c r="F25" s="39" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>설계변경 이력</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>03 설계변경 확인서: "해당 없음"</t>
+        </is>
+      </c>
+      <c r="D26" s="29" t="inlineStr">
+        <is>
+          <t>건축물대장 변동: 2022.08.18 3층 방화구획 관련 대수선, 2024.03.12 증축(1층 전기실 57.48㎡)</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
+        <is>
+          <t>임차구역(3층) 관련 변경인지 확인 후 03 작성 방향 결정</t>
+        </is>
+      </c>
+      <c r="F26" s="39" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>캡션·이미지</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>01 1.1.5 [사진 2] 캡션: Smartship 입고신청 목록</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>삽입 이미지는 [사진 1](SW 입고 확정)과 동일 파일</t>
+        </is>
+      </c>
+      <c r="E27" s="30" t="inlineStr">
+        <is>
+          <t>Smartship 입고신청 목록 화면으로 이미지 교체</t>
+        </is>
+      </c>
+      <c r="F27" s="39" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:F21"/>
+  <autoFilter ref="A3:F27"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4281,7 +4597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:K114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="23" min="1" max="1"/>
@@ -4292,6 +4608,8 @@
     <col width="48" customWidth="1" style="23" min="6" max="6"/>
     <col width="8" customWidth="1" style="23" min="7" max="7"/>
     <col width="12" customWidth="1" style="23" min="8" max="9"/>
+    <col width="11" customWidth="1" style="24" min="10" max="10"/>
+    <col width="40" customWidth="1" style="24" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="24">
@@ -4354,6 +4672,16 @@
           <t>수집 완료(O)</t>
         </is>
       </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>01 삽입(10.14)</t>
+        </is>
+      </c>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>10.14 점검 비고</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="24">
       <c r="A4" s="29" t="n">
@@ -4395,6 +4723,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J4" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="24">
       <c r="A5" s="29" t="n">
@@ -4436,6 +4770,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J5" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K5" s="29" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="24">
       <c r="A6" s="29" t="n">
@@ -4477,6 +4817,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J6" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K6" s="29" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="24">
       <c r="A7" s="29" t="n">
@@ -4514,6 +4860,8 @@
       </c>
       <c r="H7" s="29" t="n"/>
       <c r="I7" s="29" t="n"/>
+      <c r="J7" s="29" t="n"/>
+      <c r="K7" s="29" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="24">
       <c r="A8" s="29" t="n">
@@ -4551,6 +4899,8 @@
       </c>
       <c r="H8" s="29" t="n"/>
       <c r="I8" s="29" t="n"/>
+      <c r="J8" s="29" t="n"/>
+      <c r="K8" s="29" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="24">
       <c r="A9" s="29" t="n">
@@ -4592,6 +4942,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J9" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" s="29" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="24">
       <c r="A10" s="29" t="n">
@@ -4633,6 +4989,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J10" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" s="29" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="24">
       <c r="A11" s="29" t="n">
@@ -4674,6 +5036,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J11" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" s="29" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="24">
       <c r="A12" s="29" t="n">
@@ -4711,6 +5079,8 @@
       </c>
       <c r="H12" s="29" t="n"/>
       <c r="I12" s="29" t="n"/>
+      <c r="J12" s="29" t="n"/>
+      <c r="K12" s="29" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="24">
       <c r="A13" s="29" t="n">
@@ -4752,6 +5122,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J13" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" s="29" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="24">
       <c r="A14" s="29" t="n">
@@ -4793,6 +5169,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J14" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" s="29" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="24">
       <c r="A15" s="29" t="n">
@@ -4834,6 +5216,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J15" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" s="29" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="24">
       <c r="A16" s="29" t="n">
@@ -4875,6 +5263,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J16" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" s="29" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="24">
       <c r="A17" s="29" t="n">
@@ -4916,6 +5310,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J17" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" s="29" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="24">
       <c r="A18" s="29" t="n">
@@ -4948,11 +5348,17 @@
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
-          <t>캡처</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="H18" s="29" t="n"/>
       <c r="I18" s="29" t="n"/>
+      <c r="J18" s="29" t="n"/>
+      <c r="K18" s="29" t="inlineStr">
+        <is>
+          <t>유형 정정(캡처→사진)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="24">
       <c r="A19" s="29" t="n">
@@ -4994,6 +5400,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J19" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" s="29" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="24">
       <c r="A20" s="29" t="n">
@@ -5035,6 +5447,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J20" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" s="29" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="24">
       <c r="A21" s="29" t="n">
@@ -5076,6 +5494,16 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J21" s="29" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K21" s="29" t="inlineStr">
+        <is>
+          <t>삽입 이미지가 [사진 1](입고 확정)과 동일 파일 → Smartship 입고신청 목록 화면으로 교체 필요</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="24">
       <c r="A22" s="29" t="n">
@@ -5117,6 +5545,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J22" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" s="29" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="24">
       <c r="A23" s="29" t="n">
@@ -5158,6 +5592,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J23" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" s="29" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="24">
       <c r="A24" s="29" t="n">
@@ -5195,6 +5635,8 @@
       </c>
       <c r="H24" s="29" t="n"/>
       <c r="I24" s="29" t="n"/>
+      <c r="J24" s="29" t="n"/>
+      <c r="K24" s="29" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="24">
       <c r="A25" s="29" t="n">
@@ -5232,6 +5674,8 @@
       </c>
       <c r="H25" s="29" t="n"/>
       <c r="I25" s="29" t="n"/>
+      <c r="J25" s="29" t="n"/>
+      <c r="K25" s="29" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="24">
       <c r="A26" s="29" t="n">
@@ -5269,6 +5713,8 @@
       </c>
       <c r="H26" s="29" t="n"/>
       <c r="I26" s="29" t="n"/>
+      <c r="J26" s="29" t="n"/>
+      <c r="K26" s="29" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="24">
       <c r="A27" s="29" t="n">
@@ -5310,6 +5756,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J27" s="29" t="n"/>
+      <c r="K27" s="29" t="inlineStr">
+        <is>
+          <t>수집 완료, 01 미삽입</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="24">
       <c r="A28" s="29" t="n">
@@ -5351,6 +5803,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J28" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" s="29" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="24">
       <c r="A29" s="29" t="n">
@@ -5388,6 +5846,8 @@
       </c>
       <c r="H29" s="29" t="n"/>
       <c r="I29" s="29" t="n"/>
+      <c r="J29" s="29" t="n"/>
+      <c r="K29" s="29" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="24">
       <c r="A30" s="29" t="n">
@@ -5425,6 +5885,8 @@
       </c>
       <c r="H30" s="29" t="n"/>
       <c r="I30" s="29" t="n"/>
+      <c r="J30" s="29" t="n"/>
+      <c r="K30" s="29" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="24">
       <c r="A31" s="29" t="n">
@@ -5466,6 +5928,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J31" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" s="29" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="24">
       <c r="A32" s="29" t="n">
@@ -5493,7 +5961,7 @@
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>재고실사 생성·수행 화면 캡처</t>
+          <t>SW(WMS) 재고실사 관리 – 실사 생성(대상 유형·기간 지정) 및 실사 목록</t>
         </is>
       </c>
       <c r="G32" s="30" t="inlineStr">
@@ -5502,7 +5970,21 @@
         </is>
       </c>
       <c r="H32" s="29" t="n"/>
-      <c r="I32" s="29" t="n"/>
+      <c r="I32" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J32" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 재고실사 생성·수행 화면 캡처) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="24">
       <c r="A33" s="29" t="n">
@@ -5530,7 +6012,7 @@
       </c>
       <c r="F33" s="30" t="inlineStr">
         <is>
-          <t>실사 결과 및 재고 조정 이력</t>
+          <t>SW(WMS) 재고실사 상세 – 창고·입고·선반·체크재고 비교 및 셀별 불일치 조정</t>
         </is>
       </c>
       <c r="G33" s="30" t="inlineStr">
@@ -5539,7 +6021,21 @@
         </is>
       </c>
       <c r="H33" s="29" t="n"/>
-      <c r="I33" s="29" t="n"/>
+      <c r="I33" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J33" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 실사 결과 및 재고 조정 이력) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="24">
       <c r="A34" s="29" t="n">
@@ -5576,7 +6072,21 @@
         </is>
       </c>
       <c r="H34" s="29" t="n"/>
-      <c r="I34" s="29" t="n"/>
+      <c r="I34" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J34" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" s="29" t="inlineStr">
+        <is>
+          <t>01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="24">
       <c r="A35" s="29" t="n">
@@ -5604,7 +6114,7 @@
       </c>
       <c r="F35" s="30" t="inlineStr">
         <is>
-          <t>SW(WMS) SKU 이동 관리 – 유형별 이동 요청·처리 실적(입고·회수·SKU 이동·보충 등)</t>
+          <t>SW(WMS) SKU 이동 관리 – 유형별 이동 요청·처리 실적(2026.01~10, 26,348건)</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
@@ -5613,7 +6123,21 @@
         </is>
       </c>
       <c r="H35" s="29" t="n"/>
-      <c r="I35" s="29" t="n"/>
+      <c r="I35" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: SW(WMS) SKU 이동 관리 – 유형별 이동 요청·처리 실적(입고·회수·SKU 이동·보충 등)) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="24">
       <c r="A36" s="29" t="n">
@@ -5641,7 +6165,7 @@
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>전체 대시보드·대시보드 모니터 화면 캡처</t>
+          <t>SW(WMS) 전체 대시보드 – 공정별 실시간 처리 현황 및 피킹존 재고부족·미출고 모니터링</t>
         </is>
       </c>
       <c r="G36" s="30" t="inlineStr">
@@ -5650,7 +6174,21 @@
         </is>
       </c>
       <c r="H36" s="29" t="n"/>
-      <c r="I36" s="29" t="n"/>
+      <c r="I36" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J36" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 전체 대시보드·대시보드 모니터 화면 캡처) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="24">
       <c r="A37" s="29" t="n">
@@ -5688,6 +6226,8 @@
       </c>
       <c r="H37" s="29" t="n"/>
       <c r="I37" s="29" t="n"/>
+      <c r="J37" s="29" t="n"/>
+      <c r="K37" s="29" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="24">
       <c r="A38" s="29" t="n">
@@ -5729,6 +6269,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J38" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" s="29" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="24">
       <c r="A39" s="29" t="n">
@@ -5756,7 +6302,7 @@
       </c>
       <c r="F39" s="30" t="inlineStr">
         <is>
-          <t>유통기한·로트 그룹핑 화면 및 자동 할당 결과 캡처</t>
+          <t>SW(WMS) SKU 입출고 이력 – 동일 SKU 로트별 유통기한 순 출고(FEFO)</t>
         </is>
       </c>
       <c r="G39" s="30" t="inlineStr">
@@ -5765,7 +6311,21 @@
         </is>
       </c>
       <c r="H39" s="29" t="n"/>
-      <c r="I39" s="29" t="n"/>
+      <c r="I39" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J39" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 유통기한·로트 그룹핑 화면 및 자동 할당 결과 캡처) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="24">
       <c r="A40" s="29" t="n">
@@ -5793,7 +6353,7 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>픽킹 리스트 생성·관리 화면 캡처</t>
+          <t>SW(WMS) 픽킹 리스트 생성 – 선택 주문 기준 생성(패킹장비 타입·정렬 기준·피킹 시작 지점 지정)</t>
         </is>
       </c>
       <c r="G40" s="30" t="inlineStr">
@@ -5802,7 +6362,21 @@
         </is>
       </c>
       <c r="H40" s="29" t="n"/>
-      <c r="I40" s="29" t="n"/>
+      <c r="I40" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J40" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 픽킹 리스트 생성·관리 화면 캡처) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="24">
       <c r="A41" s="29" t="n">
@@ -5830,7 +6404,7 @@
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>PDA 피킹 지시 화면</t>
+          <t>SW 모바일(PDA) 피킹 리스트 관리 – 타입별 피킹 현황 및 작업자 피킹 지시 목록</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
@@ -5839,7 +6413,21 @@
         </is>
       </c>
       <c r="H41" s="29" t="n"/>
-      <c r="I41" s="29" t="n"/>
+      <c r="I41" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J41" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: PDA 피킹 지시 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="24">
       <c r="A42" s="29" t="n">
@@ -5881,6 +6469,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J42" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" s="29" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="24">
       <c r="A43" s="29" t="n">
@@ -5908,7 +6502,7 @@
       </c>
       <c r="F43" s="29" t="inlineStr">
         <is>
-          <t>PDA 피킹 화면</t>
+          <t>SW 모바일(PDA) 피킹 화면 – SKU별 로케이션·지시수량 확인 및 스캔 수량 입력</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
@@ -5917,7 +6511,21 @@
         </is>
       </c>
       <c r="H43" s="29" t="n"/>
-      <c r="I43" s="29" t="n"/>
+      <c r="I43" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J43" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: PDA 피킹 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="24">
       <c r="A44" s="29" t="n">
@@ -5955,6 +6563,8 @@
       </c>
       <c r="H44" s="29" t="n"/>
       <c r="I44" s="29" t="n"/>
+      <c r="J44" s="29" t="n"/>
+      <c r="K44" s="29" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="24">
       <c r="A45" s="29" t="n">
@@ -5996,6 +6606,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J45" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" s="29" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="24">
       <c r="A46" s="29" t="n">
@@ -6033,6 +6649,8 @@
       </c>
       <c r="H46" s="29" t="n"/>
       <c r="I46" s="29" t="n"/>
+      <c r="J46" s="29" t="n"/>
+      <c r="K46" s="29" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="24">
       <c r="A47" s="29" t="n">
@@ -6060,7 +6678,7 @@
       </c>
       <c r="F47" s="29" t="inlineStr">
         <is>
-          <t>PDA 스캔 검증 화면</t>
+          <t>SW 모바일(PDA) 피킹 스캔 검증 – 지시에 없는 SKU 스캔 시 경고·진행 차단</t>
         </is>
       </c>
       <c r="G47" s="30" t="inlineStr">
@@ -6069,7 +6687,21 @@
         </is>
       </c>
       <c r="H47" s="29" t="n"/>
-      <c r="I47" s="29" t="n"/>
+      <c r="I47" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J47" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: PDA 스캔 검증 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="24">
       <c r="A48" s="29" t="n">
@@ -6097,7 +6729,7 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>슈트 설정 화면 캡처</t>
+          <t>SW(WMS) 슈트 설정 – 슈트번호별 라우트·소트코드 매핑</t>
         </is>
       </c>
       <c r="G48" s="30" t="inlineStr">
@@ -6106,7 +6738,21 @@
         </is>
       </c>
       <c r="H48" s="29" t="n"/>
-      <c r="I48" s="29" t="n"/>
+      <c r="I48" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J48" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 슈트 설정 화면 캡처) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="24">
       <c r="A49" s="29" t="n">
@@ -6144,6 +6790,8 @@
       </c>
       <c r="H49" s="29" t="n"/>
       <c r="I49" s="29" t="n"/>
+      <c r="J49" s="29" t="n"/>
+      <c r="K49" s="29" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="24">
       <c r="A50" s="29" t="n">
@@ -6181,6 +6829,8 @@
       </c>
       <c r="H50" s="29" t="n"/>
       <c r="I50" s="29" t="n"/>
+      <c r="J50" s="29" t="n"/>
+      <c r="K50" s="29" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="24">
       <c r="A51" s="29" t="n">
@@ -6208,7 +6858,7 @@
       </c>
       <c r="F51" s="30" t="inlineStr">
         <is>
-          <t>소터 모니터링 화면 캡처</t>
+          <t>SW(WMS) 소터 모니터링 – 투입구(DWS)별·시간대별 분류 처리 건수</t>
         </is>
       </c>
       <c r="G51" s="30" t="inlineStr">
@@ -6217,7 +6867,21 @@
         </is>
       </c>
       <c r="H51" s="29" t="n"/>
-      <c r="I51" s="29" t="n"/>
+      <c r="I51" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 소터 모니터링 화면 캡처) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="24">
       <c r="A52" s="29" t="n">
@@ -6245,7 +6909,7 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>패킹 리스트 화면 캡처</t>
+          <t>SW(WMS) 픽킹 리스트 관리 – 피킹·패킹 진행 현황 및 패킹 대기 작업 실시간 조회</t>
         </is>
       </c>
       <c r="G52" s="30" t="inlineStr">
@@ -6254,7 +6918,21 @@
         </is>
       </c>
       <c r="H52" s="29" t="n"/>
-      <c r="I52" s="29" t="n"/>
+      <c r="I52" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 패킹 리스트 화면 캡처) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="24">
       <c r="A53" s="29" t="n">
@@ -6292,6 +6970,8 @@
       </c>
       <c r="H53" s="29" t="n"/>
       <c r="I53" s="29" t="n"/>
+      <c r="J53" s="29" t="n"/>
+      <c r="K53" s="29" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="24">
       <c r="A54" s="29" t="n">
@@ -6329,6 +7009,8 @@
       </c>
       <c r="H54" s="29" t="n"/>
       <c r="I54" s="29" t="n"/>
+      <c r="J54" s="29" t="n"/>
+      <c r="K54" s="29" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="24">
       <c r="A55" s="29" t="n">
@@ -6370,6 +7052,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J55" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" s="29" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1" s="24">
       <c r="A56" s="29" t="n">
@@ -6397,7 +7085,7 @@
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>검품 스캔 화면</t>
+          <t>SW(WMS) 출고 검품 – SKU 스캔 검품·녹화 시작·박스/완충재 자동 선택·출고 처리</t>
         </is>
       </c>
       <c r="G56" s="30" t="inlineStr">
@@ -6406,7 +7094,21 @@
         </is>
       </c>
       <c r="H56" s="29" t="n"/>
-      <c r="I56" s="29" t="n"/>
+      <c r="I56" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J56" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 검품 스캔 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="24">
       <c r="A57" s="29" t="n">
@@ -6434,7 +7136,7 @@
       </c>
       <c r="F57" s="30" t="inlineStr">
         <is>
-          <t>녹화 영상 조회 화면 캡처</t>
+          <t>SW(WMS) 주문 상세 – 패킹 녹화 영상(카메라 2대) 주문별 매핑</t>
         </is>
       </c>
       <c r="G57" s="30" t="inlineStr">
@@ -6443,7 +7145,21 @@
         </is>
       </c>
       <c r="H57" s="29" t="n"/>
-      <c r="I57" s="29" t="n"/>
+      <c r="I57" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J57" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 녹화 영상 조회 화면 캡처) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="24">
       <c r="A58" s="29" t="n">
@@ -6481,6 +7197,8 @@
       </c>
       <c r="H58" s="29" t="n"/>
       <c r="I58" s="29" t="n"/>
+      <c r="J58" s="29" t="n"/>
+      <c r="K58" s="29" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1" s="24">
       <c r="A59" s="29" t="n">
@@ -6518,6 +7236,8 @@
       </c>
       <c r="H59" s="29" t="n"/>
       <c r="I59" s="29" t="n"/>
+      <c r="J59" s="29" t="n"/>
+      <c r="K59" s="29" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="24">
       <c r="A60" s="29" t="n">
@@ -6555,6 +7275,8 @@
       </c>
       <c r="H60" s="29" t="n"/>
       <c r="I60" s="29" t="n"/>
+      <c r="J60" s="29" t="n"/>
+      <c r="K60" s="29" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="24">
       <c r="A61" s="29" t="n">
@@ -6592,6 +7314,8 @@
       </c>
       <c r="H61" s="29" t="n"/>
       <c r="I61" s="29" t="n"/>
+      <c r="J61" s="29" t="n"/>
+      <c r="K61" s="29" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1" s="24">
       <c r="A62" s="29" t="n">
@@ -6619,7 +7343,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>송장 출력 화면</t>
+          <t>SW(WMS) 주문 상세 – 택배사·송장번호 자동 매칭 및 박스·완충재·무게 기록</t>
         </is>
       </c>
       <c r="G62" s="30" t="inlineStr">
@@ -6628,7 +7352,21 @@
         </is>
       </c>
       <c r="H62" s="29" t="n"/>
-      <c r="I62" s="29" t="n"/>
+      <c r="I62" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 송장 출력 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="24">
       <c r="A63" s="29" t="n">
@@ -6666,6 +7404,8 @@
       </c>
       <c r="H63" s="29" t="n"/>
       <c r="I63" s="29" t="n"/>
+      <c r="J63" s="29" t="n"/>
+      <c r="K63" s="29" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1" s="24">
       <c r="A64" s="29" t="n">
@@ -6693,7 +7433,7 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>번들 검증 PDA 화면</t>
+          <t>SW 모바일(PDA) 번들 작업 – MAWB·Route 확인 및 Route 불일치 화물 스캔 차단</t>
         </is>
       </c>
       <c r="G64" s="30" t="inlineStr">
@@ -6702,7 +7442,21 @@
         </is>
       </c>
       <c r="H64" s="29" t="n"/>
-      <c r="I64" s="29" t="n"/>
+      <c r="I64" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J64" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 번들 검증 PDA 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="24">
       <c r="A65" s="29" t="n">
@@ -6740,6 +7494,8 @@
       </c>
       <c r="H65" s="29" t="n"/>
       <c r="I65" s="29" t="n"/>
+      <c r="J65" s="29" t="n"/>
+      <c r="K65" s="29" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="24">
       <c r="A66" s="29" t="n">
@@ -6767,7 +7523,7 @@
       </c>
       <c r="F66" s="29" t="inlineStr">
         <is>
-          <t>TLPS 인계 일정 화면</t>
+          <t>TMS MAWB 상세 – 항공편 출항·입항 일정 및 Flight Confirm 관리</t>
         </is>
       </c>
       <c r="G66" s="30" t="inlineStr">
@@ -6776,7 +7532,21 @@
         </is>
       </c>
       <c r="H66" s="29" t="n"/>
-      <c r="I66" s="29" t="n"/>
+      <c r="I66" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J66" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: TLPS 인계 일정 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="24">
       <c r="A67" s="29" t="n">
@@ -6814,6 +7584,8 @@
       </c>
       <c r="H67" s="29" t="n"/>
       <c r="I67" s="29" t="n"/>
+      <c r="J67" s="29" t="n"/>
+      <c r="K67" s="29" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1" s="24">
       <c r="A68" s="29" t="n">
@@ -6841,7 +7613,7 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>인계 확인(스캔) 화면</t>
+          <t>SW 모바일(PDA) MAWB·번들팩 조회 – 출발 일정별 MAWB 확정 및 번들팩별 수량·무게 확인</t>
         </is>
       </c>
       <c r="G68" s="30" t="inlineStr">
@@ -6850,7 +7622,21 @@
         </is>
       </c>
       <c r="H68" s="29" t="n"/>
-      <c r="I68" s="29" t="n"/>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 인계 확인(스캔) 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="24">
       <c r="A69" s="29" t="n">
@@ -6878,7 +7664,7 @@
       </c>
       <c r="F69" s="30" t="inlineStr">
         <is>
-          <t>출고 확정·송장 조회 화면</t>
+          <t>TX 어드민 배송 추적 – 포장번호별 출고·DPC 입고·간선 이동 이력 실시간 조회</t>
         </is>
       </c>
       <c r="G69" s="30" t="inlineStr">
@@ -6887,7 +7673,21 @@
         </is>
       </c>
       <c r="H69" s="29" t="n"/>
-      <c r="I69" s="29" t="n"/>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J69" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 출고 확정·송장 조회 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="24">
       <c r="A70" s="29" t="n">
@@ -6915,7 +7715,7 @@
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>출고 영상 매핑 화면</t>
+          <t>Smartship(OMS) 배송 현황 – 출고 후 배송 단계·배송사·송장번호 자동 연동</t>
         </is>
       </c>
       <c r="G70" s="30" t="inlineStr">
@@ -6924,7 +7724,21 @@
         </is>
       </c>
       <c r="H70" s="29" t="n"/>
-      <c r="I70" s="29" t="n"/>
+      <c r="I70" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J70" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 출고 영상 매핑 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="24">
       <c r="A71" s="29" t="n">
@@ -6962,6 +7776,8 @@
       </c>
       <c r="H71" s="29" t="n"/>
       <c r="I71" s="29" t="n"/>
+      <c r="J71" s="29" t="n"/>
+      <c r="K71" s="29" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="24">
       <c r="A72" s="29" t="n">
@@ -6999,6 +7815,8 @@
       </c>
       <c r="H72" s="29" t="n"/>
       <c r="I72" s="29" t="n"/>
+      <c r="J72" s="29" t="n"/>
+      <c r="K72" s="29" t="n"/>
     </row>
     <row r="73" ht="29.25" customHeight="1" s="24">
       <c r="A73" s="29" t="n">
@@ -7036,6 +7854,8 @@
       </c>
       <c r="H73" s="29" t="n"/>
       <c r="I73" s="29" t="n"/>
+      <c r="J73" s="29" t="n"/>
+      <c r="K73" s="29" t="n"/>
     </row>
     <row r="74" ht="29.25" customHeight="1" s="24">
       <c r="A74" s="29" t="n">
@@ -7068,11 +7888,17 @@
       </c>
       <c r="G74" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>자료</t>
         </is>
       </c>
       <c r="H74" s="29" t="n"/>
       <c r="I74" s="29" t="n"/>
+      <c r="J74" s="29" t="n"/>
+      <c r="K74" s="29" t="inlineStr">
+        <is>
+          <t>유형 정정(사진→자료)</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="29.25" customHeight="1" s="24">
       <c r="A75" s="29" t="n">
@@ -7110,6 +7936,8 @@
       </c>
       <c r="H75" s="29" t="n"/>
       <c r="I75" s="29" t="n"/>
+      <c r="J75" s="29" t="n"/>
+      <c r="K75" s="29" t="n"/>
     </row>
     <row r="76" ht="29.25" customHeight="1" s="24">
       <c r="A76" s="29" t="n">
@@ -7147,6 +7975,8 @@
       </c>
       <c r="H76" s="29" t="n"/>
       <c r="I76" s="29" t="n"/>
+      <c r="J76" s="29" t="n"/>
+      <c r="K76" s="29" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1" s="24">
       <c r="A77" s="29" t="n">
@@ -7184,6 +8014,8 @@
       </c>
       <c r="H77" s="29" t="n"/>
       <c r="I77" s="29" t="n"/>
+      <c r="J77" s="29" t="n"/>
+      <c r="K77" s="29" t="n"/>
     </row>
     <row r="78" ht="15" customHeight="1" s="24">
       <c r="A78" s="29" t="n">
@@ -7221,6 +8053,8 @@
       </c>
       <c r="H78" s="29" t="n"/>
       <c r="I78" s="29" t="n"/>
+      <c r="J78" s="29" t="n"/>
+      <c r="K78" s="29" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1" s="24">
       <c r="A79" s="29" t="n">
@@ -7258,6 +8092,8 @@
       </c>
       <c r="H79" s="29" t="n"/>
       <c r="I79" s="29" t="n"/>
+      <c r="J79" s="29" t="n"/>
+      <c r="K79" s="29" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1" s="24">
       <c r="A80" s="29" t="n">
@@ -7295,6 +8131,8 @@
       </c>
       <c r="H80" s="29" t="n"/>
       <c r="I80" s="29" t="n"/>
+      <c r="J80" s="29" t="n"/>
+      <c r="K80" s="29" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1" s="24">
       <c r="A81" s="29" t="n">
@@ -7332,6 +8170,8 @@
       </c>
       <c r="H81" s="29" t="n"/>
       <c r="I81" s="29" t="n"/>
+      <c r="J81" s="29" t="n"/>
+      <c r="K81" s="29" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1" s="24">
       <c r="A82" s="29" t="n">
@@ -7369,6 +8209,8 @@
       </c>
       <c r="H82" s="29" t="n"/>
       <c r="I82" s="29" t="n"/>
+      <c r="J82" s="29" t="n"/>
+      <c r="K82" s="29" t="n"/>
     </row>
     <row r="83" ht="15" customHeight="1" s="24">
       <c r="A83" s="29" t="n">
@@ -7410,6 +8252,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J83" s="29" t="n"/>
+      <c r="K83" s="29" t="inlineStr">
+        <is>
+          <t>수집 완료, 01 미삽입</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="29.25" customHeight="1" s="24">
       <c r="A84" s="29" t="n">
@@ -7437,7 +8285,7 @@
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>작업자 추적(QR) 화면</t>
+          <t>SW(WMS) 공정별 인원관리 – 공정별 현재 투입 인원 실시간 파악(비상 시 인원 확인)</t>
         </is>
       </c>
       <c r="G84" s="30" t="inlineStr">
@@ -7446,7 +8294,21 @@
         </is>
       </c>
       <c r="H84" s="29" t="n"/>
-      <c r="I84" s="29" t="n"/>
+      <c r="I84" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J84" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 작업자 추적(QR) 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="29.25" customHeight="1" s="24">
       <c r="A85" s="29" t="n">
@@ -7488,6 +8350,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J85" s="29" t="n"/>
+      <c r="K85" s="29" t="inlineStr">
+        <is>
+          <t>수집 완료, 01 미삽입</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="29.25" customHeight="1" s="24">
       <c r="A86" s="29" t="n">
@@ -7525,6 +8393,8 @@
       </c>
       <c r="H86" s="29" t="n"/>
       <c r="I86" s="29" t="n"/>
+      <c r="J86" s="29" t="n"/>
+      <c r="K86" s="29" t="n"/>
     </row>
     <row r="87" ht="15" customHeight="1" s="24">
       <c r="A87" s="29" t="n">
@@ -7562,6 +8432,8 @@
       </c>
       <c r="H87" s="29" t="n"/>
       <c r="I87" s="29" t="n"/>
+      <c r="J87" s="29" t="n"/>
+      <c r="K87" s="29" t="n"/>
     </row>
     <row r="88" ht="15" customHeight="1" s="24">
       <c r="A88" s="29" t="n">
@@ -7589,7 +8461,7 @@
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>작업자 추적 화면·리포트 캡처</t>
+          <t>SW(WMS) 공정별 인원 관리 – 공정별·인원별 작업자 수·처리량·작업시간 집계</t>
         </is>
       </c>
       <c r="G88" s="30" t="inlineStr">
@@ -7598,7 +8470,21 @@
         </is>
       </c>
       <c r="H88" s="29" t="n"/>
-      <c r="I88" s="29" t="n"/>
+      <c r="I88" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J88" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 작업자 추적 화면·리포트 캡처) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="24">
       <c r="A89" s="29" t="n">
@@ -7636,6 +8522,8 @@
       </c>
       <c r="H89" s="29" t="n"/>
       <c r="I89" s="29" t="n"/>
+      <c r="J89" s="29" t="n"/>
+      <c r="K89" s="29" t="n"/>
     </row>
     <row r="90" ht="15" customHeight="1" s="24">
       <c r="A90" s="29" t="n">
@@ -7673,6 +8561,8 @@
       </c>
       <c r="H90" s="29" t="n"/>
       <c r="I90" s="29" t="n"/>
+      <c r="J90" s="29" t="n"/>
+      <c r="K90" s="29" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1" s="24">
       <c r="A91" s="29" t="n">
@@ -7710,6 +8600,8 @@
       </c>
       <c r="H91" s="29" t="n"/>
       <c r="I91" s="29" t="n"/>
+      <c r="J91" s="29" t="n"/>
+      <c r="K91" s="29" t="n"/>
     </row>
     <row r="92" ht="15" customHeight="1" s="24">
       <c r="A92" s="29" t="n">
@@ -7751,6 +8643,12 @@
           <t>O</t>
         </is>
       </c>
+      <c r="J92" s="29" t="n"/>
+      <c r="K92" s="29" t="inlineStr">
+        <is>
+          <t>수집 완료, 01 미삽입</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="24">
       <c r="A93" s="29" t="n">
@@ -7788,6 +8686,8 @@
       </c>
       <c r="H93" s="29" t="n"/>
       <c r="I93" s="29" t="n"/>
+      <c r="J93" s="29" t="n"/>
+      <c r="K93" s="29" t="n"/>
     </row>
     <row r="94" ht="15" customHeight="1" s="24">
       <c r="A94" s="29" t="n">
@@ -7825,6 +8725,8 @@
       </c>
       <c r="H94" s="29" t="n"/>
       <c r="I94" s="29" t="n"/>
+      <c r="J94" s="29" t="n"/>
+      <c r="K94" s="29" t="n"/>
     </row>
     <row r="95" ht="15" customHeight="1" s="24">
       <c r="A95" s="29" t="n">
@@ -7862,6 +8764,8 @@
       </c>
       <c r="H95" s="29" t="n"/>
       <c r="I95" s="29" t="n"/>
+      <c r="J95" s="29" t="n"/>
+      <c r="K95" s="29" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="24">
       <c r="A96" s="29" t="n">
@@ -7889,7 +8793,7 @@
       </c>
       <c r="F96" s="29" t="inlineStr">
         <is>
-          <t>Smartship 주문 수집·검증 화면</t>
+          <t>Smartship(OMS) 주문 관리 – 판매채널 API 주문 자동 수집 및 풀필먼트 출고 상태 관리</t>
         </is>
       </c>
       <c r="G96" s="30" t="inlineStr">
@@ -7898,7 +8802,21 @@
         </is>
       </c>
       <c r="H96" s="29" t="n"/>
-      <c r="I96" s="29" t="n"/>
+      <c r="I96" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J96" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K96" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: Smartship 주문 수집·검증 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="24">
       <c r="A97" s="29" t="n">
@@ -7926,7 +8844,7 @@
       </c>
       <c r="F97" s="30" t="inlineStr">
         <is>
-          <t>채널 연동 현황 화면</t>
+          <t>Smartship(OMS) 쇼핑몰 주문 연동 – 판매채널별 API 자동 수집 결과</t>
         </is>
       </c>
       <c r="G97" s="30" t="inlineStr">
@@ -7935,7 +8853,21 @@
         </is>
       </c>
       <c r="H97" s="29" t="n"/>
-      <c r="I97" s="29" t="n"/>
+      <c r="I97" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J97" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 채널 연동 현황 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="24">
       <c r="A98" s="29" t="n">
@@ -7963,7 +8895,7 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>입고·출고 화면</t>
+          <t>SW(WMS) 입고 확정 – 도착완료·입고완료 처리 및 재고 반영</t>
         </is>
       </c>
       <c r="G98" s="30" t="inlineStr">
@@ -7972,7 +8904,21 @@
         </is>
       </c>
       <c r="H98" s="29" t="n"/>
-      <c r="I98" s="29" t="n"/>
+      <c r="I98" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J98" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K98" s="29" t="inlineStr">
+        <is>
+          <t>10.14 Word 캡션 수정(이미지 속 캡션과 불일치였음)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="29" t="n">
@@ -8000,7 +8946,7 @@
       </c>
       <c r="F99" s="29" t="inlineStr">
         <is>
-          <t>TLPS 운송·인계 화면</t>
+          <t>TMS MAWB 상세 – 항공편 출항·입항 일정 및 Flight Confirm 관리</t>
         </is>
       </c>
       <c r="G99" s="30" t="inlineStr">
@@ -8009,7 +8955,21 @@
         </is>
       </c>
       <c r="H99" s="29" t="n"/>
-      <c r="I99" s="29" t="n"/>
+      <c r="I99" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J99" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" s="29" t="inlineStr">
+        <is>
+          <t>10.14 Word 캡션 수정(이미지 속 캡션과 불일치였음)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="29" t="n">
@@ -8037,7 +8997,7 @@
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>대시보드·셀 상세·실사·마감리포트 화면</t>
+          <t>SW(WMS) 재고실사 관리 – 실사 생성(대상 유형·기간 지정) 및 실사 목록</t>
         </is>
       </c>
       <c r="G100" s="30" t="inlineStr">
@@ -8046,7 +9006,21 @@
         </is>
       </c>
       <c r="H100" s="29" t="n"/>
-      <c r="I100" s="29" t="n"/>
+      <c r="I100" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J100" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" s="29" t="inlineStr">
+        <is>
+          <t>10.14 Word 캡션 수정(이미지 속 캡션과 불일치였음)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="29" t="n">
@@ -8074,7 +9048,7 @@
       </c>
       <c r="F101" s="30" t="inlineStr">
         <is>
-          <t>레이아웃관리·디바이스·작업자 추적 화면</t>
+          <t>SW(WMS) 창고 레이아웃 관리 – Zone·Block·설비(소터·DWS) 배치 등록</t>
         </is>
       </c>
       <c r="G101" s="30" t="inlineStr">
@@ -8083,7 +9057,21 @@
         </is>
       </c>
       <c r="H101" s="29" t="n"/>
-      <c r="I101" s="29" t="n"/>
+      <c r="I101" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J101" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K101" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 레이아웃관리·디바이스·작업자 추적 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="29" t="n">
@@ -8111,16 +9099,30 @@
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>풀필먼트 주문관리 대시보드</t>
+          <t>SW(WMS) 전체 대시보드 – 풀필먼트 공정별 처리 현황</t>
         </is>
       </c>
       <c r="G102" s="30" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>캡처</t>
         </is>
       </c>
       <c r="H102" s="29" t="n"/>
-      <c r="I102" s="29" t="n"/>
+      <c r="I102" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J102" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K102" s="29" t="inlineStr">
+        <is>
+          <t>유형 정정(사진→캡처) / 캡션 변경(기존: 풀필먼트 주문관리 대시보드) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="29" t="n">
@@ -8148,7 +9150,7 @@
       </c>
       <c r="F103" s="30" t="inlineStr">
         <is>
-          <t>반품 출고 관리 화면</t>
+          <t>SW(WMS) 고객반품 관리 – 반품 주문 등록·DPC 도착·검품·셀러 확인·최종 완료 단계 관리</t>
         </is>
       </c>
       <c r="G103" s="30" t="inlineStr">
@@ -8157,7 +9159,21 @@
         </is>
       </c>
       <c r="H103" s="29" t="n"/>
-      <c r="I103" s="29" t="n"/>
+      <c r="I103" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J103" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K103" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 반품 출고 관리 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="29" t="n">
@@ -8185,7 +9201,7 @@
       </c>
       <c r="F104" s="30" t="inlineStr">
         <is>
-          <t>오류화물 관리 화면</t>
+          <t>SW(WMS) 오류화물(펜딩) 관리 – SKU 미정의·재고 부족·통관 품목·경로 검증 등 유형별 보류 처리</t>
         </is>
       </c>
       <c r="G104" s="30" t="inlineStr">
@@ -8194,7 +9210,21 @@
         </is>
       </c>
       <c r="H104" s="29" t="n"/>
-      <c r="I104" s="29" t="n"/>
+      <c r="I104" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J104" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K104" s="29" t="inlineStr">
+        <is>
+          <t>캡션 변경(기존: 오류화물 관리 화면) / 01에 삽입 확인 → 수집 완료 처리</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="29" t="n">
@@ -8222,7 +9252,7 @@
       </c>
       <c r="F105" s="30" t="inlineStr">
         <is>
-          <t>소터 모니터링·슈트 설정 화면</t>
+          <t>SW(WMS) 소터 모니터링 – 투입구(DWS)별·시간대별 분류 처리 건수</t>
         </is>
       </c>
       <c r="G105" s="30" t="inlineStr">
@@ -8231,7 +9261,21 @@
         </is>
       </c>
       <c r="H105" s="29" t="n"/>
-      <c r="I105" s="29" t="n"/>
+      <c r="I105" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J105" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K105" s="29" t="inlineStr">
+        <is>
+          <t>10.14 Word 캡션 수정(이미지 속 캡션과 불일치였음)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="29" t="n">
@@ -8269,9 +9313,84 @@
       </c>
       <c r="H106" s="29" t="n"/>
       <c r="I106" s="29" t="n"/>
+      <c r="J106" s="29" t="n"/>
+      <c r="K106" s="29" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="48" t="inlineStr">
+        <is>
+          <t>집계 (2026.10.14, Ⅳ장 사진 2칸 별도)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="23" t="inlineStr">
+        <is>
+          <t>전체 증빙 칸</t>
+        </is>
+      </c>
+      <c r="C109" s="23">
+        <f>COUNTA(F4:F106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="23" t="inlineStr">
+        <is>
+          <t>수집 완료(O)</t>
+        </is>
+      </c>
+      <c r="C110" s="23">
+        <f>COUNTIF(I4:I106,"O")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="23" t="inlineStr">
+        <is>
+          <t>01 삽입(O)</t>
+        </is>
+      </c>
+      <c r="C111" s="23">
+        <f>COUNTIF(J4:J106,"O")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="23" t="inlineStr">
+        <is>
+          <t>미삽입 – 현장사진</t>
+        </is>
+      </c>
+      <c r="C112" s="23">
+        <f>COUNTIFS(G4:G106,"사진",J4:J106,"&lt;&gt;O")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="23" t="inlineStr">
+        <is>
+          <t>미삽입 – 시스템 캡처</t>
+        </is>
+      </c>
+      <c r="C113" s="23">
+        <f>COUNTIFS(G4:G106,"캡처",J4:J106,"&lt;&gt;O")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="23" t="inlineStr">
+        <is>
+          <t>미삽입 – 자료</t>
+        </is>
+      </c>
+      <c r="C114" s="23">
+        <f>COUNTIFS(G4:G106,"자료",J4:J106,"&lt;&gt;O")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I106"/>
+  <autoFilter ref="A3:K106"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8334,11 +9453,11 @@
         </is>
       </c>
       <c r="C4" s="29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="30" t="inlineStr">
         <is>
-          <t>도크레벨러 수량 확인 필요: 02 설계설명서는 1개소, Lay-out(2026.07.27)에는 2개소 표기.</t>
+          <t>도크레벨러 수량 확인 필요: 02 설계설명서는 1개소, Lay-out(2026.07.27)에는 2개소 표기. (10.06 조정으로 현재 2등급)</t>
         </is>
       </c>
     </row>
@@ -8458,7 +9577,7 @@
       </c>
       <c r="D10" s="30" t="inlineStr">
         <is>
-          <t>랙 내진 설계·시공 확인서 확보 시 유지, 미확보 시 4등급.</t>
+          <t>랙 내진 설계·시공 확인서 확보 시 유지, 미확보 시 4등급. (참고: 건축물대장상 건물 내진설계 적용·내진능력 VII-0.170g 확인 — 랙 내진은 별도 자료 필요)</t>
         </is>
       </c>
     </row>

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>44개 항목 × 수록 쪽·증명자료 매핑 완료. 사진 삽입 완료 후 쪽번호 재확인, 작성 메모 삭제</t>
+          <t>44개 항목 × 수록 쪽·증명자료 매핑 완료(쪽번호 10.14 재산정, 작성 메모 삭제). 남은 사진 삽입 후 쪽번호만 다시 확인</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
-          <t>10.14: 증명자료 칸 캡션 30곳을 01 최신 캡션으로 맞춤(103칸 모두 일치). 등급 44개 일치. 남은 것: 쪽번호 재확인(01 사진 추가로 쪽 밀림 예상), 작성 메모 삭제</t>
+          <t>10.14: 캡션 30곳을 01과 일치시킴, 수록 쪽 44개를 01 현재본(총 71쪽, PDF 변환 기준)으로 재산정, 작성 메모 삭제. 남은 사진 삽입 시 쪽이 밀리면 재확인</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D4" s="29" t="inlineStr">
         <is>
-          <t>p.7</t>
+          <t>p.7~8</t>
         </is>
       </c>
       <c r="E4" s="29" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
-          <t>p.7</t>
+          <t>p.7~8</t>
         </is>
       </c>
       <c r="E5" s="29" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>p.7</t>
+          <t>p.7~8</t>
         </is>
       </c>
       <c r="E6" s="29" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="D7" s="29" t="inlineStr">
         <is>
-          <t>p.8</t>
+          <t>p.9~10</t>
         </is>
       </c>
       <c r="E7" s="29" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>p.8</t>
+          <t>p.9~10</t>
         </is>
       </c>
       <c r="E8" s="29" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
-          <t>p.8</t>
+          <t>p.9~10</t>
         </is>
       </c>
       <c r="E9" s="29" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="D10" s="29" t="inlineStr">
         <is>
-          <t>p.8</t>
+          <t>p.9~10</t>
         </is>
       </c>
       <c r="E10" s="29" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>p.8</t>
+          <t>p.9~10</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="D12" s="29" t="inlineStr">
         <is>
-          <t>p.9</t>
+          <t>p.11~12</t>
         </is>
       </c>
       <c r="E12" s="29" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="D13" s="29" t="inlineStr">
         <is>
-          <t>p.9</t>
+          <t>p.11~12</t>
         </is>
       </c>
       <c r="E13" s="29" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="D14" s="29" t="inlineStr">
         <is>
-          <t>p.9</t>
+          <t>p.11~12</t>
         </is>
       </c>
       <c r="E14" s="29" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D15" s="29" t="inlineStr">
         <is>
-          <t>p.9</t>
+          <t>p.11~12</t>
         </is>
       </c>
       <c r="E15" s="29" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="D16" s="29" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>p.13~14</t>
         </is>
       </c>
       <c r="E16" s="29" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>p.13~14</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="D18" s="29" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>p.13~14</t>
         </is>
       </c>
       <c r="E18" s="29" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="D19" s="29" t="inlineStr">
         <is>
-          <t>p.11</t>
+          <t>p.15~17</t>
         </is>
       </c>
       <c r="E19" s="29" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="D20" s="29" t="inlineStr">
         <is>
-          <t>p.11</t>
+          <t>p.15~17</t>
         </is>
       </c>
       <c r="E20" s="29" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D21" s="29" t="inlineStr">
         <is>
-          <t>p.11</t>
+          <t>p.15~17</t>
         </is>
       </c>
       <c r="E21" s="29" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="D22" s="29" t="inlineStr">
         <is>
-          <t>p.11</t>
+          <t>p.15~17</t>
         </is>
       </c>
       <c r="E22" s="29" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="D23" s="29" t="inlineStr">
         <is>
-          <t>p.12</t>
+          <t>p.18~19</t>
         </is>
       </c>
       <c r="E23" s="29" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="D24" s="29" t="inlineStr">
         <is>
-          <t>p.12</t>
+          <t>p.18~19</t>
         </is>
       </c>
       <c r="E24" s="29" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="D25" s="29" t="inlineStr">
         <is>
-          <t>p.13</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E25" s="29" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
-          <t>p.13</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E26" s="29" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
-          <t>p.13</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E27" s="29" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="D28" s="29" t="inlineStr">
         <is>
-          <t>p.14</t>
+          <t>p.21</t>
         </is>
       </c>
       <c r="E28" s="29" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>p.14</t>
+          <t>p.21</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="D30" s="29" t="inlineStr">
         <is>
-          <t>p.15</t>
+          <t>p.22</t>
         </is>
       </c>
       <c r="E30" s="29" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="D31" s="29" t="inlineStr">
         <is>
-          <t>p.15</t>
+          <t>p.22</t>
         </is>
       </c>
       <c r="E31" s="29" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
-          <t>p.16</t>
+          <t>p.23~24</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
-          <t>p.16</t>
+          <t>p.23~24</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>p.17</t>
+          <t>p.25</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
-          <t>p.18</t>
+          <t>p.26</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="D36" s="29" t="inlineStr">
         <is>
-          <t>p.19</t>
+          <t>p.27~28</t>
         </is>
       </c>
       <c r="E36" s="29" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>p.19</t>
+          <t>p.27~28</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>p.19</t>
+          <t>p.27~28</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>p.29</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>p.21</t>
+          <t>p.30~31</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>p.21</t>
+          <t>p.30~31</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>p.21</t>
+          <t>p.30~31</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>p.22</t>
+          <t>p.32~33</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>p.22</t>
+          <t>p.32~33</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>p.23</t>
+          <t>p.34</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D46" s="29" t="inlineStr">
         <is>
-          <t>p.24</t>
+          <t>p.35~36</t>
         </is>
       </c>
       <c r="E46" s="29" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="D47" s="29" t="inlineStr">
         <is>
-          <t>p.24</t>
+          <t>p.35~36</t>
         </is>
       </c>
       <c r="E47" s="29" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="D48" s="29" t="inlineStr">
         <is>
-          <t>p.25</t>
+          <t>p.37</t>
         </is>
       </c>
       <c r="E48" s="29" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>p.25</t>
+          <t>p.37</t>
         </is>
       </c>
       <c r="E49" s="29" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="D50" s="29" t="inlineStr">
         <is>
-          <t>p.26</t>
+          <t>p.38</t>
         </is>
       </c>
       <c r="E50" s="29" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="D51" s="29" t="inlineStr">
         <is>
-          <t>p.26</t>
+          <t>p.38</t>
         </is>
       </c>
       <c r="E51" s="29" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="D52" s="29" t="inlineStr">
         <is>
-          <t>p.27</t>
+          <t>p.39</t>
         </is>
       </c>
       <c r="E52" s="29" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="D53" s="29" t="inlineStr">
         <is>
-          <t>p.27</t>
+          <t>p.39</t>
         </is>
       </c>
       <c r="E53" s="29" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="D54" s="29" t="inlineStr">
         <is>
-          <t>p.28</t>
+          <t>p.40</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
-          <t>p.28</t>
+          <t>p.40</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="D56" s="29" t="inlineStr">
         <is>
-          <t>p.29</t>
+          <t>p.41~42</t>
         </is>
       </c>
       <c r="E56" s="29" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="D57" s="29" t="inlineStr">
         <is>
-          <t>p.29</t>
+          <t>p.41~42</t>
         </is>
       </c>
       <c r="E57" s="29" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="D58" s="29" t="inlineStr">
         <is>
-          <t>p.29</t>
+          <t>p.41~42</t>
         </is>
       </c>
       <c r="E58" s="29" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="D59" s="29" t="inlineStr">
         <is>
-          <t>p.29</t>
+          <t>p.41~42</t>
         </is>
       </c>
       <c r="E59" s="29" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="D60" s="29" t="inlineStr">
         <is>
-          <t>p.30</t>
+          <t>p.43</t>
         </is>
       </c>
       <c r="E60" s="29" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="D61" s="29" t="inlineStr">
         <is>
-          <t>p.31</t>
+          <t>p.44</t>
         </is>
       </c>
       <c r="E61" s="29" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="D62" s="29" t="inlineStr">
         <is>
-          <t>p.31</t>
+          <t>p.44</t>
         </is>
       </c>
       <c r="E62" s="29" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="D63" s="29" t="inlineStr">
         <is>
-          <t>p.32</t>
+          <t>p.45~46</t>
         </is>
       </c>
       <c r="E63" s="29" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D64" s="29" t="inlineStr">
         <is>
-          <t>p.32</t>
+          <t>p.45~46</t>
         </is>
       </c>
       <c r="E64" s="29" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D65" s="29" t="inlineStr">
         <is>
-          <t>p.33</t>
+          <t>p.47</t>
         </is>
       </c>
       <c r="E65" s="29" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="D66" s="29" t="inlineStr">
         <is>
-          <t>p.33</t>
+          <t>p.47</t>
         </is>
       </c>
       <c r="E66" s="29" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="D67" s="29" t="inlineStr">
         <is>
-          <t>p.34</t>
+          <t>p.48~49</t>
         </is>
       </c>
       <c r="E67" s="29" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="D68" s="29" t="inlineStr">
         <is>
-          <t>p.34</t>
+          <t>p.48~49</t>
         </is>
       </c>
       <c r="E68" s="29" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>p.35</t>
+          <t>p.50~51</t>
         </is>
       </c>
       <c r="E69" s="29" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>p.35</t>
+          <t>p.50~51</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="D71" s="29" t="inlineStr">
         <is>
-          <t>p.36</t>
+          <t>p.52~53</t>
         </is>
       </c>
       <c r="E71" s="29" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="D72" s="29" t="inlineStr">
         <is>
-          <t>p.36</t>
+          <t>p.52~53</t>
         </is>
       </c>
       <c r="E72" s="29" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="D73" s="29" t="inlineStr">
         <is>
-          <t>p.36</t>
+          <t>p.52~53</t>
         </is>
       </c>
       <c r="E73" s="29" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="D74" s="29" t="inlineStr">
         <is>
-          <t>p.38</t>
+          <t>p.54</t>
         </is>
       </c>
       <c r="E74" s="29" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="D75" s="29" t="inlineStr">
         <is>
-          <t>p.38</t>
+          <t>p.54</t>
         </is>
       </c>
       <c r="E75" s="29" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="D76" s="29" t="inlineStr">
         <is>
-          <t>p.39</t>
+          <t>p.55</t>
         </is>
       </c>
       <c r="E76" s="29" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="D77" s="29" t="inlineStr">
         <is>
-          <t>p.39</t>
+          <t>p.55</t>
         </is>
       </c>
       <c r="E77" s="29" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="D78" s="29" t="inlineStr">
         <is>
-          <t>p.40</t>
+          <t>p.56</t>
         </is>
       </c>
       <c r="E78" s="29" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D79" s="29" t="inlineStr">
         <is>
-          <t>p.40</t>
+          <t>p.56</t>
         </is>
       </c>
       <c r="E79" s="29" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="D80" s="29" t="inlineStr">
         <is>
-          <t>p.40</t>
+          <t>p.56</t>
         </is>
       </c>
       <c r="E80" s="29" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="D81" s="29" t="inlineStr">
         <is>
-          <t>p.41</t>
+          <t>p.57~58</t>
         </is>
       </c>
       <c r="E81" s="29" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>p.41</t>
+          <t>p.57~58</t>
         </is>
       </c>
       <c r="E82" s="29" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="D83" s="29" t="inlineStr">
         <is>
-          <t>p.41</t>
+          <t>p.57~58</t>
         </is>
       </c>
       <c r="E83" s="29" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>p.41</t>
+          <t>p.57~58</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="D85" s="29" t="inlineStr">
         <is>
-          <t>p.41</t>
+          <t>p.57~58</t>
         </is>
       </c>
       <c r="E85" s="29" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>p.42</t>
+          <t>p.59</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="D87" s="29" t="inlineStr">
         <is>
-          <t>p.42</t>
+          <t>p.59</t>
         </is>
       </c>
       <c r="E87" s="29" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="D88" s="29" t="inlineStr">
         <is>
-          <t>p.43</t>
+          <t>p.60</t>
         </is>
       </c>
       <c r="E88" s="29" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>p.43</t>
+          <t>p.60</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="D90" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.61</t>
         </is>
       </c>
       <c r="E90" s="29" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D91" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.61</t>
         </is>
       </c>
       <c r="E91" s="29" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="D92" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.61</t>
         </is>
       </c>
       <c r="E92" s="29" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>p.45</t>
+          <t>p.62</t>
         </is>
       </c>
       <c r="E93" s="29" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="D94" s="29" t="inlineStr">
         <is>
-          <t>p.45</t>
+          <t>p.62</t>
         </is>
       </c>
       <c r="E94" s="29" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>p.45</t>
+          <t>p.62</t>
         </is>
       </c>
       <c r="E95" s="29" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D96" s="29" t="inlineStr">
         <is>
-          <t>p.46</t>
+          <t>p.63~64</t>
         </is>
       </c>
       <c r="E96" s="29" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="D97" s="29" t="inlineStr">
         <is>
-          <t>p.46</t>
+          <t>p.63~64</t>
         </is>
       </c>
       <c r="E97" s="29" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D98" s="29" t="inlineStr">
         <is>
-          <t>p.47</t>
+          <t>p.65~66</t>
         </is>
       </c>
       <c r="E98" s="29" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="D99" s="29" t="inlineStr">
         <is>
-          <t>p.47</t>
+          <t>p.65~66</t>
         </is>
       </c>
       <c r="E99" s="29" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="D100" s="29" t="inlineStr">
         <is>
-          <t>p.48</t>
+          <t>p.67</t>
         </is>
       </c>
       <c r="E100" s="29" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="D101" s="29" t="inlineStr">
         <is>
-          <t>p.49</t>
+          <t>p.68</t>
         </is>
       </c>
       <c r="E101" s="29" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="D102" s="29" t="inlineStr">
         <is>
-          <t>p.50</t>
+          <t>p.69~70</t>
         </is>
       </c>
       <c r="E102" s="29" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="D103" s="29" t="inlineStr">
         <is>
-          <t>p.50</t>
+          <t>p.69~70</t>
         </is>
       </c>
       <c r="E103" s="29" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D104" s="29" t="inlineStr">
         <is>
-          <t>p.50</t>
+          <t>p.69~70</t>
         </is>
       </c>
       <c r="E104" s="29" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="D105" s="29" t="inlineStr">
         <is>
-          <t>p.51</t>
+          <t>p.71</t>
         </is>
       </c>
       <c r="E105" s="29" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="D106" s="29" t="inlineStr">
         <is>
-          <t>p.51</t>
+          <t>p.71</t>
         </is>
       </c>
       <c r="E106" s="29" t="inlineStr">

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -124,7 +124,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -194,6 +194,11 @@
         <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -229,7 +234,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -374,6 +379,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -734,7 +742,7 @@
     <row r="1" ht="21" customHeight="1" s="24">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>스마트물류센터 인증 제출서류 진행현황 (영종센터, 기준 2026.10.14 · 「작성 서류 - yun」 폴더 기준)</t>
+          <t>스마트물류센터 인증 제출서류 진행현황 (영종센터, 기준 2026.10.15 · 「작성 서류 - yun」 폴더 기준)</t>
         </is>
       </c>
     </row>
@@ -815,7 +823,7 @@
       </c>
       <c r="F4" s="29" t="inlineStr">
         <is>
-          <t>HWP 서식 미기재. 「신청서_기재안」 내용을 한글에서 입력, 대표자 승인·날인</t>
+          <t>기재안 완성(실무담당자 제외). HWP 서식에 옮겨 입력, 대표자 승인·날인. 실무담당자·전화·팩스·이메일 확정 후 기재</t>
         </is>
       </c>
       <c r="G4" s="30" t="inlineStr">
@@ -825,7 +833,7 @@
       </c>
       <c r="H4" s="30" t="inlineStr">
         <is>
-          <t>건축물대장으로 기재값 확정 가능: 착공 2019.07.08, 사용승인 2021.01.22, 연면적 186,095.3㎡, 주용도 창고시설(지상 6층). 단, 본점이 2026.06.01 「서울 강서구 마곡중앙8로7길 57, 비동 905~907호」로 이전(등기 2026.06.08) → 기재안 주소(강서로 463 새싹타워) 수정 필요. 실무담당자 칸 공란</t>
+          <t>10.15: 본점 주소를 사업자등록증 표기(마곡중앙8로7길 57, B동 9층 905~907호, 마곡 아이파크 디어반)로, 대표자 근거를 "각자대표"로 반영. 착공·사용승인·연면적·용도·건축물명 반영, 첨부 대응표 갱신. 실무담당자 칸은 공란 유지</t>
         </is>
       </c>
     </row>
@@ -857,7 +865,7 @@
       </c>
       <c r="F5" s="29" t="inlineStr">
         <is>
-          <t>44개 세부항목 서술 완료(789.0점·3등급). 남은 사진·증빙 48칸 + Ⅳ장 2칸(현장사진 29·자료 21) 촬영·확보 후 삽입. Ⅲ장 종업원 수·최근 3년 매출액·2023~2025 물동량·인증업무 담당자 입력, 작성 메모 14곳 확인 후 삭제</t>
+          <t>44개 세부항목 서술 완료(789.0점·3등급). 남은 사진·증빙 46칸(현장사진 29·자료 17) 확보 후 삽입, 1.1.5 [사진 2] 이미지 교체. Ⅲ장 종업원 수·매출액·인증업무 담당자 입력(물동량은 2025.6~12·2026.1~9 입력 완료), 작성 메모 14곳 삭제</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -867,7 +875,7 @@
       </c>
       <c r="H5" s="29" t="inlineStr">
         <is>
-          <t>10.14 수정본 확인: 총점 789.0점(3등급, ⑤와 일치). 사진·캡처 105칸 중 55칸 삽입. 이미지 속 캡션과 어긋난 Word 캡션 4곳 수정(2.3.1-2 사진1·2, 2.3.1-3, 2.3.2 사진1). 1.1.5 [사진 2]는 [사진 1]과 같은 이미지가 들어가 있어 교체 필요. 서약서·교육 수료증 PDF가 yun 폴더에 있어 바로 삽입 가능. 작성 메모 14곳·Ⅲ장 공란 남음</t>
+          <t>10.15: 지게차 서약서(8매)·2025 안전보건교육 기관수료증을 4칸에 삽입 → 105칸 중 59칸 삽입. 총 74쪽(PDF 변환 기준) / 10.15: Ⅲ장 물동량에 2025년 6~12월 출고 2,184,759박스 추가(6월부터 집계, 단위 박스로 통일). 매출액은 추후 수령 / 10.15: 2.1.1 도크 ⑦⑧·바닥 ⑥ 실내 접안 근거로 V 처리(3등급 유지, 바닥 ⑧⑨ 대기)</t>
         </is>
       </c>
     </row>
@@ -941,7 +949,7 @@
       </c>
       <c r="F7" s="29" t="inlineStr">
         <is>
-          <t>"해당 없음"으로 작성. 건축물대장 변경 이력 확인 → 해당 없으면 미제출 가능</t>
+          <t>"해당 없음" 유지 여부 결정(건축물대장 2022.08.18 3층 방화구획 대수선·2024.03.12 증축 이력 확인), 작성일·직인</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -951,7 +959,7 @@
       </c>
       <c r="H7" s="29" t="inlineStr">
         <is>
-          <t>건축물대장 확보: 사용승인일 2021.01.22 기재 가능. 변동사항에 2022.08.18 3층 방화구획 관련 대수선, 2024.03.12 증축(1층 전기실 57.48㎡) 이력 있음 → "해당 없음" 판단 재검토 필요</t>
+          <t>10.15: 사용승인일 2021.01.22 기재, 작성 메모에 건축물대장 변동 이력 추가</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1043,7 @@
       </c>
       <c r="H9" s="29" t="inlineStr">
         <is>
-          <t>yun 폴더 「3_운영매뉴얼_영종센터」(v2.0, 10.02 저장)도 작성일 2026-07-13, 상호 "Tracx Logis", KPI 목표 "예시" 표기 남음</t>
+          <t>10.15 yun 「3_운영매뉴얼」: 상호→트랙스로지스코리아(주)·작성일 2026-09-30·KPI "목표(예시)"→"목표" 수정 완료. 실제 실적 수치는 여전히 필요</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1127,7 @@
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
-          <t>yun 폴더 「1_물류정보시스템_기술서_영종센터」(v2.0): 작성일 2026-07-13, 상호 "Tracx Logis", "예시" 9곳, 1.3에 "한국통합물류협회" 표기 남음</t>
+          <t>10.15 yun 「1_물류정보시스템_기술서」: 상호·작성일(2026-09-30)·인증기관명(한국교통연구원) 수정, 목표 표에서 "예시" 제거. [○○] 공란 18곳(면적·물동량·기술스택 등)·개요도 [그림 3-1] 남음</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1169,7 @@
       </c>
       <c r="H12" s="29" t="inlineStr">
         <is>
-          <t>yun 폴더 「2_업무-시스템_연계기술서_영종센터」(v2.0): 작성일 2026-07-13, 상호 "Tracx Logis", 코드·SLA "예시" 6곳 남음</t>
+          <t>10.15 yun 「2_업무-시스템_연계기술서」: 상호·작성일(2026-09-30)·SLA "목표" 표기 수정 완료. 코드 표의 "예시"는 실제 예시라 유지. 데이터 흐름 도식 [그림 2-1] 남음</t>
         </is>
       </c>
     </row>
@@ -1267,17 +1275,17 @@
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>발급·수집 필요</t>
+          <t>작성 서류 - yun/트랙스로지스코리아 사업자등록증_20260611.pdf</t>
+        </is>
+      </c>
+      <c r="E15" s="50" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F15" s="30" t="inlineStr">
         <is>
-          <t>사업자등록증 사본(또는 사업자등록증명) 확보</t>
+          <t>확보 완료(2026.06.11 발급). 등록번호 109-86-19926, 각자대표 김양훈·노현석, 사업장 마곡 아이파크 디어반</t>
         </is>
       </c>
       <c r="G15" s="29" t="inlineStr">
@@ -1287,7 +1295,7 @@
       </c>
       <c r="H15" s="29" t="inlineStr">
         <is>
-          <t>yun 폴더에 해당 파일 없음</t>
+          <t>10.15: yun 폴더에서 확인. 신청서 기재안 주소·대표 표기를 사업자등록증 기준으로 맞춤</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1453,7 @@
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>44개 항목 × 수록 쪽·증명자료 매핑 완료(쪽번호 10.14 재산정, 작성 메모 삭제). 남은 사진 삽입 후 쪽번호만 다시 확인</t>
+          <t>44개 항목 × 수록 쪽·증명자료 매핑 완료, 작성 메모 삭제. 남은 사진 삽입 후 쪽번호만 다시 확인</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
@@ -1455,7 +1463,7 @@
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
-          <t>10.14: 캡션 30곳을 01과 일치시킴, 수록 쪽 44개를 01 현재본(총 71쪽, PDF 변환 기준)으로 재산정, 작성 메모 삭제. 남은 사진 삽입 시 쪽이 밀리면 재확인</t>
+          <t>10.15: 01 사진 추가에 맞춰 수록 쪽 재산정(총 74쪽), 캡션 103칸 01과 일치</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1906,12 @@
       </c>
       <c r="E5" s="30" t="inlineStr">
         <is>
-          <t>등기상 대표 방식 확인 → 신청서·확인서 표기 통일</t>
+          <t>사업자등록증(2026.06.11): 김양훈·노현석 "각자대표" 확인 → 신청서·④ 확인서에 2인 병기(각자대표)로 통일</t>
         </is>
       </c>
       <c r="F5" s="38" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2476,7 @@
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
-          <t>신청서·소개자료 주소를 등기 기준으로 수정</t>
+          <t>① 신청서 기재안 수정 완료(10.15, 사업자등록증 표기 기준). 소개자료 등 나머지 문서 주소 확인</t>
         </is>
       </c>
       <c r="F24" s="39" t="inlineStr">
@@ -5654,7 +5662,7 @@
       </c>
       <c r="D25" s="29" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>p.20~21</t>
         </is>
       </c>
       <c r="E25" s="29" t="inlineStr">
@@ -5693,7 +5701,7 @@
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>p.20~21</t>
         </is>
       </c>
       <c r="E26" s="29" t="inlineStr">
@@ -5732,7 +5740,7 @@
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>p.20~21</t>
         </is>
       </c>
       <c r="E27" s="29" t="inlineStr">
@@ -5756,10 +5764,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="J27" s="29" t="n"/>
+      <c r="J27" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="K27" s="29" t="inlineStr">
         <is>
-          <t>수집 완료, 01 미삽입</t>
+          <t>10.15 01에 삽입(서약서 8매 모음 / 기관수료증 1~2쪽)</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5791,7 @@
       </c>
       <c r="D28" s="29" t="inlineStr">
         <is>
-          <t>p.21</t>
+          <t>p.22</t>
         </is>
       </c>
       <c r="E28" s="29" t="inlineStr">
@@ -5826,7 +5838,7 @@
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>p.21</t>
+          <t>p.22</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
@@ -5865,7 +5877,7 @@
       </c>
       <c r="D30" s="29" t="inlineStr">
         <is>
-          <t>p.22</t>
+          <t>p.23</t>
         </is>
       </c>
       <c r="E30" s="29" t="inlineStr">
@@ -5904,7 +5916,7 @@
       </c>
       <c r="D31" s="29" t="inlineStr">
         <is>
-          <t>p.22</t>
+          <t>p.23</t>
         </is>
       </c>
       <c r="E31" s="29" t="inlineStr">
@@ -5951,7 +5963,7 @@
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
-          <t>p.23~24</t>
+          <t>p.24~25</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
@@ -6002,7 +6014,7 @@
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
-          <t>p.23~24</t>
+          <t>p.24~25</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
@@ -6053,7 +6065,7 @@
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>p.25</t>
+          <t>p.26</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
@@ -6104,7 +6116,7 @@
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
-          <t>p.26</t>
+          <t>p.27</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
@@ -6155,7 +6167,7 @@
       </c>
       <c r="D36" s="29" t="inlineStr">
         <is>
-          <t>p.27~28</t>
+          <t>p.28~29</t>
         </is>
       </c>
       <c r="E36" s="29" t="inlineStr">
@@ -6206,7 +6218,7 @@
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>p.27~28</t>
+          <t>p.28~29</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
@@ -6245,7 +6257,7 @@
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>p.27~28</t>
+          <t>p.28~29</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
@@ -6292,7 +6304,7 @@
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>p.29</t>
+          <t>p.30</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
@@ -6343,7 +6355,7 @@
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>p.30~31</t>
+          <t>p.31~32</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
@@ -6394,7 +6406,7 @@
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>p.30~31</t>
+          <t>p.31~32</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
@@ -6445,7 +6457,7 @@
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>p.30~31</t>
+          <t>p.31~32</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
@@ -6492,7 +6504,7 @@
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>p.32~33</t>
+          <t>p.33~34</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
@@ -6543,7 +6555,7 @@
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>p.32~33</t>
+          <t>p.33~34</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
@@ -6582,7 +6594,7 @@
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>p.34</t>
+          <t>p.35</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
@@ -6629,7 +6641,7 @@
       </c>
       <c r="D46" s="29" t="inlineStr">
         <is>
-          <t>p.35~36</t>
+          <t>p.36~37</t>
         </is>
       </c>
       <c r="E46" s="29" t="inlineStr">
@@ -6668,7 +6680,7 @@
       </c>
       <c r="D47" s="29" t="inlineStr">
         <is>
-          <t>p.35~36</t>
+          <t>p.36~37</t>
         </is>
       </c>
       <c r="E47" s="29" t="inlineStr">
@@ -6719,7 +6731,7 @@
       </c>
       <c r="D48" s="29" t="inlineStr">
         <is>
-          <t>p.37</t>
+          <t>p.38</t>
         </is>
       </c>
       <c r="E48" s="29" t="inlineStr">
@@ -6770,7 +6782,7 @@
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>p.37</t>
+          <t>p.38</t>
         </is>
       </c>
       <c r="E49" s="29" t="inlineStr">
@@ -6809,7 +6821,7 @@
       </c>
       <c r="D50" s="29" t="inlineStr">
         <is>
-          <t>p.38</t>
+          <t>p.39</t>
         </is>
       </c>
       <c r="E50" s="29" t="inlineStr">
@@ -6848,7 +6860,7 @@
       </c>
       <c r="D51" s="29" t="inlineStr">
         <is>
-          <t>p.38</t>
+          <t>p.39</t>
         </is>
       </c>
       <c r="E51" s="29" t="inlineStr">
@@ -6899,7 +6911,7 @@
       </c>
       <c r="D52" s="29" t="inlineStr">
         <is>
-          <t>p.39</t>
+          <t>p.40</t>
         </is>
       </c>
       <c r="E52" s="29" t="inlineStr">
@@ -6950,7 +6962,7 @@
       </c>
       <c r="D53" s="29" t="inlineStr">
         <is>
-          <t>p.39</t>
+          <t>p.40</t>
         </is>
       </c>
       <c r="E53" s="29" t="inlineStr">
@@ -6989,7 +7001,7 @@
       </c>
       <c r="D54" s="29" t="inlineStr">
         <is>
-          <t>p.40</t>
+          <t>p.41</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
@@ -7028,7 +7040,7 @@
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
-          <t>p.40</t>
+          <t>p.41</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
@@ -7075,7 +7087,7 @@
       </c>
       <c r="D56" s="29" t="inlineStr">
         <is>
-          <t>p.41~42</t>
+          <t>p.42~43</t>
         </is>
       </c>
       <c r="E56" s="29" t="inlineStr">
@@ -7126,7 +7138,7 @@
       </c>
       <c r="D57" s="29" t="inlineStr">
         <is>
-          <t>p.41~42</t>
+          <t>p.42~43</t>
         </is>
       </c>
       <c r="E57" s="29" t="inlineStr">
@@ -7177,7 +7189,7 @@
       </c>
       <c r="D58" s="29" t="inlineStr">
         <is>
-          <t>p.41~42</t>
+          <t>p.42~43</t>
         </is>
       </c>
       <c r="E58" s="29" t="inlineStr">
@@ -7216,7 +7228,7 @@
       </c>
       <c r="D59" s="29" t="inlineStr">
         <is>
-          <t>p.41~42</t>
+          <t>p.42~43</t>
         </is>
       </c>
       <c r="E59" s="29" t="inlineStr">
@@ -7255,7 +7267,7 @@
       </c>
       <c r="D60" s="29" t="inlineStr">
         <is>
-          <t>p.43</t>
+          <t>p.44</t>
         </is>
       </c>
       <c r="E60" s="29" t="inlineStr">
@@ -7294,7 +7306,7 @@
       </c>
       <c r="D61" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.45</t>
         </is>
       </c>
       <c r="E61" s="29" t="inlineStr">
@@ -7333,7 +7345,7 @@
       </c>
       <c r="D62" s="29" t="inlineStr">
         <is>
-          <t>p.44</t>
+          <t>p.45</t>
         </is>
       </c>
       <c r="E62" s="29" t="inlineStr">
@@ -7384,7 +7396,7 @@
       </c>
       <c r="D63" s="29" t="inlineStr">
         <is>
-          <t>p.45~46</t>
+          <t>p.46~47</t>
         </is>
       </c>
       <c r="E63" s="29" t="inlineStr">
@@ -7423,7 +7435,7 @@
       </c>
       <c r="D64" s="29" t="inlineStr">
         <is>
-          <t>p.45~46</t>
+          <t>p.46~47</t>
         </is>
       </c>
       <c r="E64" s="29" t="inlineStr">
@@ -7474,7 +7486,7 @@
       </c>
       <c r="D65" s="29" t="inlineStr">
         <is>
-          <t>p.47</t>
+          <t>p.48</t>
         </is>
       </c>
       <c r="E65" s="29" t="inlineStr">
@@ -7513,7 +7525,7 @@
       </c>
       <c r="D66" s="29" t="inlineStr">
         <is>
-          <t>p.47</t>
+          <t>p.48</t>
         </is>
       </c>
       <c r="E66" s="29" t="inlineStr">
@@ -7564,7 +7576,7 @@
       </c>
       <c r="D67" s="29" t="inlineStr">
         <is>
-          <t>p.48~49</t>
+          <t>p.49~50</t>
         </is>
       </c>
       <c r="E67" s="29" t="inlineStr">
@@ -7603,7 +7615,7 @@
       </c>
       <c r="D68" s="29" t="inlineStr">
         <is>
-          <t>p.48~49</t>
+          <t>p.49~50</t>
         </is>
       </c>
       <c r="E68" s="29" t="inlineStr">
@@ -7654,7 +7666,7 @@
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>p.50~51</t>
+          <t>p.51~52</t>
         </is>
       </c>
       <c r="E69" s="29" t="inlineStr">
@@ -7705,7 +7717,7 @@
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>p.50~51</t>
+          <t>p.51~52</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
@@ -7756,7 +7768,7 @@
       </c>
       <c r="D71" s="29" t="inlineStr">
         <is>
-          <t>p.52~53</t>
+          <t>p.53~54</t>
         </is>
       </c>
       <c r="E71" s="29" t="inlineStr">
@@ -7777,7 +7789,11 @@
       <c r="H71" s="29" t="n"/>
       <c r="I71" s="29" t="n"/>
       <c r="J71" s="29" t="n"/>
-      <c r="K71" s="29" t="n"/>
+      <c r="K71" s="29" t="inlineStr">
+        <is>
+          <t>실내 접안(트럭이 건물 안에 접안 + 천장) 보이게 촬영 — 차양·쉘터 V 판단 근거</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="24">
       <c r="A72" s="29" t="n">
@@ -7795,7 +7811,7 @@
       </c>
       <c r="D72" s="29" t="inlineStr">
         <is>
-          <t>p.52~53</t>
+          <t>p.53~54</t>
         </is>
       </c>
       <c r="E72" s="29" t="inlineStr">
@@ -7834,7 +7850,7 @@
       </c>
       <c r="D73" s="29" t="inlineStr">
         <is>
-          <t>p.52~53</t>
+          <t>p.53~54</t>
         </is>
       </c>
       <c r="E73" s="29" t="inlineStr">
@@ -7873,7 +7889,7 @@
       </c>
       <c r="D74" s="29" t="inlineStr">
         <is>
-          <t>p.54</t>
+          <t>p.55</t>
         </is>
       </c>
       <c r="E74" s="29" t="inlineStr">
@@ -7916,7 +7932,7 @@
       </c>
       <c r="D75" s="29" t="inlineStr">
         <is>
-          <t>p.54</t>
+          <t>p.55</t>
         </is>
       </c>
       <c r="E75" s="29" t="inlineStr">
@@ -7955,7 +7971,7 @@
       </c>
       <c r="D76" s="29" t="inlineStr">
         <is>
-          <t>p.55</t>
+          <t>p.56</t>
         </is>
       </c>
       <c r="E76" s="29" t="inlineStr">
@@ -7994,7 +8010,7 @@
       </c>
       <c r="D77" s="29" t="inlineStr">
         <is>
-          <t>p.55</t>
+          <t>p.56</t>
         </is>
       </c>
       <c r="E77" s="29" t="inlineStr">
@@ -8033,7 +8049,7 @@
       </c>
       <c r="D78" s="29" t="inlineStr">
         <is>
-          <t>p.56</t>
+          <t>p.57</t>
         </is>
       </c>
       <c r="E78" s="29" t="inlineStr">
@@ -8072,7 +8088,7 @@
       </c>
       <c r="D79" s="29" t="inlineStr">
         <is>
-          <t>p.56</t>
+          <t>p.57</t>
         </is>
       </c>
       <c r="E79" s="29" t="inlineStr">
@@ -8111,7 +8127,7 @@
       </c>
       <c r="D80" s="29" t="inlineStr">
         <is>
-          <t>p.56</t>
+          <t>p.57</t>
         </is>
       </c>
       <c r="E80" s="29" t="inlineStr">
@@ -8150,7 +8166,7 @@
       </c>
       <c r="D81" s="29" t="inlineStr">
         <is>
-          <t>p.57~58</t>
+          <t>p.58~60</t>
         </is>
       </c>
       <c r="E81" s="29" t="inlineStr">
@@ -8189,7 +8205,7 @@
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>p.57~58</t>
+          <t>p.58~60</t>
         </is>
       </c>
       <c r="E82" s="29" t="inlineStr">
@@ -8228,7 +8244,7 @@
       </c>
       <c r="D83" s="29" t="inlineStr">
         <is>
-          <t>p.57~58</t>
+          <t>p.58~60</t>
         </is>
       </c>
       <c r="E83" s="29" t="inlineStr">
@@ -8252,10 +8268,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="J83" s="29" t="n"/>
+      <c r="J83" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="K83" s="29" t="inlineStr">
         <is>
-          <t>수집 완료, 01 미삽입</t>
+          <t>10.15 01에 삽입(서약서 8매 모음 / 기관수료증 1~2쪽)</t>
         </is>
       </c>
     </row>
@@ -8275,7 +8295,7 @@
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>p.57~58</t>
+          <t>p.58~60</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
@@ -8326,7 +8346,7 @@
       </c>
       <c r="D85" s="29" t="inlineStr">
         <is>
-          <t>p.57~58</t>
+          <t>p.58~60</t>
         </is>
       </c>
       <c r="E85" s="29" t="inlineStr">
@@ -8350,10 +8370,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="J85" s="29" t="n"/>
+      <c r="J85" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="K85" s="29" t="inlineStr">
         <is>
-          <t>수집 완료, 01 미삽입</t>
+          <t>10.15 01에 삽입(서약서 8매 모음 / 기관수료증 1~2쪽)</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8397,7 @@
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>p.59</t>
+          <t>p.61</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
@@ -8412,7 +8436,7 @@
       </c>
       <c r="D87" s="29" t="inlineStr">
         <is>
-          <t>p.59</t>
+          <t>p.61</t>
         </is>
       </c>
       <c r="E87" s="29" t="inlineStr">
@@ -8451,7 +8475,7 @@
       </c>
       <c r="D88" s="29" t="inlineStr">
         <is>
-          <t>p.60</t>
+          <t>p.62</t>
         </is>
       </c>
       <c r="E88" s="29" t="inlineStr">
@@ -8502,7 +8526,7 @@
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>p.60</t>
+          <t>p.62</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
@@ -8541,7 +8565,7 @@
       </c>
       <c r="D90" s="29" t="inlineStr">
         <is>
-          <t>p.61</t>
+          <t>p.63~64</t>
         </is>
       </c>
       <c r="E90" s="29" t="inlineStr">
@@ -8580,7 +8604,7 @@
       </c>
       <c r="D91" s="29" t="inlineStr">
         <is>
-          <t>p.61</t>
+          <t>p.63~64</t>
         </is>
       </c>
       <c r="E91" s="29" t="inlineStr">
@@ -8619,7 +8643,7 @@
       </c>
       <c r="D92" s="29" t="inlineStr">
         <is>
-          <t>p.61</t>
+          <t>p.63~64</t>
         </is>
       </c>
       <c r="E92" s="29" t="inlineStr">
@@ -8643,10 +8667,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="J92" s="29" t="n"/>
+      <c r="J92" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="K92" s="29" t="inlineStr">
         <is>
-          <t>수집 완료, 01 미삽입</t>
+          <t>10.15 01에 삽입(서약서 8매 모음 / 기관수료증 1~2쪽)</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8694,7 @@
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>p.62</t>
+          <t>p.65</t>
         </is>
       </c>
       <c r="E93" s="29" t="inlineStr">
@@ -8705,7 +8733,7 @@
       </c>
       <c r="D94" s="29" t="inlineStr">
         <is>
-          <t>p.62</t>
+          <t>p.65</t>
         </is>
       </c>
       <c r="E94" s="29" t="inlineStr">
@@ -8744,7 +8772,7 @@
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>p.62</t>
+          <t>p.65</t>
         </is>
       </c>
       <c r="E95" s="29" t="inlineStr">
@@ -8783,7 +8811,7 @@
       </c>
       <c r="D96" s="29" t="inlineStr">
         <is>
-          <t>p.63~64</t>
+          <t>p.66~67</t>
         </is>
       </c>
       <c r="E96" s="29" t="inlineStr">
@@ -8834,7 +8862,7 @@
       </c>
       <c r="D97" s="29" t="inlineStr">
         <is>
-          <t>p.63~64</t>
+          <t>p.66~67</t>
         </is>
       </c>
       <c r="E97" s="29" t="inlineStr">
@@ -8885,7 +8913,7 @@
       </c>
       <c r="D98" s="29" t="inlineStr">
         <is>
-          <t>p.65~66</t>
+          <t>p.68~69</t>
         </is>
       </c>
       <c r="E98" s="29" t="inlineStr">
@@ -8936,7 +8964,7 @@
       </c>
       <c r="D99" s="29" t="inlineStr">
         <is>
-          <t>p.65~66</t>
+          <t>p.68~69</t>
         </is>
       </c>
       <c r="E99" s="29" t="inlineStr">
@@ -8987,7 +9015,7 @@
       </c>
       <c r="D100" s="29" t="inlineStr">
         <is>
-          <t>p.67</t>
+          <t>p.70</t>
         </is>
       </c>
       <c r="E100" s="29" t="inlineStr">
@@ -9038,7 +9066,7 @@
       </c>
       <c r="D101" s="29" t="inlineStr">
         <is>
-          <t>p.68</t>
+          <t>p.71</t>
         </is>
       </c>
       <c r="E101" s="29" t="inlineStr">
@@ -9089,7 +9117,7 @@
       </c>
       <c r="D102" s="29" t="inlineStr">
         <is>
-          <t>p.69~70</t>
+          <t>p.72~73</t>
         </is>
       </c>
       <c r="E102" s="29" t="inlineStr">
@@ -9140,7 +9168,7 @@
       </c>
       <c r="D103" s="29" t="inlineStr">
         <is>
-          <t>p.69~70</t>
+          <t>p.72~73</t>
         </is>
       </c>
       <c r="E103" s="29" t="inlineStr">
@@ -9191,7 +9219,7 @@
       </c>
       <c r="D104" s="29" t="inlineStr">
         <is>
-          <t>p.69~70</t>
+          <t>p.72~73</t>
         </is>
       </c>
       <c r="E104" s="29" t="inlineStr">
@@ -9242,7 +9270,7 @@
       </c>
       <c r="D105" s="29" t="inlineStr">
         <is>
-          <t>p.71</t>
+          <t>p.74</t>
         </is>
       </c>
       <c r="E105" s="29" t="inlineStr">
@@ -9293,7 +9321,7 @@
       </c>
       <c r="D106" s="29" t="inlineStr">
         <is>
-          <t>p.71</t>
+          <t>p.74</t>
         </is>
       </c>
       <c r="E106" s="29" t="inlineStr">
@@ -9403,7 +9431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="23" min="1" max="1"/>
@@ -9517,7 +9545,7 @@
       </c>
       <c r="D7" s="29" t="inlineStr">
         <is>
-          <t>"확인" 항목은 현장·임대인(아레나스) 제원으로 적용 여부를 확정한 뒤 등급 재계산.</t>
+          <t>도크 10개 모두 적용(10.15, 실내 접안 구조로 차양·날씨 대응 확보). 바닥 ⑥ 적용. 남은 "확인": 바닥 ⑧ AGV·⑨ 자동창고 평탄도 → 임대인(아레나스) 제원 확보 시 2등급(+2.0점), 미적용이면 4등급.</t>
         </is>
       </c>
     </row>

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -875,7 +875,7 @@
       </c>
       <c r="H5" s="29" t="inlineStr">
         <is>
-          <t>10.15: 지게차 서약서(8매)·2025 안전보건교육 기관수료증을 4칸에 삽입 → 105칸 중 59칸 삽입. 총 74쪽(PDF 변환 기준) / 10.15: Ⅲ장 물동량에 2025년 6~12월 출고 2,184,759박스 추가(6월부터 집계, 단위 박스로 통일). 매출액은 추후 수령 / 10.15: 2.1.1 도크 ⑦⑧·바닥 ⑥ 실내 접안 근거로 V 처리(3등급 유지, 바닥 ⑧⑨ 대기)</t>
+          <t>10.15: 지게차 서약서(8매)·2025 안전보건교육 기관수료증을 4칸에 삽입 → 105칸 중 59칸 삽입. 총 74쪽(PDF 변환 기준) / 10.15: Ⅲ장 물동량에 2025년 6~12월 출고 2,184,759박스 추가(6월부터 집계, 단위 박스로 통일). 매출액은 추후 수령 / 10.15: 2.1.1 도크 ⑦⑧·바닥 ⑥ 실내 접안 근거로 V 처리(3등급 유지, 바닥 ⑧⑨ 대기) / 10.15: 기준일자 2026.10.31로 변경</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="23" min="1" max="1"/>
@@ -2286,22 +2286,22 @@
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
-          <t>03·⑦·⑧·④: 공란 / 06 제정일: "2026. . ." / yun 1~3 기술서·매뉴얼: 2026-07-13</t>
+          <t>④·⑦·⑧: 파일 없음(작성 시 2026.10.31로 기재)</t>
         </is>
       </c>
       <c r="D18" s="29" t="inlineStr">
         <is>
-          <t>01·02·06 기준일자: 2026.09.30 / 04·05: 2026년 8월 10일</t>
+          <t>10.15: 기준일자·작성일 2026.10.31로 통일 — yun 01·02·03(작성일)·06(기준일·제정일)·⑥·1~4, 제출서류_10종 01~08 표지 작성일 반영 완료</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>모든 서류 기준일자 통일(공고문: 기준일자 제시 필수)</t>
+          <t>④·⑦·⑧ 작성 시 2026.10.31 기재</t>
         </is>
       </c>
       <c r="F18" s="38" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음</t>
         </is>
       </c>
     </row>
@@ -2575,6 +2575,18 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
   </sheetData>
   <autoFilter ref="A3:F27"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -9431,7 +9443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="23" min="1" max="1"/>

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F11" s="30" t="inlineStr">
         <is>
-          <t>작성일 공란, 아키텍처 개요도 미삽입, 연동 채널 목록 확정, "▷ 필요한 내용"·[작성 양식] 안내문 삭제, 화면 캡처 삽입</t>
+          <t>[확인 필요] 8곳 입력(IT·현장 확인): 일평균 주문 건수, 국내:해외 비중, 서버 프레임워크·DB 종류, DAS 스테이션 수, 3D 소터 처리량, PTL 구역 수, 소터 슈트 수</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
-          <t>10.15 yun 「1_물류정보시스템_기술서」: 상호·작성일(2026-09-30)·인증기관명(한국교통연구원) 수정, 목표 표에서 "예시" 제거. [○○] 공란 18곳(면적·물동량·기술스택 등)·개요도 [그림 3-1] 남음</t>
+          <t>10.15 yun 「1_물류정보시스템_기술서」 보완: 센터 정보·물동량(일평균 약 13,600박스, 재고형:셀러 발송분 36:64)·기술 스택·설비 수량(PDA 35대, DWS 투입구 6개)·자동화율(평균 52%) 입력, 채널 목록 기재, 구성도 [그림 3-1] 새로 작성(기존 "Tracx Logis" 표기 그림 교체), 시스템 화면 4장 추가. [확인 필요] 8곳 남음: 일평균 주문 건수, 국내:해외 비중, 서버 프레임워크·DB, DAS 스테이션·3D 소터 처리량·PTL 구역·슈트 수</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>작성일 공란, 데이터 흐름 도식 추가, "▷ 필요한 내용" 안내문 삭제</t>
+          <t>내용 검토 후 제출본 확정(남은 공란 없음)</t>
         </is>
       </c>
       <c r="G12" s="29" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H12" s="29" t="inlineStr">
         <is>
-          <t>10.15 yun 「2_업무-시스템_연계기술서」: 상호·작성일(2026-09-30)·SLA "목표" 표기 수정 완료. 코드 표의 "예시"는 실제 예시라 유지. 데이터 흐름 도식 [그림 2-1] 남음</t>
+          <t>10.15 yun 「2_업무-시스템_연계기술서」: 연계 흐름도 [그림 2-1] 새로 작성(재고 입고·WMS 출고·셀러 발송분·공통 후단 4개 흐름). 상호·작성일·SLA 표기 수정 완료</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="23" min="1" max="1"/>
@@ -2575,18 +2575,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
   </sheetData>
   <autoFilter ref="A3:F27"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="F5" s="29" t="inlineStr">
         <is>
-          <t>44개 세부항목 서술 완료(789.0점·3등급). 남은 사진·증빙 46칸(현장사진 29·자료 17) 확보 후 삽입, 1.1.5 [사진 2] 이미지 교체. Ⅲ장 종업원 수·매출액·인증업무 담당자 입력(물동량은 2025.6~12·2026.1~9 입력 완료), 작성 메모 14곳 삭제</t>
+          <t>44개 세부항목 서술 완료(787.0점·3등급). 남은 사진·증빙 45칸(현장사진 29·자료 16) 확보 후 삽입, 1.1.5 [사진 2] 이미지 교체. Ⅲ장 종업원 수·매출액·인증업무 담당자 입력(물동량은 2025.6~12·2026.1~9 입력 완료), 작성 메모 13곳 삭제</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="H5" s="29" t="inlineStr">
         <is>
-          <t>10.15: 지게차 서약서(8매)·2025 안전보건교육 기관수료증을 4칸에 삽입 → 105칸 중 59칸 삽입. 총 74쪽(PDF 변환 기준) / 10.15: Ⅲ장 물동량에 2025년 6~12월 출고 2,184,759박스 추가(6월부터 집계, 단위 박스로 통일). 매출액은 추후 수령 / 10.15: 2.1.1 도크 ⑦⑧·바닥 ⑥ 실내 접안 근거로 V 처리(3등급 유지, 바닥 ⑧⑨ 대기) / 10.15: 기준일자 2026.10.31로 변경</t>
+          <t>10.15: 지게차 서약서(8매)·2025 안전보건교육 기관수료증을 4칸에 삽입 → 105칸 중 59칸 삽입. 총 74쪽(PDF 변환 기준) / 10.15: Ⅲ장 물동량에 2025년 6~12월 출고 2,184,759박스 추가(6월부터 집계, 단위 박스로 통일). 매출액은 추후 수령 / 10.15: 2.1.1 도크 ⑦⑧·바닥 ⑥ 실내 접안 근거로 V 처리(3등급 유지, 바닥 ⑧⑨ 대기) / 10.15: 기준일자 2026.10.31로 변경 / 10.15: 2.2.2 UPH 실적(③④·판단근거) 기재, [사진 2] 월별 UPH 실적표 삽입 → 105칸 중 60칸, UPH 작성 메모 삭제, 총 75쪽 / 10.15: QR 작업자 추적을 "도입·시범 운영 중"으로 통일(1.1.2·2.1.5·2.2.1·2.2.2·2.3.1-4), 1.1.2 2→3등급(−2.0점) → 총점 787.0(3등급)</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F9" s="29" t="inlineStr">
         <is>
-          <t>3.2절 최근 3년 실적·물동량·RTO/RPO가 "예시" 수치 → 실제 값 교체, [작성 양식] 표 삭제</t>
+          <t>3.2절 최근 3년 실적·물동량·RTO/RPO가 "예시" 수치 → 실제 값 교체, [작성 양식] 표 삭제 (UPH 실적은 확보 — 01 2.2.2 실적표 참조)</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H9" s="29" t="inlineStr">
         <is>
-          <t>10.15 yun 「3_운영매뉴얼」: 상호→트랙스로지스코리아(주)·작성일 2026-09-30·KPI "목표(예시)"→"목표" 수정 완료. 실제 실적 수치는 여전히 필요</t>
+          <t>10.15 yun 「3_운영매뉴얼」: 상호→트랙스로지스코리아(주)·작성일 2026-09-30·KPI "목표(예시)"→"목표" 수정 완료. 실제 실적 수치는 여전히 필요 / 10.15: 13장 KPI UPH 산식(출고 박스÷투입 인시)·목표(OPS 815·풀필먼트 205박스/인·일)·2026.1~9 실적(OPS 86.5·풀필 24.8) 기재</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H10" s="29" t="inlineStr">
         <is>
-          <t>교육 이력 반영 확인(2025 정기 안전교육 1~4차, 지게차 서약 2026.06.23). 근거 파일 「교육 결과 보고서_2025.xls」 폴더에 확보. [ ] 19곳 남음 / 교육 결과 보고서_2025.pdf·지게차 서약서 PDF도 확보</t>
+          <t>교육 이력 반영 확인(2025 정기 안전교육 1~4차, 지게차 서약 2026.06.23). 근거 파일 「교육 결과 보고서_2025.xls」 폴더에 확보. [ ] 19곳 남음 / 교육 결과 보고서_2025.pdf·지게차 서약서 PDF도 확보 / 10.15: 비상 시 인원 확인을 일별 근무 현황(출근 명부) 기준으로 수정, 작업자 추적(QR)은 시범 운영 중으로 표기</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>근거 기준 조정본 789.0점(3등급). ②-1과 동일 등급으로 제출</t>
+          <t>근거 기준 조정본 787.0점(3등급). ②-1과 동일 등급으로 제출</t>
         </is>
       </c>
       <c r="G18" s="30" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="H18" s="30" t="inlineStr">
         <is>
-          <t>근거기준 점수표 789.0점(3등급) — 01·⑥·3번 시트와 44개 항목 등급 일치 확인</t>
+          <t>근거기준 점수표 787.0점(3등급) — 01·⑥·3번 시트와 44개 항목 등급 일치 확인 / 10.15: 1.1.2 2→3등급(QR 작업자 추적 시범 운영 중) 반영 → 787.0점</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
-          <t>10.15: 01 사진 추가에 맞춰 수록 쪽 재산정(총 74쪽), 캡션 103칸 01과 일치</t>
+          <t>10.15: 01 사진 추가에 맞춰 수록 쪽 재산정(총 74쪽), 캡션 103칸 01과 일치 / 10.15: 2.2.2 사진 추가로 2.2.2~2.3.2 수록 쪽 재산정(총 75쪽), 2.2.2 [사진 2] 캡션 01과 일치 / 10.15: 1.1.2 3등급, QR 관련 캡션 3칸 01과 일치</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="23" min="1" max="1"/>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E13" s="30" t="inlineStr">
         <is>
-          <t>실적 확보 필수 — 없으면 2.2 성과관리 등급 하락(허위기재 시 인증 취소 사유)</t>
+          <t>실적 확보 필수 — 없으면 2.2 성과관리 등급 하락(허위기재 시 인증 취소 사유) / 10.15: UPH는 2025.11~2026.10 실측 확보해 01 2.2.2 반영</t>
         </is>
       </c>
       <c r="F13" s="38" t="inlineStr">
@@ -2570,6 +2570,36 @@
         </is>
       </c>
       <c r="F27" s="39" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>UPH 산출 근거</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>01 2.2.2 ①②: 개인 QR 스캔 → 시스템이 UPH 산출</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="inlineStr">
+        <is>
+          <t>[사진 2] 실적표 출처는 센터 일별 운영실적 엑셀(공정별 근무시간·출고 물량). QR 기록은 누락이 많아 미사용. 2023~2025.5 자료 없음(2025.6 집계 시작)</t>
+        </is>
+      </c>
+      <c r="E28" s="30" t="inlineStr">
+        <is>
+          <t>10.15 반영: 01 2.2.2 ①~③·연동과정·판단근거를 실제 방식(출고 실적=TMS·WMS, 투입 인시=일별 근무 현황)으로 수정하고 ⑤에 "QR 작업자 추적 도입·시범 운영 중" 기재, 2.3.1-4 ③도 동일 표현. 추가 반영: 1.1.2 2→3등급, 2.1.5·2.2.1·06 비상 인원점검 표현도 "시범 운영 중"으로 통일 → 처리 완료</t>
+        </is>
+      </c>
+      <c r="F28" s="39" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
@@ -2727,7 +2757,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="43">
         <f>0.5*D5+0.5*D5*(1-(E5-1)/5)</f>
@@ -2743,7 +2773,7 @@
       </c>
       <c r="J5" s="30" t="inlineStr">
         <is>
-          <t>작업정보를 온라인·실시간 확인하고, 공정별 인원 관리(WMS-입고 공정)로 하역 투입 인원·작업시간을 실시간 확인·레포트 분석하므로 2등급 (2026.10.06 조정)</t>
+          <t>하역 작업 시 정보시스템(SW 입고신청·WMS)에서 제공된 작업정보를 온라인으로 확인하고 도착 처리 결과가 실시간 연동되므로 3등급으로 평가함. 하역 투입 인원·작업시간의 시스템 실시간 관리(QR 작업자 추적)는 도입·시범 운영 중이어서 2등급은 적용하지 않음(기존 2등급에서 조정). (2026.10.15 조정)</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4235,7 @@
       </c>
       <c r="J39" s="30" t="inlineStr">
         <is>
-          <t>정보시스템과 연계해 생산성 정보를 수집·모니터링·분석·피드백하므로 3등급으로 평가함.</t>
+          <t>정보시스템(TMS·SW(WMS))의 출고 실적과 일별 근무 현황의 투입 인시를 결합해 UPH를 월별로 모니터링·분석하고 일 목표 생산성 관리와 인력 배치에 피드백함(2026.1~9월 UPH OPS 86.5·풀필먼트 24.8, 풀필먼트 2025.11~12월 대비 약 43% 향상). 투입 인시의 시스템 자동 수집을 위해 QR 작업자 추적을 도입·시범 운영 중임. 이에 3등급으로 평가함.</t>
         </is>
       </c>
     </row>
@@ -4983,7 +5013,7 @@
       </c>
       <c r="F10" s="46" t="inlineStr">
         <is>
-          <t>SW(WMS) 공정별 인원관리 – 현재 투입 인원(WMS-입고 공정)</t>
+          <t>SW(WMS) 공정별 인원관리(QR, 시범 운영 중) – 현재 투입 인원(WMS-입고 공정)</t>
         </is>
       </c>
       <c r="G10" s="30" t="inlineStr">
@@ -5030,7 +5060,7 @@
       </c>
       <c r="F11" s="46" t="inlineStr">
         <is>
-          <t>SW(WMS) 공정별 인원관리 – 기간별 작업 레포트</t>
+          <t>SW(WMS) 공정별 인원관리(QR, 시범 운영 중) – 기간별 작업 레포트</t>
         </is>
       </c>
       <c r="G11" s="30" t="inlineStr">
@@ -8305,7 +8335,7 @@
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>SW(WMS) 공정별 인원관리 – 공정별 현재 투입 인원 실시간 파악(비상 시 인원 확인)</t>
+          <t>SW(WMS) 공정별 인원관리(QR, 시범 운영 중) – 공정별 현재 투입 인원 파악(비상 시 인원 확인)</t>
         </is>
       </c>
       <c r="G84" s="30" t="inlineStr">
@@ -8485,7 +8515,7 @@
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>SW(WMS) 공정별 인원 관리 – 공정별·인원별 작업자 수·처리량·작업시간 집계</t>
+          <t>SW(WMS) 작업자 추적(QR, 시범 운영 중) – 공정별·인원별 작업자 수·처리량·작업시간 집계 화면</t>
         </is>
       </c>
       <c r="G88" s="30" t="inlineStr">
@@ -8526,7 +8556,7 @@
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>p.62</t>
+          <t>p.63</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
@@ -8536,7 +8566,7 @@
       </c>
       <c r="F89" s="30" t="inlineStr">
         <is>
-          <t>최근 3년 UPH 실적표</t>
+          <t>월별 UPH 실적표(2025.11~2026.10) – 공정별 출고 박스÷투입 인시, 풀필먼트 UPH 19.3→27.6(약 43% 향상)</t>
         </is>
       </c>
       <c r="G89" s="30" t="inlineStr">
@@ -8545,9 +8575,21 @@
         </is>
       </c>
       <c r="H89" s="29" t="n"/>
-      <c r="I89" s="29" t="n"/>
-      <c r="J89" s="29" t="n"/>
-      <c r="K89" s="29" t="n"/>
+      <c r="I89" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J89" s="29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" s="29" t="inlineStr">
+        <is>
+          <t>10.15: 기존 캡션 「최근 3년 UPH 실적표」 → 운영실적 기반 월별 UPH 실적표 작성·삽입</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="24">
       <c r="A90" s="29" t="n">
@@ -8565,7 +8607,7 @@
       </c>
       <c r="D90" s="29" t="inlineStr">
         <is>
-          <t>p.63~64</t>
+          <t>p.64~65</t>
         </is>
       </c>
       <c r="E90" s="29" t="inlineStr">
@@ -8604,7 +8646,7 @@
       </c>
       <c r="D91" s="29" t="inlineStr">
         <is>
-          <t>p.63~64</t>
+          <t>p.64~65</t>
         </is>
       </c>
       <c r="E91" s="29" t="inlineStr">
@@ -8643,7 +8685,7 @@
       </c>
       <c r="D92" s="29" t="inlineStr">
         <is>
-          <t>p.63~64</t>
+          <t>p.64~65</t>
         </is>
       </c>
       <c r="E92" s="29" t="inlineStr">
@@ -8694,7 +8736,7 @@
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>p.65</t>
+          <t>p.66</t>
         </is>
       </c>
       <c r="E93" s="29" t="inlineStr">
@@ -8733,7 +8775,7 @@
       </c>
       <c r="D94" s="29" t="inlineStr">
         <is>
-          <t>p.65</t>
+          <t>p.66</t>
         </is>
       </c>
       <c r="E94" s="29" t="inlineStr">
@@ -8772,7 +8814,7 @@
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>p.65</t>
+          <t>p.66</t>
         </is>
       </c>
       <c r="E95" s="29" t="inlineStr">
@@ -8811,7 +8853,7 @@
       </c>
       <c r="D96" s="29" t="inlineStr">
         <is>
-          <t>p.66~67</t>
+          <t>p.67~68</t>
         </is>
       </c>
       <c r="E96" s="29" t="inlineStr">
@@ -8862,7 +8904,7 @@
       </c>
       <c r="D97" s="29" t="inlineStr">
         <is>
-          <t>p.66~67</t>
+          <t>p.67~68</t>
         </is>
       </c>
       <c r="E97" s="29" t="inlineStr">
@@ -8913,7 +8955,7 @@
       </c>
       <c r="D98" s="29" t="inlineStr">
         <is>
-          <t>p.68~69</t>
+          <t>p.69~70</t>
         </is>
       </c>
       <c r="E98" s="29" t="inlineStr">
@@ -8964,7 +9006,7 @@
       </c>
       <c r="D99" s="29" t="inlineStr">
         <is>
-          <t>p.68~69</t>
+          <t>p.69~70</t>
         </is>
       </c>
       <c r="E99" s="29" t="inlineStr">
@@ -9015,7 +9057,7 @@
       </c>
       <c r="D100" s="29" t="inlineStr">
         <is>
-          <t>p.70</t>
+          <t>p.71</t>
         </is>
       </c>
       <c r="E100" s="29" t="inlineStr">
@@ -9066,7 +9108,7 @@
       </c>
       <c r="D101" s="29" t="inlineStr">
         <is>
-          <t>p.71</t>
+          <t>p.72</t>
         </is>
       </c>
       <c r="E101" s="29" t="inlineStr">
@@ -9117,7 +9159,7 @@
       </c>
       <c r="D102" s="29" t="inlineStr">
         <is>
-          <t>p.72~73</t>
+          <t>p.73~74</t>
         </is>
       </c>
       <c r="E102" s="29" t="inlineStr">
@@ -9168,7 +9210,7 @@
       </c>
       <c r="D103" s="29" t="inlineStr">
         <is>
-          <t>p.72~73</t>
+          <t>p.73~74</t>
         </is>
       </c>
       <c r="E103" s="29" t="inlineStr">
@@ -9219,7 +9261,7 @@
       </c>
       <c r="D104" s="29" t="inlineStr">
         <is>
-          <t>p.72~73</t>
+          <t>p.73~74</t>
         </is>
       </c>
       <c r="E104" s="29" t="inlineStr">
@@ -9270,7 +9312,7 @@
       </c>
       <c r="D105" s="29" t="inlineStr">
         <is>
-          <t>p.74</t>
+          <t>p.75</t>
         </is>
       </c>
       <c r="E105" s="29" t="inlineStr">
@@ -9321,7 +9363,7 @@
       </c>
       <c r="D106" s="29" t="inlineStr">
         <is>
-          <t>p.74</t>
+          <t>p.75</t>
         </is>
       </c>
       <c r="E106" s="29" t="inlineStr">
@@ -9344,6 +9386,7 @@
       <c r="J106" s="29" t="n"/>
       <c r="K106" s="29" t="n"/>
     </row>
+    <row r="107"/>
     <row r="108">
       <c r="B108" s="48" t="inlineStr">
         <is>
@@ -9481,11 +9524,11 @@
         </is>
       </c>
       <c r="C4" s="29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="30" t="inlineStr">
         <is>
-          <t>도크레벨러 수량 확인 필요: 02 설계설명서는 1개소, Lay-out(2026.07.27)에는 2개소 표기. (10.06 조정으로 현재 2등급)</t>
+          <t>도크레벨러 수량 확인 필요: 02 설계설명서는 1개소, Lay-out(2026.07.27)에는 2개소 표기. (10.15: QR 작업자 추적 시범 운영 중이라 3등급으로 환원. QR 정착·실시간 레포트 운영 시 2등급 상향 가능, +2.0점)</t>
         </is>
       </c>
     </row>
@@ -9645,7 +9688,7 @@
       </c>
       <c r="D12" s="29" t="inlineStr">
         <is>
-          <t>UPH 실적(42→46→50건)이 "예시" 수치. 실제 데이터로 교체.</t>
+          <t>10.15 반영: UPH 실측(2025.11~2026.10, 운영실적 기준) 기재, 실제 집계 방식(근무 현황 기반 인시)과 QR 도입·시범 운영 중으로 서술. 3등급 유지. 심사에서 인시 수기 집계를 "정보시스템 연계 부족"으로 보면 4등급(−3.0점, 총점 784.0, 3등급 유지). 3개년: 공고문은 "최근 3년 이내 실적 중심"이라 2025.6 이후 자료로 충분</t>
         </is>
       </c>
     </row>

--- a/작성 서류 - yun/00_진행현황_누락점검표.xlsx
+++ b/작성 서류 - yun/00_진행현황_누락점검표.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>10.15: 지게차 서약서(8매)·2025 안전보건교육 기관수료증을 4칸에 삽입 → 105칸 중 59칸 삽입. 총 74쪽(PDF 변환 기준) / 10.15: Ⅲ장 물동량에 2025년 6~12월 출고 2,184,759박스 추가(6월부터 집계, 단위 박스로 통일). 매출액은 추후 수령 / 10.15: 2.1.1 도크 ⑦⑧·바닥 ⑥ 실내 접안 근거로 V 처리(3등급 유지, 바닥 ⑧⑨ 대기) / 10.15: 기준일자 2026.10.31로 변경 / 10.15: 2.2.2 UPH 실적(③④·판단근거) 기재, [사진 2] 월별 UPH 실적표 삽입 → 105칸 중 60칸, UPH 작성 메모 삭제, 총 75쪽 / 10.15: QR 작업자 추적을 "도입·시범 운영 중"으로 통일(1.1.2·2.1.5·2.2.1·2.2.2·2.3.1-4), 1.1.2 2→3등급(−2.0점) → 총점 787.0(3등급) / 10.15: 휠소터 시간당 3,500개·슈트 18개 반영(1.6/2.3 설비 칸), 2.2.4 ③ "LED 조명 미적용" 확정·[사진 3] 캡션 변경·작성 메모 삭제 / 10.16: 사용자 평가요소 확인 반영 — 2.1.1 2등급(바닥 ⑧⑨ V), 2.1.3 1등급(확인 3개 V), 2.1.4 미적용(①~④ 미적용 → 미적용 6개, 0점), 2.1.5 4등급(랙 내진 미적용). 도크레벨러 1개소, 인증업무 담당자 장윤진, 휠소터 3,500개 재반영 → 총점 772.0(3등급, 750 기준 여유 22점) / 10.16: 2.3.2 [사진 2] 휠소터 실도면 삽입(105칸 중 61칸), 총 75쪽 유지 / 10.16: DAS 운영 중단 반영(1.4 피킹 설비·지시, 2.3.2 설비 칸에서 DAS 삭제) / 10.16: 2.2.2 UPH 실적표를 2026.09 마감 기준으로 조정(10월 1~14일 제외), 2.3.2 사진 크기 조정으로 총 75쪽 유지</t>
+          <t>10.15: 지게차 서약서(8매)·2025 안전보건교육 기관수료증을 4칸에 삽입 → 105칸 중 59칸 삽입. 총 74쪽(PDF 변환 기준) / 10.15: Ⅲ장 물동량에 2025년 6~12월 출고 2,184,759박스 추가(6월부터 집계, 단위 박스로 통일). 매출액은 추후 수령 / 10.15: 2.1.1 도크 ⑦⑧·바닥 ⑥ 실내 접안 근거로 V 처리(3등급 유지, 바닥 ⑧⑨ 대기) / 10.15: 기준일자 2026.10.31로 변경 / 10.15: 2.2.2 UPH 실적(③④·판단근거) 기재, [사진 2] 월별 UPH 실적표 삽입 → 105칸 중 60칸, UPH 작성 메모 삭제, 총 75쪽 / 10.15: QR 작업자 추적을 "도입·시범 운영 중"으로 통일(1.1.2·2.1.5·2.2.1·2.2.2·2.3.1-4), 1.1.2 2→3등급(−2.0점) → 총점 787.0(3등급) / 10.15: 휠소터 시간당 3,500개·슈트 18개 반영(1.6/2.3 설비 칸), 2.2.4 ③ "LED 조명 미적용" 확정·[사진 3] 캡션 변경·작성 메모 삭제 / 10.16: 사용자 평가요소 확인 반영 — 2.1.1 2등급(바닥 ⑧⑨ V), 2.1.3 1등급(확인 3개 V), 2.1.4 미적용(①~④ 미적용 → 미적용 6개, 0점), 2.1.5 4등급(랙 내진 미적용). 도크레벨러 1개소, 인증업무 담당자 장윤진, 휠소터 3,500개 재반영 → 총점 772.0(3등급, 750 기준 여유 22점) / 10.16: 2.3.2 [사진 2] 휠소터 실도면 삽입(105칸 중 61칸), 총 75쪽 유지 / 10.16: DAS 운영 중단 반영(1.4 피킹 설비·지시, 2.3.2 설비 칸에서 DAS 삭제) / 10.16: 2.2.2 UPH 실적표를 2026.09 마감 기준으로 조정(10월 1~14일 제외), 2.3.2 사진 크기 조정으로 총 75쪽 유지 / 10.16: 1.4 피킹 영역 500㎡→478.1㎡(02 Lay-out 기준 통일)</t>
         </is>
       </c>
       <c r="I5" s="36" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>변동 없음. 작성 메모 2곳(검수+맵핑 877.5㎡ 분야 배정, 출고 처리능력 30,000 vs 35,000), 단면도 "확보 필요", 상호 일부 "트랙스로지스" 표기 / 10.15: 처리능력 휠소터 시간당 약 4,000개 → 3,500개(슈트 18개)로 수정 / 10.16: 입고 주요 설비에서 휴대용 DWS 삭제(휴대용 DWS 없음 확인), 도크레벨러 1개소 표기</t>
+          <t>변동 없음. 작성 메모 2곳(검수+맵핑 877.5㎡ 분야 배정, 출고 처리능력 30,000 vs 35,000), 단면도 "확보 필요", 상호 일부 "트랙스로지스" 표기 / 10.15: 처리능력 휠소터 시간당 약 4,000개 → 3,500개(슈트 18개)로 수정 / 10.16: 입고 주요 설비에서 휴대용 DWS 삭제(휴대용 DWS 없음 확인), 도크레벨러 1개소 표기 / 10.16: 면적 운영면적 기준(2,845평≈9,405㎡) 확인, 피킹 478.1㎡ 메모 삭제(01도 478.1㎡로 통일). 작성 메모 1곳(검수+맵핑 877.5㎡ 분야 배정) 남음</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
